--- a/docs/DEMO_Agrodrones_Bajio_FICTICIO.xlsx
+++ b/docs/DEMO_Agrodrones_Bajio_FICTICIO.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="344">
   <si>
     <t xml:space="preserve">ARCHIVO DE DEMOSTRACION — DATOS COMPLETAMENTE FICTICIOS</t>
   </si>
@@ -2233,17 +2233,17 @@
       </c>
       <c r="P10" s="15" t="n">
         <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A10,cobranza!$D$3:$D$1000),0)</f>
-        <v>100000</v>
+        <v>124000</v>
       </c>
       <c r="Q10" s="15" t="n">
         <f aca="false">IFERROR(H10-P10,"")</f>
-        <v>165000</v>
+        <v>141000</v>
       </c>
       <c r="R10" s="17"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B11" s="12" t="n">
         <v>46119</v>
@@ -2271,9 +2271,7 @@
         <v>47</v>
       </c>
       <c r="K11" s="11"/>
-      <c r="L11" s="11" t="s">
-        <v>58</v>
-      </c>
+      <c r="L11" s="11"/>
       <c r="M11" s="11" t="s">
         <v>48</v>
       </c>
@@ -2287,11 +2285,11 @@
       </c>
       <c r="P11" s="15" t="n">
         <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A11,cobranza!$D$3:$D$1000),0)</f>
-        <v>24000</v>
+        <v>124000</v>
       </c>
       <c r="Q11" s="15" t="n">
         <f aca="false">IFERROR(H11-P11,"")</f>
-        <v>0</v>
+        <v>-100000</v>
       </c>
       <c r="R11" s="17"/>
     </row>
@@ -2615,17 +2613,17 @@
       </c>
       <c r="P17" s="15" t="n">
         <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A17,cobranza!$D$3:$D$1000),0)</f>
-        <v>420000</v>
+        <v>431500</v>
       </c>
       <c r="Q17" s="15" t="n">
         <f aca="false">IFERROR(H17-P17,"")</f>
-        <v>100000</v>
+        <v>88500</v>
       </c>
       <c r="R17" s="17"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B18" s="12" t="n">
         <v>46205</v>
@@ -2669,11 +2667,11 @@
       </c>
       <c r="P18" s="15" t="n">
         <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A18,cobranza!$D$3:$D$1000),0)</f>
-        <v>11500</v>
+        <v>431500</v>
       </c>
       <c r="Q18" s="15" t="n">
         <f aca="false">IFERROR(H18-P18,"")</f>
-        <v>0</v>
+        <v>-420000</v>
       </c>
       <c r="R18" s="17"/>
     </row>
@@ -12241,7 +12239,7 @@
         <v>141</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C14" s="12" t="n">
         <v>46119</v>
@@ -12430,7 +12428,7 @@
         <v>151</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C23" s="12" t="n">
         <v>46205</v>

--- a/docs/DEMO_Agrodrones_Bajio_FICTICIO.xlsx
+++ b/docs/DEMO_Agrodrones_Bajio_FICTICIO.xlsx
@@ -1570,7 +1570,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:B17"/>
+  <dimension ref="B2:B26"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="100"/>
@@ -1646,6 +1646,62 @@
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="2" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Dos ventas con varios productos en el mismo folio (V-008 y V-015).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Avisos que vera al cargar este archivo. Ninguno es un error: estan puestos a proposito.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Linea Demo (V-006): es una unidad de exhibicion, no una venta. Se lista aparte y no cuenta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Abonos que suman mas que el precio (V-018): se cobro de mas, para mostrar un saldo a favor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Falta fecha (V-025): una venta sin fecha de entrega. Se reporta aparte, no se descarta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Condicion distinta en sus partidas (V-015): el equipo dice Credito y su accesorio Contado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    La aplicacion aplica el primero a toda la venta y lo avisa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Sin dias de credito y con saldo (cinco ventas): su antiguedad se mide desde la entrega.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/docs/DEMO_Agrodrones_Bajio_FICTICIO.xlsx
+++ b/docs/DEMO_Agrodrones_Bajio_FICTICIO.xlsx
@@ -1846,11 +1846,11 @@
         <v>0.269230769230769</v>
       </c>
       <c r="P3" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A3,cobranza!$D$3:$D$1000),0)</f>
+        <f aca="false">IF($A3="","",IF(COUNTIF($A$3:$A3,$A3)=1,SUMIF(cobranza!$B$3:$B$1000,$A3,cobranza!$D$3:$D$1000),"↑"))</f>
         <v>200000</v>
       </c>
       <c r="Q3" s="15" t="n">
-        <f aca="false">IFERROR(H3-P3,"")</f>
+        <f aca="false">IF($A3="","",IF(COUNTIF($A$3:$A3,$A3)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A3,$C$3:$C$1000,"&lt;&gt;Demo")-P3,"↑"))</f>
         <v>320000</v>
       </c>
       <c r="R3" s="17"/>
@@ -1900,11 +1900,11 @@
         <v>0.283018867924528</v>
       </c>
       <c r="P4" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A4,cobranza!$D$3:$D$1000),0)</f>
+        <f aca="false">IF($A4="","",IF(COUNTIF($A$3:$A4,$A4)=1,SUMIF(cobranza!$B$3:$B$1000,$A4,cobranza!$D$3:$D$1000),"↑"))</f>
         <v>90000</v>
       </c>
       <c r="Q4" s="15" t="n">
-        <f aca="false">IFERROR(H4-P4,"")</f>
+        <f aca="false">IF($A4="","",IF(COUNTIF($A$3:$A4,$A4)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A4,$C$3:$C$1000,"&lt;&gt;Demo")-P4,"↑"))</f>
         <v>175000</v>
       </c>
       <c r="R4" s="17"/>
@@ -1956,11 +1956,11 @@
         <v>0.233766233766234</v>
       </c>
       <c r="P5" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A5,cobranza!$D$3:$D$1000),0)</f>
+        <f aca="false">IF($A5="","",IF(COUNTIF($A$3:$A5,$A5)=1,SUMIF(cobranza!$B$3:$B$1000,$A5,cobranza!$D$3:$D$1000),"↑"))</f>
         <v>210000</v>
       </c>
       <c r="Q5" s="15" t="n">
-        <f aca="false">IFERROR(H5-P5,"")</f>
+        <f aca="false">IF($A5="","",IF(COUNTIF($A$3:$A5,$A5)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A5,$C$3:$C$1000,"&lt;&gt;Demo")-P5,"↑"))</f>
         <v>175000</v>
       </c>
       <c r="R5" s="17"/>
@@ -2010,11 +2010,11 @@
         <v>0.333333333333333</v>
       </c>
       <c r="P6" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A6,cobranza!$D$3:$D$1000),0)</f>
+        <f aca="false">IF($A6="","",IF(COUNTIF($A$3:$A6,$A6)=1,SUMIF(cobranza!$B$3:$B$1000,$A6,cobranza!$D$3:$D$1000),"↑"))</f>
         <v>42000</v>
       </c>
       <c r="Q6" s="15" t="n">
-        <f aca="false">IFERROR(H6-P6,"")</f>
+        <f aca="false">IF($A6="","",IF(COUNTIF($A$3:$A6,$A6)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A6,$C$3:$C$1000,"&lt;&gt;Demo")-P6,"↑"))</f>
         <v>0</v>
       </c>
       <c r="R6" s="17"/>
@@ -2066,11 +2066,11 @@
         <v>0.280898876404494</v>
       </c>
       <c r="P7" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A7,cobranza!$D$3:$D$1000),0)</f>
+        <f aca="false">IF($A7="","",IF(COUNTIF($A$3:$A7,$A7)=1,SUMIF(cobranza!$B$3:$B$1000,$A7,cobranza!$D$3:$D$1000),"↑"))</f>
         <v>178000</v>
       </c>
       <c r="Q7" s="15" t="n">
-        <f aca="false">IFERROR(H7-P7,"")</f>
+        <f aca="false">IF($A7="","",IF(COUNTIF($A$3:$A7,$A7)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A7,$C$3:$C$1000,"&lt;&gt;Demo")-P7,"↑"))</f>
         <v>0</v>
       </c>
       <c r="R7" s="17"/>
@@ -2116,11 +2116,11 @@
         <v/>
       </c>
       <c r="P8" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A8,cobranza!$D$3:$D$1000),0)</f>
+        <f aca="false">IF($A8="","",IF(COUNTIF($A$3:$A8,$A8)=1,SUMIF(cobranza!$B$3:$B$1000,$A8,cobranza!$D$3:$D$1000),"↑"))</f>
         <v>295000</v>
       </c>
       <c r="Q8" s="15" t="n">
-        <f aca="false">IFERROR(H8-P8,"")</f>
+        <f aca="false">IF($A8="","",IF(COUNTIF($A$3:$A8,$A8)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A8,$C$3:$C$1000,"&lt;&gt;Demo")-P8,"↑"))</f>
         <v>-295000</v>
       </c>
       <c r="R8" s="18" t="s">
@@ -2176,11 +2176,11 @@
         <v>0.269230769230769</v>
       </c>
       <c r="P9" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A9,cobranza!$D$3:$D$1000),0)</f>
+        <f aca="false">IF($A9="","",IF(COUNTIF($A$3:$A9,$A9)=1,SUMIF(cobranza!$B$3:$B$1000,$A9,cobranza!$D$3:$D$1000),"↑"))</f>
         <v>295000</v>
       </c>
       <c r="Q9" s="15" t="n">
-        <f aca="false">IFERROR(H9-P9,"")</f>
+        <f aca="false">IF($A9="","",IF(COUNTIF($A$3:$A9,$A9)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A9,$C$3:$C$1000,"&lt;&gt;Demo")-P9,"↑"))</f>
         <v>225000</v>
       </c>
       <c r="R9" s="17"/>
@@ -2232,12 +2232,12 @@
         <v>0.283018867924528</v>
       </c>
       <c r="P10" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A10,cobranza!$D$3:$D$1000),0)</f>
+        <f aca="false">IF($A10="","",IF(COUNTIF($A$3:$A10,$A10)=1,SUMIF(cobranza!$B$3:$B$1000,$A10,cobranza!$D$3:$D$1000),"↑"))</f>
         <v>124000</v>
       </c>
       <c r="Q10" s="15" t="n">
-        <f aca="false">IFERROR(H10-P10,"")</f>
-        <v>141000</v>
+        <f aca="false">IF($A10="","",IF(COUNTIF($A$3:$A10,$A10)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A10,$C$3:$C$1000,"&lt;&gt;Demo")-P10,"↑"))</f>
+        <v>165000</v>
       </c>
       <c r="R10" s="17"/>
     </row>
@@ -2283,13 +2283,13 @@
         <f aca="false">IFERROR(N11/H11,"")</f>
         <v>0.395833333333333</v>
       </c>
-      <c r="P11" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A11,cobranza!$D$3:$D$1000),0)</f>
-        <v>124000</v>
-      </c>
-      <c r="Q11" s="15" t="n">
-        <f aca="false">IFERROR(H11-P11,"")</f>
-        <v>-100000</v>
+      <c r="P11" s="15" t="str">
+        <f aca="false">IF($A11="","",IF(COUNTIF($A$3:$A11,$A11)=1,SUMIF(cobranza!$B$3:$B$1000,$A11,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v>↑</v>
+      </c>
+      <c r="Q11" s="15" t="str">
+        <f aca="false">IF($A11="","",IF(COUNTIF($A$3:$A11,$A11)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A11,$C$3:$C$1000,"&lt;&gt;Demo")-P11,"↑"))</f>
+        <v>↑</v>
       </c>
       <c r="R11" s="17"/>
     </row>
@@ -2336,11 +2336,11 @@
         <v>0.4375</v>
       </c>
       <c r="P12" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A12,cobranza!$D$3:$D$1000),0)</f>
+        <f aca="false">IF($A12="","",IF(COUNTIF($A$3:$A12,$A12)=1,SUMIF(cobranza!$B$3:$B$1000,$A12,cobranza!$D$3:$D$1000),"↑"))</f>
         <v>32000</v>
       </c>
       <c r="Q12" s="15" t="n">
-        <f aca="false">IFERROR(H12-P12,"")</f>
+        <f aca="false">IF($A12="","",IF(COUNTIF($A$3:$A12,$A12)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A12,$C$3:$C$1000,"&lt;&gt;Demo")-P12,"↑"))</f>
         <v>0</v>
       </c>
       <c r="R12" s="17"/>
@@ -2394,11 +2394,11 @@
         <v>0.233766233766234</v>
       </c>
       <c r="P13" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A13,cobranza!$D$3:$D$1000),0)</f>
+        <f aca="false">IF($A13="","",IF(COUNTIF($A$3:$A13,$A13)=1,SUMIF(cobranza!$B$3:$B$1000,$A13,cobranza!$D$3:$D$1000),"↑"))</f>
         <v>290000</v>
       </c>
       <c r="Q13" s="15" t="n">
-        <f aca="false">IFERROR(H13-P13,"")</f>
+        <f aca="false">IF($A13="","",IF(COUNTIF($A$3:$A13,$A13)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A13,$C$3:$C$1000,"&lt;&gt;Demo")-P13,"↑"))</f>
         <v>95000</v>
       </c>
       <c r="R13" s="17"/>
@@ -2446,11 +2446,11 @@
         <v>0.625</v>
       </c>
       <c r="P14" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A14,cobranza!$D$3:$D$1000),0)</f>
+        <f aca="false">IF($A14="","",IF(COUNTIF($A$3:$A14,$A14)=1,SUMIF(cobranza!$B$3:$B$1000,$A14,cobranza!$D$3:$D$1000),"↑"))</f>
         <v>12000</v>
       </c>
       <c r="Q14" s="15" t="n">
-        <f aca="false">IFERROR(H14-P14,"")</f>
+        <f aca="false">IF($A14="","",IF(COUNTIF($A$3:$A14,$A14)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A14,$C$3:$C$1000,"&lt;&gt;Demo")-P14,"↑"))</f>
         <v>0</v>
       </c>
       <c r="R14" s="17"/>
@@ -2500,11 +2500,11 @@
         <v>0.280898876404494</v>
       </c>
       <c r="P15" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A15,cobranza!$D$3:$D$1000),0)</f>
+        <f aca="false">IF($A15="","",IF(COUNTIF($A$3:$A15,$A15)=1,SUMIF(cobranza!$B$3:$B$1000,$A15,cobranza!$D$3:$D$1000),"↑"))</f>
         <v>60000</v>
       </c>
       <c r="Q15" s="15" t="n">
-        <f aca="false">IFERROR(H15-P15,"")</f>
+        <f aca="false">IF($A15="","",IF(COUNTIF($A$3:$A15,$A15)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A15,$C$3:$C$1000,"&lt;&gt;Demo")-P15,"↑"))</f>
         <v>118000</v>
       </c>
       <c r="R15" s="17"/>
@@ -2554,11 +2554,11 @@
         <v>0.448979591836735</v>
       </c>
       <c r="P16" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A16,cobranza!$D$3:$D$1000),0)</f>
+        <f aca="false">IF($A16="","",IF(COUNTIF($A$3:$A16,$A16)=1,SUMIF(cobranza!$B$3:$B$1000,$A16,cobranza!$D$3:$D$1000),"↑"))</f>
         <v>9800</v>
       </c>
       <c r="Q16" s="15" t="n">
-        <f aca="false">IFERROR(H16-P16,"")</f>
+        <f aca="false">IF($A16="","",IF(COUNTIF($A$3:$A16,$A16)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A16,$C$3:$C$1000,"&lt;&gt;Demo")-P16,"↑"))</f>
         <v>0</v>
       </c>
       <c r="R16" s="17"/>
@@ -2612,12 +2612,12 @@
         <v>0.269230769230769</v>
       </c>
       <c r="P17" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A17,cobranza!$D$3:$D$1000),0)</f>
+        <f aca="false">IF($A17="","",IF(COUNTIF($A$3:$A17,$A17)=1,SUMIF(cobranza!$B$3:$B$1000,$A17,cobranza!$D$3:$D$1000),"↑"))</f>
         <v>431500</v>
       </c>
       <c r="Q17" s="15" t="n">
-        <f aca="false">IFERROR(H17-P17,"")</f>
-        <v>88500</v>
+        <f aca="false">IF($A17="","",IF(COUNTIF($A$3:$A17,$A17)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A17,$C$3:$C$1000,"&lt;&gt;Demo")-P17,"↑"))</f>
+        <v>100000</v>
       </c>
       <c r="R17" s="17"/>
     </row>
@@ -2665,13 +2665,13 @@
         <f aca="false">IFERROR(N18/H18,"")</f>
         <v>0.408695652173913</v>
       </c>
-      <c r="P18" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A18,cobranza!$D$3:$D$1000),0)</f>
-        <v>431500</v>
-      </c>
-      <c r="Q18" s="15" t="n">
-        <f aca="false">IFERROR(H18-P18,"")</f>
-        <v>-420000</v>
+      <c r="P18" s="15" t="str">
+        <f aca="false">IF($A18="","",IF(COUNTIF($A$3:$A18,$A18)=1,SUMIF(cobranza!$B$3:$B$1000,$A18,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v>↑</v>
+      </c>
+      <c r="Q18" s="15" t="str">
+        <f aca="false">IF($A18="","",IF(COUNTIF($A$3:$A18,$A18)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A18,$C$3:$C$1000,"&lt;&gt;Demo")-P18,"↑"))</f>
+        <v>↑</v>
       </c>
       <c r="R18" s="17"/>
     </row>
@@ -2722,11 +2722,11 @@
         <v>0.283018867924528</v>
       </c>
       <c r="P19" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A19,cobranza!$D$3:$D$1000),0)</f>
+        <f aca="false">IF($A19="","",IF(COUNTIF($A$3:$A19,$A19)=1,SUMIF(cobranza!$B$3:$B$1000,$A19,cobranza!$D$3:$D$1000),"↑"))</f>
         <v>150000</v>
       </c>
       <c r="Q19" s="15" t="n">
-        <f aca="false">IFERROR(H19-P19,"")</f>
+        <f aca="false">IF($A19="","",IF(COUNTIF($A$3:$A19,$A19)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A19,$C$3:$C$1000,"&lt;&gt;Demo")-P19,"↑"))</f>
         <v>115000</v>
       </c>
       <c r="R19" s="17"/>
@@ -2776,11 +2776,11 @@
         <v>0.457627118644068</v>
       </c>
       <c r="P20" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A20,cobranza!$D$3:$D$1000),0)</f>
+        <f aca="false">IF($A20="","",IF(COUNTIF($A$3:$A20,$A20)=1,SUMIF(cobranza!$B$3:$B$1000,$A20,cobranza!$D$3:$D$1000),"↑"))</f>
         <v>6100</v>
       </c>
       <c r="Q20" s="15" t="n">
-        <f aca="false">IFERROR(H20-P20,"")</f>
+        <f aca="false">IF($A20="","",IF(COUNTIF($A$3:$A20,$A20)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A20,$C$3:$C$1000,"&lt;&gt;Demo")-P20,"↑"))</f>
         <v>-200</v>
       </c>
       <c r="R20" s="17"/>
@@ -2834,11 +2834,11 @@
         <v>0.233766233766234</v>
       </c>
       <c r="P21" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A21,cobranza!$D$3:$D$1000),0)</f>
+        <f aca="false">IF($A21="","",IF(COUNTIF($A$3:$A21,$A21)=1,SUMIF(cobranza!$B$3:$B$1000,$A21,cobranza!$D$3:$D$1000),"↑"))</f>
         <v>180000</v>
       </c>
       <c r="Q21" s="15" t="n">
-        <f aca="false">IFERROR(H21-P21,"")</f>
+        <f aca="false">IF($A21="","",IF(COUNTIF($A$3:$A21,$A21)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A21,$C$3:$C$1000,"&lt;&gt;Demo")-P21,"↑"))</f>
         <v>205000</v>
       </c>
       <c r="R21" s="17"/>
@@ -2886,11 +2886,11 @@
         <v>0.4375</v>
       </c>
       <c r="P22" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A22,cobranza!$D$3:$D$1000),0)</f>
+        <f aca="false">IF($A22="","",IF(COUNTIF($A$3:$A22,$A22)=1,SUMIF(cobranza!$B$3:$B$1000,$A22,cobranza!$D$3:$D$1000),"↑"))</f>
         <v>32000</v>
       </c>
       <c r="Q22" s="15" t="n">
-        <f aca="false">IFERROR(H22-P22,"")</f>
+        <f aca="false">IF($A22="","",IF(COUNTIF($A$3:$A22,$A22)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A22,$C$3:$C$1000,"&lt;&gt;Demo")-P22,"↑"))</f>
         <v>0</v>
       </c>
       <c r="R22" s="17"/>
@@ -2942,11 +2942,11 @@
         <v>0.280898876404494</v>
       </c>
       <c r="P23" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A23,cobranza!$D$3:$D$1000),0)</f>
+        <f aca="false">IF($A23="","",IF(COUNTIF($A$3:$A23,$A23)=1,SUMIF(cobranza!$B$3:$B$1000,$A23,cobranza!$D$3:$D$1000),"↑"))</f>
         <v>80000</v>
       </c>
       <c r="Q23" s="15" t="n">
-        <f aca="false">IFERROR(H23-P23,"")</f>
+        <f aca="false">IF($A23="","",IF(COUNTIF($A$3:$A23,$A23)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A23,$C$3:$C$1000,"&lt;&gt;Demo")-P23,"↑"))</f>
         <v>98000</v>
       </c>
       <c r="R23" s="17"/>
@@ -2996,11 +2996,11 @@
         <v>0.472222222222222</v>
       </c>
       <c r="P24" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A24,cobranza!$D$3:$D$1000),0)</f>
+        <f aca="false">IF($A24="","",IF(COUNTIF($A$3:$A24,$A24)=1,SUMIF(cobranza!$B$3:$B$1000,$A24,cobranza!$D$3:$D$1000),"↑"))</f>
         <v>3600</v>
       </c>
       <c r="Q24" s="15" t="n">
-        <f aca="false">IFERROR(H24-P24,"")</f>
+        <f aca="false">IF($A24="","",IF(COUNTIF($A$3:$A24,$A24)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A24,$C$3:$C$1000,"&lt;&gt;Demo")-P24,"↑"))</f>
         <v>0</v>
       </c>
       <c r="R24" s="17"/>
@@ -3050,11 +3050,11 @@
         <v>0.283018867924528</v>
       </c>
       <c r="P25" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A25,cobranza!$D$3:$D$1000),0)</f>
+        <f aca="false">IF($A25="","",IF(COUNTIF($A$3:$A25,$A25)=1,SUMIF(cobranza!$B$3:$B$1000,$A25,cobranza!$D$3:$D$1000),"↑"))</f>
         <v>100000</v>
       </c>
       <c r="Q25" s="15" t="n">
-        <f aca="false">IFERROR(H25-P25,"")</f>
+        <f aca="false">IF($A25="","",IF(COUNTIF($A$3:$A25,$A25)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A25,$C$3:$C$1000,"&lt;&gt;Demo")-P25,"↑"))</f>
         <v>165000</v>
       </c>
       <c r="R25" s="17"/>
@@ -3104,11 +3104,11 @@
         <v>0.408695652173913</v>
       </c>
       <c r="P26" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A26,cobranza!$D$3:$D$1000),0)</f>
+        <f aca="false">IF($A26="","",IF(COUNTIF($A$3:$A26,$A26)=1,SUMIF(cobranza!$B$3:$B$1000,$A26,cobranza!$D$3:$D$1000),"↑"))</f>
         <v>11500</v>
       </c>
       <c r="Q26" s="15" t="n">
-        <f aca="false">IFERROR(H26-P26,"")</f>
+        <f aca="false">IF($A26="","",IF(COUNTIF($A$3:$A26,$A26)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A26,$C$3:$C$1000,"&lt;&gt;Demo")-P26,"↑"))</f>
         <v>0</v>
       </c>
       <c r="R26" s="17"/>
@@ -3156,11 +3156,11 @@
         <v>0.472222222222222</v>
       </c>
       <c r="P27" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A27,cobranza!$D$3:$D$1000),0)</f>
+        <f aca="false">IF($A27="","",IF(COUNTIF($A$3:$A27,$A27)=1,SUMIF(cobranza!$B$3:$B$1000,$A27,cobranza!$D$3:$D$1000),"↑"))</f>
         <v>3600</v>
       </c>
       <c r="Q27" s="15" t="n">
-        <f aca="false">IFERROR(H27-P27,"")</f>
+        <f aca="false">IF($A27="","",IF(COUNTIF($A$3:$A27,$A27)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A27,$C$3:$C$1000,"&lt;&gt;Demo")-P27,"↑"))</f>
         <v>0</v>
       </c>
       <c r="R27" s="17"/>
@@ -3187,13 +3187,13 @@
         <f aca="false">IFERROR(N28/H28,"")</f>
         <v/>
       </c>
-      <c r="P28" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A28,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q28" s="15" t="n">
-        <f aca="false">IFERROR(H28-P28,"")</f>
-        <v>0</v>
+      <c r="P28" s="15" t="str">
+        <f aca="false">IF($A28="","",IF(COUNTIF($A$3:$A28,$A28)=1,SUMIF(cobranza!$B$3:$B$1000,$A28,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q28" s="15" t="str">
+        <f aca="false">IF($A28="","",IF(COUNTIF($A$3:$A28,$A28)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A28,$C$3:$C$1000,"&lt;&gt;Demo")-P28,"↑"))</f>
+        <v/>
       </c>
       <c r="R28" s="17"/>
     </row>
@@ -3219,13 +3219,13 @@
         <f aca="false">IFERROR(N29/H29,"")</f>
         <v/>
       </c>
-      <c r="P29" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A29,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q29" s="15" t="n">
-        <f aca="false">IFERROR(H29-P29,"")</f>
-        <v>0</v>
+      <c r="P29" s="15" t="str">
+        <f aca="false">IF($A29="","",IF(COUNTIF($A$3:$A29,$A29)=1,SUMIF(cobranza!$B$3:$B$1000,$A29,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q29" s="15" t="str">
+        <f aca="false">IF($A29="","",IF(COUNTIF($A$3:$A29,$A29)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A29,$C$3:$C$1000,"&lt;&gt;Demo")-P29,"↑"))</f>
+        <v/>
       </c>
       <c r="R29" s="17"/>
     </row>
@@ -3251,13 +3251,13 @@
         <f aca="false">IFERROR(N30/H30,"")</f>
         <v/>
       </c>
-      <c r="P30" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A30,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q30" s="15" t="n">
-        <f aca="false">IFERROR(H30-P30,"")</f>
-        <v>0</v>
+      <c r="P30" s="15" t="str">
+        <f aca="false">IF($A30="","",IF(COUNTIF($A$3:$A30,$A30)=1,SUMIF(cobranza!$B$3:$B$1000,$A30,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q30" s="15" t="str">
+        <f aca="false">IF($A30="","",IF(COUNTIF($A$3:$A30,$A30)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A30,$C$3:$C$1000,"&lt;&gt;Demo")-P30,"↑"))</f>
+        <v/>
       </c>
       <c r="R30" s="17"/>
     </row>
@@ -3283,13 +3283,13 @@
         <f aca="false">IFERROR(N31/H31,"")</f>
         <v/>
       </c>
-      <c r="P31" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A31,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q31" s="15" t="n">
-        <f aca="false">IFERROR(H31-P31,"")</f>
-        <v>0</v>
+      <c r="P31" s="15" t="str">
+        <f aca="false">IF($A31="","",IF(COUNTIF($A$3:$A31,$A31)=1,SUMIF(cobranza!$B$3:$B$1000,$A31,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q31" s="15" t="str">
+        <f aca="false">IF($A31="","",IF(COUNTIF($A$3:$A31,$A31)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A31,$C$3:$C$1000,"&lt;&gt;Demo")-P31,"↑"))</f>
+        <v/>
       </c>
       <c r="R31" s="17"/>
     </row>
@@ -3315,13 +3315,13 @@
         <f aca="false">IFERROR(N32/H32,"")</f>
         <v/>
       </c>
-      <c r="P32" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A32,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q32" s="15" t="n">
-        <f aca="false">IFERROR(H32-P32,"")</f>
-        <v>0</v>
+      <c r="P32" s="15" t="str">
+        <f aca="false">IF($A32="","",IF(COUNTIF($A$3:$A32,$A32)=1,SUMIF(cobranza!$B$3:$B$1000,$A32,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q32" s="15" t="str">
+        <f aca="false">IF($A32="","",IF(COUNTIF($A$3:$A32,$A32)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A32,$C$3:$C$1000,"&lt;&gt;Demo")-P32,"↑"))</f>
+        <v/>
       </c>
       <c r="R32" s="17"/>
     </row>
@@ -3347,13 +3347,13 @@
         <f aca="false">IFERROR(N33/H33,"")</f>
         <v/>
       </c>
-      <c r="P33" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A33,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q33" s="15" t="n">
-        <f aca="false">IFERROR(H33-P33,"")</f>
-        <v>0</v>
+      <c r="P33" s="15" t="str">
+        <f aca="false">IF($A33="","",IF(COUNTIF($A$3:$A33,$A33)=1,SUMIF(cobranza!$B$3:$B$1000,$A33,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q33" s="15" t="str">
+        <f aca="false">IF($A33="","",IF(COUNTIF($A$3:$A33,$A33)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A33,$C$3:$C$1000,"&lt;&gt;Demo")-P33,"↑"))</f>
+        <v/>
       </c>
       <c r="R33" s="17"/>
     </row>
@@ -3379,13 +3379,13 @@
         <f aca="false">IFERROR(N34/H34,"")</f>
         <v/>
       </c>
-      <c r="P34" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A34,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q34" s="15" t="n">
-        <f aca="false">IFERROR(H34-P34,"")</f>
-        <v>0</v>
+      <c r="P34" s="15" t="str">
+        <f aca="false">IF($A34="","",IF(COUNTIF($A$3:$A34,$A34)=1,SUMIF(cobranza!$B$3:$B$1000,$A34,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q34" s="15" t="str">
+        <f aca="false">IF($A34="","",IF(COUNTIF($A$3:$A34,$A34)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A34,$C$3:$C$1000,"&lt;&gt;Demo")-P34,"↑"))</f>
+        <v/>
       </c>
       <c r="R34" s="17"/>
     </row>
@@ -3411,13 +3411,13 @@
         <f aca="false">IFERROR(N35/H35,"")</f>
         <v/>
       </c>
-      <c r="P35" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A35,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q35" s="15" t="n">
-        <f aca="false">IFERROR(H35-P35,"")</f>
-        <v>0</v>
+      <c r="P35" s="15" t="str">
+        <f aca="false">IF($A35="","",IF(COUNTIF($A$3:$A35,$A35)=1,SUMIF(cobranza!$B$3:$B$1000,$A35,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q35" s="15" t="str">
+        <f aca="false">IF($A35="","",IF(COUNTIF($A$3:$A35,$A35)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A35,$C$3:$C$1000,"&lt;&gt;Demo")-P35,"↑"))</f>
+        <v/>
       </c>
       <c r="R35" s="17"/>
     </row>
@@ -3443,13 +3443,13 @@
         <f aca="false">IFERROR(N36/H36,"")</f>
         <v/>
       </c>
-      <c r="P36" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A36,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q36" s="15" t="n">
-        <f aca="false">IFERROR(H36-P36,"")</f>
-        <v>0</v>
+      <c r="P36" s="15" t="str">
+        <f aca="false">IF($A36="","",IF(COUNTIF($A$3:$A36,$A36)=1,SUMIF(cobranza!$B$3:$B$1000,$A36,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q36" s="15" t="str">
+        <f aca="false">IF($A36="","",IF(COUNTIF($A$3:$A36,$A36)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A36,$C$3:$C$1000,"&lt;&gt;Demo")-P36,"↑"))</f>
+        <v/>
       </c>
       <c r="R36" s="17"/>
     </row>
@@ -3475,13 +3475,13 @@
         <f aca="false">IFERROR(N37/H37,"")</f>
         <v/>
       </c>
-      <c r="P37" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A37,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q37" s="15" t="n">
-        <f aca="false">IFERROR(H37-P37,"")</f>
-        <v>0</v>
+      <c r="P37" s="15" t="str">
+        <f aca="false">IF($A37="","",IF(COUNTIF($A$3:$A37,$A37)=1,SUMIF(cobranza!$B$3:$B$1000,$A37,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q37" s="15" t="str">
+        <f aca="false">IF($A37="","",IF(COUNTIF($A$3:$A37,$A37)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A37,$C$3:$C$1000,"&lt;&gt;Demo")-P37,"↑"))</f>
+        <v/>
       </c>
       <c r="R37" s="17"/>
     </row>
@@ -3507,13 +3507,13 @@
         <f aca="false">IFERROR(N38/H38,"")</f>
         <v/>
       </c>
-      <c r="P38" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A38,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q38" s="15" t="n">
-        <f aca="false">IFERROR(H38-P38,"")</f>
-        <v>0</v>
+      <c r="P38" s="15" t="str">
+        <f aca="false">IF($A38="","",IF(COUNTIF($A$3:$A38,$A38)=1,SUMIF(cobranza!$B$3:$B$1000,$A38,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q38" s="15" t="str">
+        <f aca="false">IF($A38="","",IF(COUNTIF($A$3:$A38,$A38)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A38,$C$3:$C$1000,"&lt;&gt;Demo")-P38,"↑"))</f>
+        <v/>
       </c>
       <c r="R38" s="17"/>
     </row>
@@ -3539,13 +3539,13 @@
         <f aca="false">IFERROR(N39/H39,"")</f>
         <v/>
       </c>
-      <c r="P39" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A39,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q39" s="15" t="n">
-        <f aca="false">IFERROR(H39-P39,"")</f>
-        <v>0</v>
+      <c r="P39" s="15" t="str">
+        <f aca="false">IF($A39="","",IF(COUNTIF($A$3:$A39,$A39)=1,SUMIF(cobranza!$B$3:$B$1000,$A39,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q39" s="15" t="str">
+        <f aca="false">IF($A39="","",IF(COUNTIF($A$3:$A39,$A39)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A39,$C$3:$C$1000,"&lt;&gt;Demo")-P39,"↑"))</f>
+        <v/>
       </c>
       <c r="R39" s="17"/>
     </row>
@@ -3571,13 +3571,13 @@
         <f aca="false">IFERROR(N40/H40,"")</f>
         <v/>
       </c>
-      <c r="P40" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A40,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q40" s="15" t="n">
-        <f aca="false">IFERROR(H40-P40,"")</f>
-        <v>0</v>
+      <c r="P40" s="15" t="str">
+        <f aca="false">IF($A40="","",IF(COUNTIF($A$3:$A40,$A40)=1,SUMIF(cobranza!$B$3:$B$1000,$A40,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q40" s="15" t="str">
+        <f aca="false">IF($A40="","",IF(COUNTIF($A$3:$A40,$A40)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A40,$C$3:$C$1000,"&lt;&gt;Demo")-P40,"↑"))</f>
+        <v/>
       </c>
       <c r="R40" s="17"/>
     </row>
@@ -3603,13 +3603,13 @@
         <f aca="false">IFERROR(N41/H41,"")</f>
         <v/>
       </c>
-      <c r="P41" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A41,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q41" s="15" t="n">
-        <f aca="false">IFERROR(H41-P41,"")</f>
-        <v>0</v>
+      <c r="P41" s="15" t="str">
+        <f aca="false">IF($A41="","",IF(COUNTIF($A$3:$A41,$A41)=1,SUMIF(cobranza!$B$3:$B$1000,$A41,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q41" s="15" t="str">
+        <f aca="false">IF($A41="","",IF(COUNTIF($A$3:$A41,$A41)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A41,$C$3:$C$1000,"&lt;&gt;Demo")-P41,"↑"))</f>
+        <v/>
       </c>
       <c r="R41" s="17"/>
     </row>
@@ -3635,13 +3635,13 @@
         <f aca="false">IFERROR(N42/H42,"")</f>
         <v/>
       </c>
-      <c r="P42" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A42,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q42" s="15" t="n">
-        <f aca="false">IFERROR(H42-P42,"")</f>
-        <v>0</v>
+      <c r="P42" s="15" t="str">
+        <f aca="false">IF($A42="","",IF(COUNTIF($A$3:$A42,$A42)=1,SUMIF(cobranza!$B$3:$B$1000,$A42,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q42" s="15" t="str">
+        <f aca="false">IF($A42="","",IF(COUNTIF($A$3:$A42,$A42)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A42,$C$3:$C$1000,"&lt;&gt;Demo")-P42,"↑"))</f>
+        <v/>
       </c>
       <c r="R42" s="17"/>
     </row>
@@ -3667,13 +3667,13 @@
         <f aca="false">IFERROR(N43/H43,"")</f>
         <v/>
       </c>
-      <c r="P43" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A43,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q43" s="15" t="n">
-        <f aca="false">IFERROR(H43-P43,"")</f>
-        <v>0</v>
+      <c r="P43" s="15" t="str">
+        <f aca="false">IF($A43="","",IF(COUNTIF($A$3:$A43,$A43)=1,SUMIF(cobranza!$B$3:$B$1000,$A43,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q43" s="15" t="str">
+        <f aca="false">IF($A43="","",IF(COUNTIF($A$3:$A43,$A43)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A43,$C$3:$C$1000,"&lt;&gt;Demo")-P43,"↑"))</f>
+        <v/>
       </c>
       <c r="R43" s="17"/>
     </row>
@@ -3699,13 +3699,13 @@
         <f aca="false">IFERROR(N44/H44,"")</f>
         <v/>
       </c>
-      <c r="P44" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A44,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q44" s="15" t="n">
-        <f aca="false">IFERROR(H44-P44,"")</f>
-        <v>0</v>
+      <c r="P44" s="15" t="str">
+        <f aca="false">IF($A44="","",IF(COUNTIF($A$3:$A44,$A44)=1,SUMIF(cobranza!$B$3:$B$1000,$A44,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q44" s="15" t="str">
+        <f aca="false">IF($A44="","",IF(COUNTIF($A$3:$A44,$A44)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A44,$C$3:$C$1000,"&lt;&gt;Demo")-P44,"↑"))</f>
+        <v/>
       </c>
       <c r="R44" s="17"/>
     </row>
@@ -3731,13 +3731,13 @@
         <f aca="false">IFERROR(N45/H45,"")</f>
         <v/>
       </c>
-      <c r="P45" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A45,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q45" s="15" t="n">
-        <f aca="false">IFERROR(H45-P45,"")</f>
-        <v>0</v>
+      <c r="P45" s="15" t="str">
+        <f aca="false">IF($A45="","",IF(COUNTIF($A$3:$A45,$A45)=1,SUMIF(cobranza!$B$3:$B$1000,$A45,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q45" s="15" t="str">
+        <f aca="false">IF($A45="","",IF(COUNTIF($A$3:$A45,$A45)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A45,$C$3:$C$1000,"&lt;&gt;Demo")-P45,"↑"))</f>
+        <v/>
       </c>
       <c r="R45" s="17"/>
     </row>
@@ -3763,13 +3763,13 @@
         <f aca="false">IFERROR(N46/H46,"")</f>
         <v/>
       </c>
-      <c r="P46" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A46,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q46" s="15" t="n">
-        <f aca="false">IFERROR(H46-P46,"")</f>
-        <v>0</v>
+      <c r="P46" s="15" t="str">
+        <f aca="false">IF($A46="","",IF(COUNTIF($A$3:$A46,$A46)=1,SUMIF(cobranza!$B$3:$B$1000,$A46,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q46" s="15" t="str">
+        <f aca="false">IF($A46="","",IF(COUNTIF($A$3:$A46,$A46)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A46,$C$3:$C$1000,"&lt;&gt;Demo")-P46,"↑"))</f>
+        <v/>
       </c>
       <c r="R46" s="17"/>
     </row>
@@ -3795,13 +3795,13 @@
         <f aca="false">IFERROR(N47/H47,"")</f>
         <v/>
       </c>
-      <c r="P47" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A47,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q47" s="15" t="n">
-        <f aca="false">IFERROR(H47-P47,"")</f>
-        <v>0</v>
+      <c r="P47" s="15" t="str">
+        <f aca="false">IF($A47="","",IF(COUNTIF($A$3:$A47,$A47)=1,SUMIF(cobranza!$B$3:$B$1000,$A47,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q47" s="15" t="str">
+        <f aca="false">IF($A47="","",IF(COUNTIF($A$3:$A47,$A47)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A47,$C$3:$C$1000,"&lt;&gt;Demo")-P47,"↑"))</f>
+        <v/>
       </c>
       <c r="R47" s="17"/>
     </row>
@@ -3827,13 +3827,13 @@
         <f aca="false">IFERROR(N48/H48,"")</f>
         <v/>
       </c>
-      <c r="P48" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A48,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q48" s="15" t="n">
-        <f aca="false">IFERROR(H48-P48,"")</f>
-        <v>0</v>
+      <c r="P48" s="15" t="str">
+        <f aca="false">IF($A48="","",IF(COUNTIF($A$3:$A48,$A48)=1,SUMIF(cobranza!$B$3:$B$1000,$A48,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q48" s="15" t="str">
+        <f aca="false">IF($A48="","",IF(COUNTIF($A$3:$A48,$A48)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A48,$C$3:$C$1000,"&lt;&gt;Demo")-P48,"↑"))</f>
+        <v/>
       </c>
       <c r="R48" s="17"/>
     </row>
@@ -3859,13 +3859,13 @@
         <f aca="false">IFERROR(N49/H49,"")</f>
         <v/>
       </c>
-      <c r="P49" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A49,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q49" s="15" t="n">
-        <f aca="false">IFERROR(H49-P49,"")</f>
-        <v>0</v>
+      <c r="P49" s="15" t="str">
+        <f aca="false">IF($A49="","",IF(COUNTIF($A$3:$A49,$A49)=1,SUMIF(cobranza!$B$3:$B$1000,$A49,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q49" s="15" t="str">
+        <f aca="false">IF($A49="","",IF(COUNTIF($A$3:$A49,$A49)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A49,$C$3:$C$1000,"&lt;&gt;Demo")-P49,"↑"))</f>
+        <v/>
       </c>
       <c r="R49" s="17"/>
     </row>
@@ -3891,13 +3891,13 @@
         <f aca="false">IFERROR(N50/H50,"")</f>
         <v/>
       </c>
-      <c r="P50" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A50,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q50" s="15" t="n">
-        <f aca="false">IFERROR(H50-P50,"")</f>
-        <v>0</v>
+      <c r="P50" s="15" t="str">
+        <f aca="false">IF($A50="","",IF(COUNTIF($A$3:$A50,$A50)=1,SUMIF(cobranza!$B$3:$B$1000,$A50,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q50" s="15" t="str">
+        <f aca="false">IF($A50="","",IF(COUNTIF($A$3:$A50,$A50)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A50,$C$3:$C$1000,"&lt;&gt;Demo")-P50,"↑"))</f>
+        <v/>
       </c>
       <c r="R50" s="17"/>
     </row>
@@ -3923,13 +3923,13 @@
         <f aca="false">IFERROR(N51/H51,"")</f>
         <v/>
       </c>
-      <c r="P51" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A51,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q51" s="15" t="n">
-        <f aca="false">IFERROR(H51-P51,"")</f>
-        <v>0</v>
+      <c r="P51" s="15" t="str">
+        <f aca="false">IF($A51="","",IF(COUNTIF($A$3:$A51,$A51)=1,SUMIF(cobranza!$B$3:$B$1000,$A51,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q51" s="15" t="str">
+        <f aca="false">IF($A51="","",IF(COUNTIF($A$3:$A51,$A51)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A51,$C$3:$C$1000,"&lt;&gt;Demo")-P51,"↑"))</f>
+        <v/>
       </c>
       <c r="R51" s="17"/>
     </row>
@@ -3955,13 +3955,13 @@
         <f aca="false">IFERROR(N52/H52,"")</f>
         <v/>
       </c>
-      <c r="P52" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A52,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q52" s="15" t="n">
-        <f aca="false">IFERROR(H52-P52,"")</f>
-        <v>0</v>
+      <c r="P52" s="15" t="str">
+        <f aca="false">IF($A52="","",IF(COUNTIF($A$3:$A52,$A52)=1,SUMIF(cobranza!$B$3:$B$1000,$A52,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q52" s="15" t="str">
+        <f aca="false">IF($A52="","",IF(COUNTIF($A$3:$A52,$A52)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A52,$C$3:$C$1000,"&lt;&gt;Demo")-P52,"↑"))</f>
+        <v/>
       </c>
       <c r="R52" s="17"/>
     </row>
@@ -3987,13 +3987,13 @@
         <f aca="false">IFERROR(N53/H53,"")</f>
         <v/>
       </c>
-      <c r="P53" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A53,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q53" s="15" t="n">
-        <f aca="false">IFERROR(H53-P53,"")</f>
-        <v>0</v>
+      <c r="P53" s="15" t="str">
+        <f aca="false">IF($A53="","",IF(COUNTIF($A$3:$A53,$A53)=1,SUMIF(cobranza!$B$3:$B$1000,$A53,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q53" s="15" t="str">
+        <f aca="false">IF($A53="","",IF(COUNTIF($A$3:$A53,$A53)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A53,$C$3:$C$1000,"&lt;&gt;Demo")-P53,"↑"))</f>
+        <v/>
       </c>
       <c r="R53" s="17"/>
     </row>
@@ -4019,13 +4019,13 @@
         <f aca="false">IFERROR(N54/H54,"")</f>
         <v/>
       </c>
-      <c r="P54" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A54,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q54" s="15" t="n">
-        <f aca="false">IFERROR(H54-P54,"")</f>
-        <v>0</v>
+      <c r="P54" s="15" t="str">
+        <f aca="false">IF($A54="","",IF(COUNTIF($A$3:$A54,$A54)=1,SUMIF(cobranza!$B$3:$B$1000,$A54,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q54" s="15" t="str">
+        <f aca="false">IF($A54="","",IF(COUNTIF($A$3:$A54,$A54)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A54,$C$3:$C$1000,"&lt;&gt;Demo")-P54,"↑"))</f>
+        <v/>
       </c>
       <c r="R54" s="17"/>
     </row>
@@ -4051,13 +4051,13 @@
         <f aca="false">IFERROR(N55/H55,"")</f>
         <v/>
       </c>
-      <c r="P55" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A55,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q55" s="15" t="n">
-        <f aca="false">IFERROR(H55-P55,"")</f>
-        <v>0</v>
+      <c r="P55" s="15" t="str">
+        <f aca="false">IF($A55="","",IF(COUNTIF($A$3:$A55,$A55)=1,SUMIF(cobranza!$B$3:$B$1000,$A55,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q55" s="15" t="str">
+        <f aca="false">IF($A55="","",IF(COUNTIF($A$3:$A55,$A55)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A55,$C$3:$C$1000,"&lt;&gt;Demo")-P55,"↑"))</f>
+        <v/>
       </c>
       <c r="R55" s="17"/>
     </row>
@@ -4083,13 +4083,13 @@
         <f aca="false">IFERROR(N56/H56,"")</f>
         <v/>
       </c>
-      <c r="P56" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A56,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q56" s="15" t="n">
-        <f aca="false">IFERROR(H56-P56,"")</f>
-        <v>0</v>
+      <c r="P56" s="15" t="str">
+        <f aca="false">IF($A56="","",IF(COUNTIF($A$3:$A56,$A56)=1,SUMIF(cobranza!$B$3:$B$1000,$A56,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q56" s="15" t="str">
+        <f aca="false">IF($A56="","",IF(COUNTIF($A$3:$A56,$A56)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A56,$C$3:$C$1000,"&lt;&gt;Demo")-P56,"↑"))</f>
+        <v/>
       </c>
       <c r="R56" s="17"/>
     </row>
@@ -4115,13 +4115,13 @@
         <f aca="false">IFERROR(N57/H57,"")</f>
         <v/>
       </c>
-      <c r="P57" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A57,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q57" s="15" t="n">
-        <f aca="false">IFERROR(H57-P57,"")</f>
-        <v>0</v>
+      <c r="P57" s="15" t="str">
+        <f aca="false">IF($A57="","",IF(COUNTIF($A$3:$A57,$A57)=1,SUMIF(cobranza!$B$3:$B$1000,$A57,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q57" s="15" t="str">
+        <f aca="false">IF($A57="","",IF(COUNTIF($A$3:$A57,$A57)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A57,$C$3:$C$1000,"&lt;&gt;Demo")-P57,"↑"))</f>
+        <v/>
       </c>
       <c r="R57" s="17"/>
     </row>
@@ -4147,13 +4147,13 @@
         <f aca="false">IFERROR(N58/H58,"")</f>
         <v/>
       </c>
-      <c r="P58" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A58,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q58" s="15" t="n">
-        <f aca="false">IFERROR(H58-P58,"")</f>
-        <v>0</v>
+      <c r="P58" s="15" t="str">
+        <f aca="false">IF($A58="","",IF(COUNTIF($A$3:$A58,$A58)=1,SUMIF(cobranza!$B$3:$B$1000,$A58,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q58" s="15" t="str">
+        <f aca="false">IF($A58="","",IF(COUNTIF($A$3:$A58,$A58)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A58,$C$3:$C$1000,"&lt;&gt;Demo")-P58,"↑"))</f>
+        <v/>
       </c>
       <c r="R58" s="17"/>
     </row>
@@ -4179,13 +4179,13 @@
         <f aca="false">IFERROR(N59/H59,"")</f>
         <v/>
       </c>
-      <c r="P59" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A59,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q59" s="15" t="n">
-        <f aca="false">IFERROR(H59-P59,"")</f>
-        <v>0</v>
+      <c r="P59" s="15" t="str">
+        <f aca="false">IF($A59="","",IF(COUNTIF($A$3:$A59,$A59)=1,SUMIF(cobranza!$B$3:$B$1000,$A59,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q59" s="15" t="str">
+        <f aca="false">IF($A59="","",IF(COUNTIF($A$3:$A59,$A59)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A59,$C$3:$C$1000,"&lt;&gt;Demo")-P59,"↑"))</f>
+        <v/>
       </c>
       <c r="R59" s="17"/>
     </row>
@@ -4211,13 +4211,13 @@
         <f aca="false">IFERROR(N60/H60,"")</f>
         <v/>
       </c>
-      <c r="P60" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A60,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q60" s="15" t="n">
-        <f aca="false">IFERROR(H60-P60,"")</f>
-        <v>0</v>
+      <c r="P60" s="15" t="str">
+        <f aca="false">IF($A60="","",IF(COUNTIF($A$3:$A60,$A60)=1,SUMIF(cobranza!$B$3:$B$1000,$A60,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q60" s="15" t="str">
+        <f aca="false">IF($A60="","",IF(COUNTIF($A$3:$A60,$A60)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A60,$C$3:$C$1000,"&lt;&gt;Demo")-P60,"↑"))</f>
+        <v/>
       </c>
       <c r="R60" s="17"/>
     </row>
@@ -4243,13 +4243,13 @@
         <f aca="false">IFERROR(N61/H61,"")</f>
         <v/>
       </c>
-      <c r="P61" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A61,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q61" s="15" t="n">
-        <f aca="false">IFERROR(H61-P61,"")</f>
-        <v>0</v>
+      <c r="P61" s="15" t="str">
+        <f aca="false">IF($A61="","",IF(COUNTIF($A$3:$A61,$A61)=1,SUMIF(cobranza!$B$3:$B$1000,$A61,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q61" s="15" t="str">
+        <f aca="false">IF($A61="","",IF(COUNTIF($A$3:$A61,$A61)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A61,$C$3:$C$1000,"&lt;&gt;Demo")-P61,"↑"))</f>
+        <v/>
       </c>
       <c r="R61" s="17"/>
     </row>
@@ -4275,13 +4275,13 @@
         <f aca="false">IFERROR(N62/H62,"")</f>
         <v/>
       </c>
-      <c r="P62" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A62,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q62" s="15" t="n">
-        <f aca="false">IFERROR(H62-P62,"")</f>
-        <v>0</v>
+      <c r="P62" s="15" t="str">
+        <f aca="false">IF($A62="","",IF(COUNTIF($A$3:$A62,$A62)=1,SUMIF(cobranza!$B$3:$B$1000,$A62,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q62" s="15" t="str">
+        <f aca="false">IF($A62="","",IF(COUNTIF($A$3:$A62,$A62)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A62,$C$3:$C$1000,"&lt;&gt;Demo")-P62,"↑"))</f>
+        <v/>
       </c>
       <c r="R62" s="17"/>
     </row>
@@ -4307,13 +4307,13 @@
         <f aca="false">IFERROR(N63/H63,"")</f>
         <v/>
       </c>
-      <c r="P63" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A63,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q63" s="15" t="n">
-        <f aca="false">IFERROR(H63-P63,"")</f>
-        <v>0</v>
+      <c r="P63" s="15" t="str">
+        <f aca="false">IF($A63="","",IF(COUNTIF($A$3:$A63,$A63)=1,SUMIF(cobranza!$B$3:$B$1000,$A63,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q63" s="15" t="str">
+        <f aca="false">IF($A63="","",IF(COUNTIF($A$3:$A63,$A63)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A63,$C$3:$C$1000,"&lt;&gt;Demo")-P63,"↑"))</f>
+        <v/>
       </c>
       <c r="R63" s="17"/>
     </row>
@@ -4339,13 +4339,13 @@
         <f aca="false">IFERROR(N64/H64,"")</f>
         <v/>
       </c>
-      <c r="P64" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A64,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q64" s="15" t="n">
-        <f aca="false">IFERROR(H64-P64,"")</f>
-        <v>0</v>
+      <c r="P64" s="15" t="str">
+        <f aca="false">IF($A64="","",IF(COUNTIF($A$3:$A64,$A64)=1,SUMIF(cobranza!$B$3:$B$1000,$A64,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q64" s="15" t="str">
+        <f aca="false">IF($A64="","",IF(COUNTIF($A$3:$A64,$A64)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A64,$C$3:$C$1000,"&lt;&gt;Demo")-P64,"↑"))</f>
+        <v/>
       </c>
       <c r="R64" s="17"/>
     </row>
@@ -4371,13 +4371,13 @@
         <f aca="false">IFERROR(N65/H65,"")</f>
         <v/>
       </c>
-      <c r="P65" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A65,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q65" s="15" t="n">
-        <f aca="false">IFERROR(H65-P65,"")</f>
-        <v>0</v>
+      <c r="P65" s="15" t="str">
+        <f aca="false">IF($A65="","",IF(COUNTIF($A$3:$A65,$A65)=1,SUMIF(cobranza!$B$3:$B$1000,$A65,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q65" s="15" t="str">
+        <f aca="false">IF($A65="","",IF(COUNTIF($A$3:$A65,$A65)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A65,$C$3:$C$1000,"&lt;&gt;Demo")-P65,"↑"))</f>
+        <v/>
       </c>
       <c r="R65" s="17"/>
     </row>
@@ -4403,13 +4403,13 @@
         <f aca="false">IFERROR(N66/H66,"")</f>
         <v/>
       </c>
-      <c r="P66" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A66,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q66" s="15" t="n">
-        <f aca="false">IFERROR(H66-P66,"")</f>
-        <v>0</v>
+      <c r="P66" s="15" t="str">
+        <f aca="false">IF($A66="","",IF(COUNTIF($A$3:$A66,$A66)=1,SUMIF(cobranza!$B$3:$B$1000,$A66,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q66" s="15" t="str">
+        <f aca="false">IF($A66="","",IF(COUNTIF($A$3:$A66,$A66)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A66,$C$3:$C$1000,"&lt;&gt;Demo")-P66,"↑"))</f>
+        <v/>
       </c>
       <c r="R66" s="17"/>
     </row>
@@ -4435,13 +4435,13 @@
         <f aca="false">IFERROR(N67/H67,"")</f>
         <v/>
       </c>
-      <c r="P67" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A67,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q67" s="15" t="n">
-        <f aca="false">IFERROR(H67-P67,"")</f>
-        <v>0</v>
+      <c r="P67" s="15" t="str">
+        <f aca="false">IF($A67="","",IF(COUNTIF($A$3:$A67,$A67)=1,SUMIF(cobranza!$B$3:$B$1000,$A67,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q67" s="15" t="str">
+        <f aca="false">IF($A67="","",IF(COUNTIF($A$3:$A67,$A67)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A67,$C$3:$C$1000,"&lt;&gt;Demo")-P67,"↑"))</f>
+        <v/>
       </c>
       <c r="R67" s="17"/>
     </row>
@@ -4467,13 +4467,13 @@
         <f aca="false">IFERROR(N68/H68,"")</f>
         <v/>
       </c>
-      <c r="P68" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A68,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q68" s="15" t="n">
-        <f aca="false">IFERROR(H68-P68,"")</f>
-        <v>0</v>
+      <c r="P68" s="15" t="str">
+        <f aca="false">IF($A68="","",IF(COUNTIF($A$3:$A68,$A68)=1,SUMIF(cobranza!$B$3:$B$1000,$A68,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q68" s="15" t="str">
+        <f aca="false">IF($A68="","",IF(COUNTIF($A$3:$A68,$A68)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A68,$C$3:$C$1000,"&lt;&gt;Demo")-P68,"↑"))</f>
+        <v/>
       </c>
       <c r="R68" s="17"/>
     </row>
@@ -4499,13 +4499,13 @@
         <f aca="false">IFERROR(N69/H69,"")</f>
         <v/>
       </c>
-      <c r="P69" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A69,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q69" s="15" t="n">
-        <f aca="false">IFERROR(H69-P69,"")</f>
-        <v>0</v>
+      <c r="P69" s="15" t="str">
+        <f aca="false">IF($A69="","",IF(COUNTIF($A$3:$A69,$A69)=1,SUMIF(cobranza!$B$3:$B$1000,$A69,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q69" s="15" t="str">
+        <f aca="false">IF($A69="","",IF(COUNTIF($A$3:$A69,$A69)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A69,$C$3:$C$1000,"&lt;&gt;Demo")-P69,"↑"))</f>
+        <v/>
       </c>
       <c r="R69" s="17"/>
     </row>
@@ -4531,13 +4531,13 @@
         <f aca="false">IFERROR(N70/H70,"")</f>
         <v/>
       </c>
-      <c r="P70" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A70,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q70" s="15" t="n">
-        <f aca="false">IFERROR(H70-P70,"")</f>
-        <v>0</v>
+      <c r="P70" s="15" t="str">
+        <f aca="false">IF($A70="","",IF(COUNTIF($A$3:$A70,$A70)=1,SUMIF(cobranza!$B$3:$B$1000,$A70,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q70" s="15" t="str">
+        <f aca="false">IF($A70="","",IF(COUNTIF($A$3:$A70,$A70)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A70,$C$3:$C$1000,"&lt;&gt;Demo")-P70,"↑"))</f>
+        <v/>
       </c>
       <c r="R70" s="17"/>
     </row>
@@ -4563,13 +4563,13 @@
         <f aca="false">IFERROR(N71/H71,"")</f>
         <v/>
       </c>
-      <c r="P71" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A71,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q71" s="15" t="n">
-        <f aca="false">IFERROR(H71-P71,"")</f>
-        <v>0</v>
+      <c r="P71" s="15" t="str">
+        <f aca="false">IF($A71="","",IF(COUNTIF($A$3:$A71,$A71)=1,SUMIF(cobranza!$B$3:$B$1000,$A71,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q71" s="15" t="str">
+        <f aca="false">IF($A71="","",IF(COUNTIF($A$3:$A71,$A71)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A71,$C$3:$C$1000,"&lt;&gt;Demo")-P71,"↑"))</f>
+        <v/>
       </c>
       <c r="R71" s="17"/>
     </row>
@@ -4595,13 +4595,13 @@
         <f aca="false">IFERROR(N72/H72,"")</f>
         <v/>
       </c>
-      <c r="P72" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A72,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q72" s="15" t="n">
-        <f aca="false">IFERROR(H72-P72,"")</f>
-        <v>0</v>
+      <c r="P72" s="15" t="str">
+        <f aca="false">IF($A72="","",IF(COUNTIF($A$3:$A72,$A72)=1,SUMIF(cobranza!$B$3:$B$1000,$A72,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q72" s="15" t="str">
+        <f aca="false">IF($A72="","",IF(COUNTIF($A$3:$A72,$A72)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A72,$C$3:$C$1000,"&lt;&gt;Demo")-P72,"↑"))</f>
+        <v/>
       </c>
       <c r="R72" s="17"/>
     </row>
@@ -4627,13 +4627,13 @@
         <f aca="false">IFERROR(N73/H73,"")</f>
         <v/>
       </c>
-      <c r="P73" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A73,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q73" s="15" t="n">
-        <f aca="false">IFERROR(H73-P73,"")</f>
-        <v>0</v>
+      <c r="P73" s="15" t="str">
+        <f aca="false">IF($A73="","",IF(COUNTIF($A$3:$A73,$A73)=1,SUMIF(cobranza!$B$3:$B$1000,$A73,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q73" s="15" t="str">
+        <f aca="false">IF($A73="","",IF(COUNTIF($A$3:$A73,$A73)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A73,$C$3:$C$1000,"&lt;&gt;Demo")-P73,"↑"))</f>
+        <v/>
       </c>
       <c r="R73" s="17"/>
     </row>
@@ -4659,13 +4659,13 @@
         <f aca="false">IFERROR(N74/H74,"")</f>
         <v/>
       </c>
-      <c r="P74" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A74,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q74" s="15" t="n">
-        <f aca="false">IFERROR(H74-P74,"")</f>
-        <v>0</v>
+      <c r="P74" s="15" t="str">
+        <f aca="false">IF($A74="","",IF(COUNTIF($A$3:$A74,$A74)=1,SUMIF(cobranza!$B$3:$B$1000,$A74,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q74" s="15" t="str">
+        <f aca="false">IF($A74="","",IF(COUNTIF($A$3:$A74,$A74)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A74,$C$3:$C$1000,"&lt;&gt;Demo")-P74,"↑"))</f>
+        <v/>
       </c>
       <c r="R74" s="17"/>
     </row>
@@ -4691,13 +4691,13 @@
         <f aca="false">IFERROR(N75/H75,"")</f>
         <v/>
       </c>
-      <c r="P75" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A75,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q75" s="15" t="n">
-        <f aca="false">IFERROR(H75-P75,"")</f>
-        <v>0</v>
+      <c r="P75" s="15" t="str">
+        <f aca="false">IF($A75="","",IF(COUNTIF($A$3:$A75,$A75)=1,SUMIF(cobranza!$B$3:$B$1000,$A75,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q75" s="15" t="str">
+        <f aca="false">IF($A75="","",IF(COUNTIF($A$3:$A75,$A75)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A75,$C$3:$C$1000,"&lt;&gt;Demo")-P75,"↑"))</f>
+        <v/>
       </c>
       <c r="R75" s="17"/>
     </row>
@@ -4723,13 +4723,13 @@
         <f aca="false">IFERROR(N76/H76,"")</f>
         <v/>
       </c>
-      <c r="P76" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A76,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q76" s="15" t="n">
-        <f aca="false">IFERROR(H76-P76,"")</f>
-        <v>0</v>
+      <c r="P76" s="15" t="str">
+        <f aca="false">IF($A76="","",IF(COUNTIF($A$3:$A76,$A76)=1,SUMIF(cobranza!$B$3:$B$1000,$A76,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q76" s="15" t="str">
+        <f aca="false">IF($A76="","",IF(COUNTIF($A$3:$A76,$A76)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A76,$C$3:$C$1000,"&lt;&gt;Demo")-P76,"↑"))</f>
+        <v/>
       </c>
       <c r="R76" s="17"/>
     </row>
@@ -4755,13 +4755,13 @@
         <f aca="false">IFERROR(N77/H77,"")</f>
         <v/>
       </c>
-      <c r="P77" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A77,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q77" s="15" t="n">
-        <f aca="false">IFERROR(H77-P77,"")</f>
-        <v>0</v>
+      <c r="P77" s="15" t="str">
+        <f aca="false">IF($A77="","",IF(COUNTIF($A$3:$A77,$A77)=1,SUMIF(cobranza!$B$3:$B$1000,$A77,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q77" s="15" t="str">
+        <f aca="false">IF($A77="","",IF(COUNTIF($A$3:$A77,$A77)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A77,$C$3:$C$1000,"&lt;&gt;Demo")-P77,"↑"))</f>
+        <v/>
       </c>
       <c r="R77" s="17"/>
     </row>
@@ -4787,13 +4787,13 @@
         <f aca="false">IFERROR(N78/H78,"")</f>
         <v/>
       </c>
-      <c r="P78" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A78,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q78" s="15" t="n">
-        <f aca="false">IFERROR(H78-P78,"")</f>
-        <v>0</v>
+      <c r="P78" s="15" t="str">
+        <f aca="false">IF($A78="","",IF(COUNTIF($A$3:$A78,$A78)=1,SUMIF(cobranza!$B$3:$B$1000,$A78,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q78" s="15" t="str">
+        <f aca="false">IF($A78="","",IF(COUNTIF($A$3:$A78,$A78)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A78,$C$3:$C$1000,"&lt;&gt;Demo")-P78,"↑"))</f>
+        <v/>
       </c>
       <c r="R78" s="17"/>
     </row>
@@ -4819,13 +4819,13 @@
         <f aca="false">IFERROR(N79/H79,"")</f>
         <v/>
       </c>
-      <c r="P79" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A79,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q79" s="15" t="n">
-        <f aca="false">IFERROR(H79-P79,"")</f>
-        <v>0</v>
+      <c r="P79" s="15" t="str">
+        <f aca="false">IF($A79="","",IF(COUNTIF($A$3:$A79,$A79)=1,SUMIF(cobranza!$B$3:$B$1000,$A79,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q79" s="15" t="str">
+        <f aca="false">IF($A79="","",IF(COUNTIF($A$3:$A79,$A79)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A79,$C$3:$C$1000,"&lt;&gt;Demo")-P79,"↑"))</f>
+        <v/>
       </c>
       <c r="R79" s="17"/>
     </row>
@@ -4851,13 +4851,13 @@
         <f aca="false">IFERROR(N80/H80,"")</f>
         <v/>
       </c>
-      <c r="P80" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A80,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q80" s="15" t="n">
-        <f aca="false">IFERROR(H80-P80,"")</f>
-        <v>0</v>
+      <c r="P80" s="15" t="str">
+        <f aca="false">IF($A80="","",IF(COUNTIF($A$3:$A80,$A80)=1,SUMIF(cobranza!$B$3:$B$1000,$A80,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q80" s="15" t="str">
+        <f aca="false">IF($A80="","",IF(COUNTIF($A$3:$A80,$A80)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A80,$C$3:$C$1000,"&lt;&gt;Demo")-P80,"↑"))</f>
+        <v/>
       </c>
       <c r="R80" s="17"/>
     </row>
@@ -4883,13 +4883,13 @@
         <f aca="false">IFERROR(N81/H81,"")</f>
         <v/>
       </c>
-      <c r="P81" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A81,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q81" s="15" t="n">
-        <f aca="false">IFERROR(H81-P81,"")</f>
-        <v>0</v>
+      <c r="P81" s="15" t="str">
+        <f aca="false">IF($A81="","",IF(COUNTIF($A$3:$A81,$A81)=1,SUMIF(cobranza!$B$3:$B$1000,$A81,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q81" s="15" t="str">
+        <f aca="false">IF($A81="","",IF(COUNTIF($A$3:$A81,$A81)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A81,$C$3:$C$1000,"&lt;&gt;Demo")-P81,"↑"))</f>
+        <v/>
       </c>
       <c r="R81" s="17"/>
     </row>
@@ -4915,13 +4915,13 @@
         <f aca="false">IFERROR(N82/H82,"")</f>
         <v/>
       </c>
-      <c r="P82" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A82,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q82" s="15" t="n">
-        <f aca="false">IFERROR(H82-P82,"")</f>
-        <v>0</v>
+      <c r="P82" s="15" t="str">
+        <f aca="false">IF($A82="","",IF(COUNTIF($A$3:$A82,$A82)=1,SUMIF(cobranza!$B$3:$B$1000,$A82,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q82" s="15" t="str">
+        <f aca="false">IF($A82="","",IF(COUNTIF($A$3:$A82,$A82)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A82,$C$3:$C$1000,"&lt;&gt;Demo")-P82,"↑"))</f>
+        <v/>
       </c>
       <c r="R82" s="17"/>
     </row>
@@ -4947,13 +4947,13 @@
         <f aca="false">IFERROR(N83/H83,"")</f>
         <v/>
       </c>
-      <c r="P83" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A83,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q83" s="15" t="n">
-        <f aca="false">IFERROR(H83-P83,"")</f>
-        <v>0</v>
+      <c r="P83" s="15" t="str">
+        <f aca="false">IF($A83="","",IF(COUNTIF($A$3:$A83,$A83)=1,SUMIF(cobranza!$B$3:$B$1000,$A83,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q83" s="15" t="str">
+        <f aca="false">IF($A83="","",IF(COUNTIF($A$3:$A83,$A83)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A83,$C$3:$C$1000,"&lt;&gt;Demo")-P83,"↑"))</f>
+        <v/>
       </c>
       <c r="R83" s="17"/>
     </row>
@@ -4979,13 +4979,13 @@
         <f aca="false">IFERROR(N84/H84,"")</f>
         <v/>
       </c>
-      <c r="P84" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A84,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q84" s="15" t="n">
-        <f aca="false">IFERROR(H84-P84,"")</f>
-        <v>0</v>
+      <c r="P84" s="15" t="str">
+        <f aca="false">IF($A84="","",IF(COUNTIF($A$3:$A84,$A84)=1,SUMIF(cobranza!$B$3:$B$1000,$A84,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q84" s="15" t="str">
+        <f aca="false">IF($A84="","",IF(COUNTIF($A$3:$A84,$A84)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A84,$C$3:$C$1000,"&lt;&gt;Demo")-P84,"↑"))</f>
+        <v/>
       </c>
       <c r="R84" s="17"/>
     </row>
@@ -5011,13 +5011,13 @@
         <f aca="false">IFERROR(N85/H85,"")</f>
         <v/>
       </c>
-      <c r="P85" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A85,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q85" s="15" t="n">
-        <f aca="false">IFERROR(H85-P85,"")</f>
-        <v>0</v>
+      <c r="P85" s="15" t="str">
+        <f aca="false">IF($A85="","",IF(COUNTIF($A$3:$A85,$A85)=1,SUMIF(cobranza!$B$3:$B$1000,$A85,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q85" s="15" t="str">
+        <f aca="false">IF($A85="","",IF(COUNTIF($A$3:$A85,$A85)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A85,$C$3:$C$1000,"&lt;&gt;Demo")-P85,"↑"))</f>
+        <v/>
       </c>
       <c r="R85" s="17"/>
     </row>
@@ -5043,13 +5043,13 @@
         <f aca="false">IFERROR(N86/H86,"")</f>
         <v/>
       </c>
-      <c r="P86" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A86,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q86" s="15" t="n">
-        <f aca="false">IFERROR(H86-P86,"")</f>
-        <v>0</v>
+      <c r="P86" s="15" t="str">
+        <f aca="false">IF($A86="","",IF(COUNTIF($A$3:$A86,$A86)=1,SUMIF(cobranza!$B$3:$B$1000,$A86,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q86" s="15" t="str">
+        <f aca="false">IF($A86="","",IF(COUNTIF($A$3:$A86,$A86)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A86,$C$3:$C$1000,"&lt;&gt;Demo")-P86,"↑"))</f>
+        <v/>
       </c>
       <c r="R86" s="17"/>
     </row>
@@ -5075,13 +5075,13 @@
         <f aca="false">IFERROR(N87/H87,"")</f>
         <v/>
       </c>
-      <c r="P87" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A87,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q87" s="15" t="n">
-        <f aca="false">IFERROR(H87-P87,"")</f>
-        <v>0</v>
+      <c r="P87" s="15" t="str">
+        <f aca="false">IF($A87="","",IF(COUNTIF($A$3:$A87,$A87)=1,SUMIF(cobranza!$B$3:$B$1000,$A87,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q87" s="15" t="str">
+        <f aca="false">IF($A87="","",IF(COUNTIF($A$3:$A87,$A87)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A87,$C$3:$C$1000,"&lt;&gt;Demo")-P87,"↑"))</f>
+        <v/>
       </c>
       <c r="R87" s="17"/>
     </row>
@@ -5107,13 +5107,13 @@
         <f aca="false">IFERROR(N88/H88,"")</f>
         <v/>
       </c>
-      <c r="P88" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A88,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q88" s="15" t="n">
-        <f aca="false">IFERROR(H88-P88,"")</f>
-        <v>0</v>
+      <c r="P88" s="15" t="str">
+        <f aca="false">IF($A88="","",IF(COUNTIF($A$3:$A88,$A88)=1,SUMIF(cobranza!$B$3:$B$1000,$A88,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q88" s="15" t="str">
+        <f aca="false">IF($A88="","",IF(COUNTIF($A$3:$A88,$A88)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A88,$C$3:$C$1000,"&lt;&gt;Demo")-P88,"↑"))</f>
+        <v/>
       </c>
       <c r="R88" s="17"/>
     </row>
@@ -5139,13 +5139,13 @@
         <f aca="false">IFERROR(N89/H89,"")</f>
         <v/>
       </c>
-      <c r="P89" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A89,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q89" s="15" t="n">
-        <f aca="false">IFERROR(H89-P89,"")</f>
-        <v>0</v>
+      <c r="P89" s="15" t="str">
+        <f aca="false">IF($A89="","",IF(COUNTIF($A$3:$A89,$A89)=1,SUMIF(cobranza!$B$3:$B$1000,$A89,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q89" s="15" t="str">
+        <f aca="false">IF($A89="","",IF(COUNTIF($A$3:$A89,$A89)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A89,$C$3:$C$1000,"&lt;&gt;Demo")-P89,"↑"))</f>
+        <v/>
       </c>
       <c r="R89" s="17"/>
     </row>
@@ -5171,13 +5171,13 @@
         <f aca="false">IFERROR(N90/H90,"")</f>
         <v/>
       </c>
-      <c r="P90" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A90,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q90" s="15" t="n">
-        <f aca="false">IFERROR(H90-P90,"")</f>
-        <v>0</v>
+      <c r="P90" s="15" t="str">
+        <f aca="false">IF($A90="","",IF(COUNTIF($A$3:$A90,$A90)=1,SUMIF(cobranza!$B$3:$B$1000,$A90,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q90" s="15" t="str">
+        <f aca="false">IF($A90="","",IF(COUNTIF($A$3:$A90,$A90)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A90,$C$3:$C$1000,"&lt;&gt;Demo")-P90,"↑"))</f>
+        <v/>
       </c>
       <c r="R90" s="17"/>
     </row>
@@ -5203,13 +5203,13 @@
         <f aca="false">IFERROR(N91/H91,"")</f>
         <v/>
       </c>
-      <c r="P91" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A91,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q91" s="15" t="n">
-        <f aca="false">IFERROR(H91-P91,"")</f>
-        <v>0</v>
+      <c r="P91" s="15" t="str">
+        <f aca="false">IF($A91="","",IF(COUNTIF($A$3:$A91,$A91)=1,SUMIF(cobranza!$B$3:$B$1000,$A91,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q91" s="15" t="str">
+        <f aca="false">IF($A91="","",IF(COUNTIF($A$3:$A91,$A91)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A91,$C$3:$C$1000,"&lt;&gt;Demo")-P91,"↑"))</f>
+        <v/>
       </c>
       <c r="R91" s="17"/>
     </row>
@@ -5235,13 +5235,13 @@
         <f aca="false">IFERROR(N92/H92,"")</f>
         <v/>
       </c>
-      <c r="P92" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A92,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q92" s="15" t="n">
-        <f aca="false">IFERROR(H92-P92,"")</f>
-        <v>0</v>
+      <c r="P92" s="15" t="str">
+        <f aca="false">IF($A92="","",IF(COUNTIF($A$3:$A92,$A92)=1,SUMIF(cobranza!$B$3:$B$1000,$A92,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q92" s="15" t="str">
+        <f aca="false">IF($A92="","",IF(COUNTIF($A$3:$A92,$A92)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A92,$C$3:$C$1000,"&lt;&gt;Demo")-P92,"↑"))</f>
+        <v/>
       </c>
       <c r="R92" s="17"/>
     </row>
@@ -5267,13 +5267,13 @@
         <f aca="false">IFERROR(N93/H93,"")</f>
         <v/>
       </c>
-      <c r="P93" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A93,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q93" s="15" t="n">
-        <f aca="false">IFERROR(H93-P93,"")</f>
-        <v>0</v>
+      <c r="P93" s="15" t="str">
+        <f aca="false">IF($A93="","",IF(COUNTIF($A$3:$A93,$A93)=1,SUMIF(cobranza!$B$3:$B$1000,$A93,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q93" s="15" t="str">
+        <f aca="false">IF($A93="","",IF(COUNTIF($A$3:$A93,$A93)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A93,$C$3:$C$1000,"&lt;&gt;Demo")-P93,"↑"))</f>
+        <v/>
       </c>
       <c r="R93" s="17"/>
     </row>
@@ -5299,13 +5299,13 @@
         <f aca="false">IFERROR(N94/H94,"")</f>
         <v/>
       </c>
-      <c r="P94" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A94,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q94" s="15" t="n">
-        <f aca="false">IFERROR(H94-P94,"")</f>
-        <v>0</v>
+      <c r="P94" s="15" t="str">
+        <f aca="false">IF($A94="","",IF(COUNTIF($A$3:$A94,$A94)=1,SUMIF(cobranza!$B$3:$B$1000,$A94,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q94" s="15" t="str">
+        <f aca="false">IF($A94="","",IF(COUNTIF($A$3:$A94,$A94)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A94,$C$3:$C$1000,"&lt;&gt;Demo")-P94,"↑"))</f>
+        <v/>
       </c>
       <c r="R94" s="17"/>
     </row>
@@ -5331,13 +5331,13 @@
         <f aca="false">IFERROR(N95/H95,"")</f>
         <v/>
       </c>
-      <c r="P95" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A95,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q95" s="15" t="n">
-        <f aca="false">IFERROR(H95-P95,"")</f>
-        <v>0</v>
+      <c r="P95" s="15" t="str">
+        <f aca="false">IF($A95="","",IF(COUNTIF($A$3:$A95,$A95)=1,SUMIF(cobranza!$B$3:$B$1000,$A95,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q95" s="15" t="str">
+        <f aca="false">IF($A95="","",IF(COUNTIF($A$3:$A95,$A95)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A95,$C$3:$C$1000,"&lt;&gt;Demo")-P95,"↑"))</f>
+        <v/>
       </c>
       <c r="R95" s="17"/>
     </row>
@@ -5363,13 +5363,13 @@
         <f aca="false">IFERROR(N96/H96,"")</f>
         <v/>
       </c>
-      <c r="P96" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A96,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q96" s="15" t="n">
-        <f aca="false">IFERROR(H96-P96,"")</f>
-        <v>0</v>
+      <c r="P96" s="15" t="str">
+        <f aca="false">IF($A96="","",IF(COUNTIF($A$3:$A96,$A96)=1,SUMIF(cobranza!$B$3:$B$1000,$A96,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q96" s="15" t="str">
+        <f aca="false">IF($A96="","",IF(COUNTIF($A$3:$A96,$A96)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A96,$C$3:$C$1000,"&lt;&gt;Demo")-P96,"↑"))</f>
+        <v/>
       </c>
       <c r="R96" s="17"/>
     </row>
@@ -5395,13 +5395,13 @@
         <f aca="false">IFERROR(N97/H97,"")</f>
         <v/>
       </c>
-      <c r="P97" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A97,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q97" s="15" t="n">
-        <f aca="false">IFERROR(H97-P97,"")</f>
-        <v>0</v>
+      <c r="P97" s="15" t="str">
+        <f aca="false">IF($A97="","",IF(COUNTIF($A$3:$A97,$A97)=1,SUMIF(cobranza!$B$3:$B$1000,$A97,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q97" s="15" t="str">
+        <f aca="false">IF($A97="","",IF(COUNTIF($A$3:$A97,$A97)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A97,$C$3:$C$1000,"&lt;&gt;Demo")-P97,"↑"))</f>
+        <v/>
       </c>
       <c r="R97" s="17"/>
     </row>
@@ -5427,13 +5427,13 @@
         <f aca="false">IFERROR(N98/H98,"")</f>
         <v/>
       </c>
-      <c r="P98" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A98,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q98" s="15" t="n">
-        <f aca="false">IFERROR(H98-P98,"")</f>
-        <v>0</v>
+      <c r="P98" s="15" t="str">
+        <f aca="false">IF($A98="","",IF(COUNTIF($A$3:$A98,$A98)=1,SUMIF(cobranza!$B$3:$B$1000,$A98,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q98" s="15" t="str">
+        <f aca="false">IF($A98="","",IF(COUNTIF($A$3:$A98,$A98)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A98,$C$3:$C$1000,"&lt;&gt;Demo")-P98,"↑"))</f>
+        <v/>
       </c>
       <c r="R98" s="17"/>
     </row>
@@ -5459,13 +5459,13 @@
         <f aca="false">IFERROR(N99/H99,"")</f>
         <v/>
       </c>
-      <c r="P99" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A99,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q99" s="15" t="n">
-        <f aca="false">IFERROR(H99-P99,"")</f>
-        <v>0</v>
+      <c r="P99" s="15" t="str">
+        <f aca="false">IF($A99="","",IF(COUNTIF($A$3:$A99,$A99)=1,SUMIF(cobranza!$B$3:$B$1000,$A99,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q99" s="15" t="str">
+        <f aca="false">IF($A99="","",IF(COUNTIF($A$3:$A99,$A99)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A99,$C$3:$C$1000,"&lt;&gt;Demo")-P99,"↑"))</f>
+        <v/>
       </c>
       <c r="R99" s="17"/>
     </row>
@@ -5491,13 +5491,13 @@
         <f aca="false">IFERROR(N100/H100,"")</f>
         <v/>
       </c>
-      <c r="P100" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A100,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q100" s="15" t="n">
-        <f aca="false">IFERROR(H100-P100,"")</f>
-        <v>0</v>
+      <c r="P100" s="15" t="str">
+        <f aca="false">IF($A100="","",IF(COUNTIF($A$3:$A100,$A100)=1,SUMIF(cobranza!$B$3:$B$1000,$A100,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q100" s="15" t="str">
+        <f aca="false">IF($A100="","",IF(COUNTIF($A$3:$A100,$A100)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A100,$C$3:$C$1000,"&lt;&gt;Demo")-P100,"↑"))</f>
+        <v/>
       </c>
       <c r="R100" s="17"/>
     </row>
@@ -5523,13 +5523,13 @@
         <f aca="false">IFERROR(N101/H101,"")</f>
         <v/>
       </c>
-      <c r="P101" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A101,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q101" s="15" t="n">
-        <f aca="false">IFERROR(H101-P101,"")</f>
-        <v>0</v>
+      <c r="P101" s="15" t="str">
+        <f aca="false">IF($A101="","",IF(COUNTIF($A$3:$A101,$A101)=1,SUMIF(cobranza!$B$3:$B$1000,$A101,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q101" s="15" t="str">
+        <f aca="false">IF($A101="","",IF(COUNTIF($A$3:$A101,$A101)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A101,$C$3:$C$1000,"&lt;&gt;Demo")-P101,"↑"))</f>
+        <v/>
       </c>
       <c r="R101" s="17"/>
     </row>
@@ -5555,13 +5555,13 @@
         <f aca="false">IFERROR(N102/H102,"")</f>
         <v/>
       </c>
-      <c r="P102" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A102,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q102" s="15" t="n">
-        <f aca="false">IFERROR(H102-P102,"")</f>
-        <v>0</v>
+      <c r="P102" s="15" t="str">
+        <f aca="false">IF($A102="","",IF(COUNTIF($A$3:$A102,$A102)=1,SUMIF(cobranza!$B$3:$B$1000,$A102,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q102" s="15" t="str">
+        <f aca="false">IF($A102="","",IF(COUNTIF($A$3:$A102,$A102)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A102,$C$3:$C$1000,"&lt;&gt;Demo")-P102,"↑"))</f>
+        <v/>
       </c>
       <c r="R102" s="17"/>
     </row>
@@ -5587,13 +5587,13 @@
         <f aca="false">IFERROR(N103/H103,"")</f>
         <v/>
       </c>
-      <c r="P103" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A103,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q103" s="15" t="n">
-        <f aca="false">IFERROR(H103-P103,"")</f>
-        <v>0</v>
+      <c r="P103" s="15" t="str">
+        <f aca="false">IF($A103="","",IF(COUNTIF($A$3:$A103,$A103)=1,SUMIF(cobranza!$B$3:$B$1000,$A103,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q103" s="15" t="str">
+        <f aca="false">IF($A103="","",IF(COUNTIF($A$3:$A103,$A103)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A103,$C$3:$C$1000,"&lt;&gt;Demo")-P103,"↑"))</f>
+        <v/>
       </c>
       <c r="R103" s="17"/>
     </row>
@@ -5619,13 +5619,13 @@
         <f aca="false">IFERROR(N104/H104,"")</f>
         <v/>
       </c>
-      <c r="P104" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A104,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q104" s="15" t="n">
-        <f aca="false">IFERROR(H104-P104,"")</f>
-        <v>0</v>
+      <c r="P104" s="15" t="str">
+        <f aca="false">IF($A104="","",IF(COUNTIF($A$3:$A104,$A104)=1,SUMIF(cobranza!$B$3:$B$1000,$A104,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q104" s="15" t="str">
+        <f aca="false">IF($A104="","",IF(COUNTIF($A$3:$A104,$A104)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A104,$C$3:$C$1000,"&lt;&gt;Demo")-P104,"↑"))</f>
+        <v/>
       </c>
       <c r="R104" s="17"/>
     </row>
@@ -5651,13 +5651,13 @@
         <f aca="false">IFERROR(N105/H105,"")</f>
         <v/>
       </c>
-      <c r="P105" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A105,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q105" s="15" t="n">
-        <f aca="false">IFERROR(H105-P105,"")</f>
-        <v>0</v>
+      <c r="P105" s="15" t="str">
+        <f aca="false">IF($A105="","",IF(COUNTIF($A$3:$A105,$A105)=1,SUMIF(cobranza!$B$3:$B$1000,$A105,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q105" s="15" t="str">
+        <f aca="false">IF($A105="","",IF(COUNTIF($A$3:$A105,$A105)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A105,$C$3:$C$1000,"&lt;&gt;Demo")-P105,"↑"))</f>
+        <v/>
       </c>
       <c r="R105" s="17"/>
     </row>
@@ -5683,13 +5683,13 @@
         <f aca="false">IFERROR(N106/H106,"")</f>
         <v/>
       </c>
-      <c r="P106" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A106,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q106" s="15" t="n">
-        <f aca="false">IFERROR(H106-P106,"")</f>
-        <v>0</v>
+      <c r="P106" s="15" t="str">
+        <f aca="false">IF($A106="","",IF(COUNTIF($A$3:$A106,$A106)=1,SUMIF(cobranza!$B$3:$B$1000,$A106,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q106" s="15" t="str">
+        <f aca="false">IF($A106="","",IF(COUNTIF($A$3:$A106,$A106)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A106,$C$3:$C$1000,"&lt;&gt;Demo")-P106,"↑"))</f>
+        <v/>
       </c>
       <c r="R106" s="17"/>
     </row>
@@ -5715,13 +5715,13 @@
         <f aca="false">IFERROR(N107/H107,"")</f>
         <v/>
       </c>
-      <c r="P107" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A107,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q107" s="15" t="n">
-        <f aca="false">IFERROR(H107-P107,"")</f>
-        <v>0</v>
+      <c r="P107" s="15" t="str">
+        <f aca="false">IF($A107="","",IF(COUNTIF($A$3:$A107,$A107)=1,SUMIF(cobranza!$B$3:$B$1000,$A107,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q107" s="15" t="str">
+        <f aca="false">IF($A107="","",IF(COUNTIF($A$3:$A107,$A107)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A107,$C$3:$C$1000,"&lt;&gt;Demo")-P107,"↑"))</f>
+        <v/>
       </c>
       <c r="R107" s="17"/>
     </row>
@@ -5747,13 +5747,13 @@
         <f aca="false">IFERROR(N108/H108,"")</f>
         <v/>
       </c>
-      <c r="P108" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A108,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q108" s="15" t="n">
-        <f aca="false">IFERROR(H108-P108,"")</f>
-        <v>0</v>
+      <c r="P108" s="15" t="str">
+        <f aca="false">IF($A108="","",IF(COUNTIF($A$3:$A108,$A108)=1,SUMIF(cobranza!$B$3:$B$1000,$A108,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q108" s="15" t="str">
+        <f aca="false">IF($A108="","",IF(COUNTIF($A$3:$A108,$A108)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A108,$C$3:$C$1000,"&lt;&gt;Demo")-P108,"↑"))</f>
+        <v/>
       </c>
       <c r="R108" s="17"/>
     </row>
@@ -5779,13 +5779,13 @@
         <f aca="false">IFERROR(N109/H109,"")</f>
         <v/>
       </c>
-      <c r="P109" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A109,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q109" s="15" t="n">
-        <f aca="false">IFERROR(H109-P109,"")</f>
-        <v>0</v>
+      <c r="P109" s="15" t="str">
+        <f aca="false">IF($A109="","",IF(COUNTIF($A$3:$A109,$A109)=1,SUMIF(cobranza!$B$3:$B$1000,$A109,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q109" s="15" t="str">
+        <f aca="false">IF($A109="","",IF(COUNTIF($A$3:$A109,$A109)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A109,$C$3:$C$1000,"&lt;&gt;Demo")-P109,"↑"))</f>
+        <v/>
       </c>
       <c r="R109" s="17"/>
     </row>
@@ -5811,13 +5811,13 @@
         <f aca="false">IFERROR(N110/H110,"")</f>
         <v/>
       </c>
-      <c r="P110" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A110,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q110" s="15" t="n">
-        <f aca="false">IFERROR(H110-P110,"")</f>
-        <v>0</v>
+      <c r="P110" s="15" t="str">
+        <f aca="false">IF($A110="","",IF(COUNTIF($A$3:$A110,$A110)=1,SUMIF(cobranza!$B$3:$B$1000,$A110,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q110" s="15" t="str">
+        <f aca="false">IF($A110="","",IF(COUNTIF($A$3:$A110,$A110)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A110,$C$3:$C$1000,"&lt;&gt;Demo")-P110,"↑"))</f>
+        <v/>
       </c>
       <c r="R110" s="17"/>
     </row>
@@ -5843,13 +5843,13 @@
         <f aca="false">IFERROR(N111/H111,"")</f>
         <v/>
       </c>
-      <c r="P111" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A111,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q111" s="15" t="n">
-        <f aca="false">IFERROR(H111-P111,"")</f>
-        <v>0</v>
+      <c r="P111" s="15" t="str">
+        <f aca="false">IF($A111="","",IF(COUNTIF($A$3:$A111,$A111)=1,SUMIF(cobranza!$B$3:$B$1000,$A111,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q111" s="15" t="str">
+        <f aca="false">IF($A111="","",IF(COUNTIF($A$3:$A111,$A111)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A111,$C$3:$C$1000,"&lt;&gt;Demo")-P111,"↑"))</f>
+        <v/>
       </c>
       <c r="R111" s="17"/>
     </row>
@@ -5875,13 +5875,13 @@
         <f aca="false">IFERROR(N112/H112,"")</f>
         <v/>
       </c>
-      <c r="P112" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A112,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q112" s="15" t="n">
-        <f aca="false">IFERROR(H112-P112,"")</f>
-        <v>0</v>
+      <c r="P112" s="15" t="str">
+        <f aca="false">IF($A112="","",IF(COUNTIF($A$3:$A112,$A112)=1,SUMIF(cobranza!$B$3:$B$1000,$A112,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q112" s="15" t="str">
+        <f aca="false">IF($A112="","",IF(COUNTIF($A$3:$A112,$A112)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A112,$C$3:$C$1000,"&lt;&gt;Demo")-P112,"↑"))</f>
+        <v/>
       </c>
       <c r="R112" s="17"/>
     </row>
@@ -5907,13 +5907,13 @@
         <f aca="false">IFERROR(N113/H113,"")</f>
         <v/>
       </c>
-      <c r="P113" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A113,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q113" s="15" t="n">
-        <f aca="false">IFERROR(H113-P113,"")</f>
-        <v>0</v>
+      <c r="P113" s="15" t="str">
+        <f aca="false">IF($A113="","",IF(COUNTIF($A$3:$A113,$A113)=1,SUMIF(cobranza!$B$3:$B$1000,$A113,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q113" s="15" t="str">
+        <f aca="false">IF($A113="","",IF(COUNTIF($A$3:$A113,$A113)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A113,$C$3:$C$1000,"&lt;&gt;Demo")-P113,"↑"))</f>
+        <v/>
       </c>
       <c r="R113" s="17"/>
     </row>
@@ -5939,13 +5939,13 @@
         <f aca="false">IFERROR(N114/H114,"")</f>
         <v/>
       </c>
-      <c r="P114" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A114,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q114" s="15" t="n">
-        <f aca="false">IFERROR(H114-P114,"")</f>
-        <v>0</v>
+      <c r="P114" s="15" t="str">
+        <f aca="false">IF($A114="","",IF(COUNTIF($A$3:$A114,$A114)=1,SUMIF(cobranza!$B$3:$B$1000,$A114,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q114" s="15" t="str">
+        <f aca="false">IF($A114="","",IF(COUNTIF($A$3:$A114,$A114)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A114,$C$3:$C$1000,"&lt;&gt;Demo")-P114,"↑"))</f>
+        <v/>
       </c>
       <c r="R114" s="17"/>
     </row>
@@ -5971,13 +5971,13 @@
         <f aca="false">IFERROR(N115/H115,"")</f>
         <v/>
       </c>
-      <c r="P115" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A115,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q115" s="15" t="n">
-        <f aca="false">IFERROR(H115-P115,"")</f>
-        <v>0</v>
+      <c r="P115" s="15" t="str">
+        <f aca="false">IF($A115="","",IF(COUNTIF($A$3:$A115,$A115)=1,SUMIF(cobranza!$B$3:$B$1000,$A115,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q115" s="15" t="str">
+        <f aca="false">IF($A115="","",IF(COUNTIF($A$3:$A115,$A115)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A115,$C$3:$C$1000,"&lt;&gt;Demo")-P115,"↑"))</f>
+        <v/>
       </c>
       <c r="R115" s="17"/>
     </row>
@@ -6003,13 +6003,13 @@
         <f aca="false">IFERROR(N116/H116,"")</f>
         <v/>
       </c>
-      <c r="P116" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A116,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q116" s="15" t="n">
-        <f aca="false">IFERROR(H116-P116,"")</f>
-        <v>0</v>
+      <c r="P116" s="15" t="str">
+        <f aca="false">IF($A116="","",IF(COUNTIF($A$3:$A116,$A116)=1,SUMIF(cobranza!$B$3:$B$1000,$A116,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q116" s="15" t="str">
+        <f aca="false">IF($A116="","",IF(COUNTIF($A$3:$A116,$A116)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A116,$C$3:$C$1000,"&lt;&gt;Demo")-P116,"↑"))</f>
+        <v/>
       </c>
       <c r="R116" s="17"/>
     </row>
@@ -6035,13 +6035,13 @@
         <f aca="false">IFERROR(N117/H117,"")</f>
         <v/>
       </c>
-      <c r="P117" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A117,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q117" s="15" t="n">
-        <f aca="false">IFERROR(H117-P117,"")</f>
-        <v>0</v>
+      <c r="P117" s="15" t="str">
+        <f aca="false">IF($A117="","",IF(COUNTIF($A$3:$A117,$A117)=1,SUMIF(cobranza!$B$3:$B$1000,$A117,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q117" s="15" t="str">
+        <f aca="false">IF($A117="","",IF(COUNTIF($A$3:$A117,$A117)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A117,$C$3:$C$1000,"&lt;&gt;Demo")-P117,"↑"))</f>
+        <v/>
       </c>
       <c r="R117" s="17"/>
     </row>
@@ -6067,13 +6067,13 @@
         <f aca="false">IFERROR(N118/H118,"")</f>
         <v/>
       </c>
-      <c r="P118" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A118,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q118" s="15" t="n">
-        <f aca="false">IFERROR(H118-P118,"")</f>
-        <v>0</v>
+      <c r="P118" s="15" t="str">
+        <f aca="false">IF($A118="","",IF(COUNTIF($A$3:$A118,$A118)=1,SUMIF(cobranza!$B$3:$B$1000,$A118,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q118" s="15" t="str">
+        <f aca="false">IF($A118="","",IF(COUNTIF($A$3:$A118,$A118)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A118,$C$3:$C$1000,"&lt;&gt;Demo")-P118,"↑"))</f>
+        <v/>
       </c>
       <c r="R118" s="17"/>
     </row>
@@ -6099,13 +6099,13 @@
         <f aca="false">IFERROR(N119/H119,"")</f>
         <v/>
       </c>
-      <c r="P119" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A119,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q119" s="15" t="n">
-        <f aca="false">IFERROR(H119-P119,"")</f>
-        <v>0</v>
+      <c r="P119" s="15" t="str">
+        <f aca="false">IF($A119="","",IF(COUNTIF($A$3:$A119,$A119)=1,SUMIF(cobranza!$B$3:$B$1000,$A119,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q119" s="15" t="str">
+        <f aca="false">IF($A119="","",IF(COUNTIF($A$3:$A119,$A119)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A119,$C$3:$C$1000,"&lt;&gt;Demo")-P119,"↑"))</f>
+        <v/>
       </c>
       <c r="R119" s="17"/>
     </row>
@@ -6131,13 +6131,13 @@
         <f aca="false">IFERROR(N120/H120,"")</f>
         <v/>
       </c>
-      <c r="P120" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A120,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q120" s="15" t="n">
-        <f aca="false">IFERROR(H120-P120,"")</f>
-        <v>0</v>
+      <c r="P120" s="15" t="str">
+        <f aca="false">IF($A120="","",IF(COUNTIF($A$3:$A120,$A120)=1,SUMIF(cobranza!$B$3:$B$1000,$A120,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q120" s="15" t="str">
+        <f aca="false">IF($A120="","",IF(COUNTIF($A$3:$A120,$A120)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A120,$C$3:$C$1000,"&lt;&gt;Demo")-P120,"↑"))</f>
+        <v/>
       </c>
       <c r="R120" s="17"/>
     </row>
@@ -6163,13 +6163,13 @@
         <f aca="false">IFERROR(N121/H121,"")</f>
         <v/>
       </c>
-      <c r="P121" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A121,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q121" s="15" t="n">
-        <f aca="false">IFERROR(H121-P121,"")</f>
-        <v>0</v>
+      <c r="P121" s="15" t="str">
+        <f aca="false">IF($A121="","",IF(COUNTIF($A$3:$A121,$A121)=1,SUMIF(cobranza!$B$3:$B$1000,$A121,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q121" s="15" t="str">
+        <f aca="false">IF($A121="","",IF(COUNTIF($A$3:$A121,$A121)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A121,$C$3:$C$1000,"&lt;&gt;Demo")-P121,"↑"))</f>
+        <v/>
       </c>
       <c r="R121" s="17"/>
     </row>
@@ -6195,13 +6195,13 @@
         <f aca="false">IFERROR(N122/H122,"")</f>
         <v/>
       </c>
-      <c r="P122" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A122,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q122" s="15" t="n">
-        <f aca="false">IFERROR(H122-P122,"")</f>
-        <v>0</v>
+      <c r="P122" s="15" t="str">
+        <f aca="false">IF($A122="","",IF(COUNTIF($A$3:$A122,$A122)=1,SUMIF(cobranza!$B$3:$B$1000,$A122,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q122" s="15" t="str">
+        <f aca="false">IF($A122="","",IF(COUNTIF($A$3:$A122,$A122)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A122,$C$3:$C$1000,"&lt;&gt;Demo")-P122,"↑"))</f>
+        <v/>
       </c>
       <c r="R122" s="17"/>
     </row>
@@ -6227,13 +6227,13 @@
         <f aca="false">IFERROR(N123/H123,"")</f>
         <v/>
       </c>
-      <c r="P123" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A123,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q123" s="15" t="n">
-        <f aca="false">IFERROR(H123-P123,"")</f>
-        <v>0</v>
+      <c r="P123" s="15" t="str">
+        <f aca="false">IF($A123="","",IF(COUNTIF($A$3:$A123,$A123)=1,SUMIF(cobranza!$B$3:$B$1000,$A123,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q123" s="15" t="str">
+        <f aca="false">IF($A123="","",IF(COUNTIF($A$3:$A123,$A123)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A123,$C$3:$C$1000,"&lt;&gt;Demo")-P123,"↑"))</f>
+        <v/>
       </c>
       <c r="R123" s="17"/>
     </row>
@@ -6259,13 +6259,13 @@
         <f aca="false">IFERROR(N124/H124,"")</f>
         <v/>
       </c>
-      <c r="P124" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A124,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q124" s="15" t="n">
-        <f aca="false">IFERROR(H124-P124,"")</f>
-        <v>0</v>
+      <c r="P124" s="15" t="str">
+        <f aca="false">IF($A124="","",IF(COUNTIF($A$3:$A124,$A124)=1,SUMIF(cobranza!$B$3:$B$1000,$A124,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q124" s="15" t="str">
+        <f aca="false">IF($A124="","",IF(COUNTIF($A$3:$A124,$A124)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A124,$C$3:$C$1000,"&lt;&gt;Demo")-P124,"↑"))</f>
+        <v/>
       </c>
       <c r="R124" s="17"/>
     </row>
@@ -6291,13 +6291,13 @@
         <f aca="false">IFERROR(N125/H125,"")</f>
         <v/>
       </c>
-      <c r="P125" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A125,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q125" s="15" t="n">
-        <f aca="false">IFERROR(H125-P125,"")</f>
-        <v>0</v>
+      <c r="P125" s="15" t="str">
+        <f aca="false">IF($A125="","",IF(COUNTIF($A$3:$A125,$A125)=1,SUMIF(cobranza!$B$3:$B$1000,$A125,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q125" s="15" t="str">
+        <f aca="false">IF($A125="","",IF(COUNTIF($A$3:$A125,$A125)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A125,$C$3:$C$1000,"&lt;&gt;Demo")-P125,"↑"))</f>
+        <v/>
       </c>
       <c r="R125" s="17"/>
     </row>
@@ -6323,13 +6323,13 @@
         <f aca="false">IFERROR(N126/H126,"")</f>
         <v/>
       </c>
-      <c r="P126" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A126,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q126" s="15" t="n">
-        <f aca="false">IFERROR(H126-P126,"")</f>
-        <v>0</v>
+      <c r="P126" s="15" t="str">
+        <f aca="false">IF($A126="","",IF(COUNTIF($A$3:$A126,$A126)=1,SUMIF(cobranza!$B$3:$B$1000,$A126,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q126" s="15" t="str">
+        <f aca="false">IF($A126="","",IF(COUNTIF($A$3:$A126,$A126)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A126,$C$3:$C$1000,"&lt;&gt;Demo")-P126,"↑"))</f>
+        <v/>
       </c>
       <c r="R126" s="17"/>
     </row>
@@ -6355,13 +6355,13 @@
         <f aca="false">IFERROR(N127/H127,"")</f>
         <v/>
       </c>
-      <c r="P127" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A127,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q127" s="15" t="n">
-        <f aca="false">IFERROR(H127-P127,"")</f>
-        <v>0</v>
+      <c r="P127" s="15" t="str">
+        <f aca="false">IF($A127="","",IF(COUNTIF($A$3:$A127,$A127)=1,SUMIF(cobranza!$B$3:$B$1000,$A127,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q127" s="15" t="str">
+        <f aca="false">IF($A127="","",IF(COUNTIF($A$3:$A127,$A127)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A127,$C$3:$C$1000,"&lt;&gt;Demo")-P127,"↑"))</f>
+        <v/>
       </c>
       <c r="R127" s="17"/>
     </row>
@@ -6387,13 +6387,13 @@
         <f aca="false">IFERROR(N128/H128,"")</f>
         <v/>
       </c>
-      <c r="P128" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A128,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q128" s="15" t="n">
-        <f aca="false">IFERROR(H128-P128,"")</f>
-        <v>0</v>
+      <c r="P128" s="15" t="str">
+        <f aca="false">IF($A128="","",IF(COUNTIF($A$3:$A128,$A128)=1,SUMIF(cobranza!$B$3:$B$1000,$A128,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q128" s="15" t="str">
+        <f aca="false">IF($A128="","",IF(COUNTIF($A$3:$A128,$A128)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A128,$C$3:$C$1000,"&lt;&gt;Demo")-P128,"↑"))</f>
+        <v/>
       </c>
       <c r="R128" s="17"/>
     </row>
@@ -6419,13 +6419,13 @@
         <f aca="false">IFERROR(N129/H129,"")</f>
         <v/>
       </c>
-      <c r="P129" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A129,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q129" s="15" t="n">
-        <f aca="false">IFERROR(H129-P129,"")</f>
-        <v>0</v>
+      <c r="P129" s="15" t="str">
+        <f aca="false">IF($A129="","",IF(COUNTIF($A$3:$A129,$A129)=1,SUMIF(cobranza!$B$3:$B$1000,$A129,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q129" s="15" t="str">
+        <f aca="false">IF($A129="","",IF(COUNTIF($A$3:$A129,$A129)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A129,$C$3:$C$1000,"&lt;&gt;Demo")-P129,"↑"))</f>
+        <v/>
       </c>
       <c r="R129" s="17"/>
     </row>
@@ -6451,13 +6451,13 @@
         <f aca="false">IFERROR(N130/H130,"")</f>
         <v/>
       </c>
-      <c r="P130" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A130,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q130" s="15" t="n">
-        <f aca="false">IFERROR(H130-P130,"")</f>
-        <v>0</v>
+      <c r="P130" s="15" t="str">
+        <f aca="false">IF($A130="","",IF(COUNTIF($A$3:$A130,$A130)=1,SUMIF(cobranza!$B$3:$B$1000,$A130,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q130" s="15" t="str">
+        <f aca="false">IF($A130="","",IF(COUNTIF($A$3:$A130,$A130)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A130,$C$3:$C$1000,"&lt;&gt;Demo")-P130,"↑"))</f>
+        <v/>
       </c>
       <c r="R130" s="17"/>
     </row>
@@ -6483,13 +6483,13 @@
         <f aca="false">IFERROR(N131/H131,"")</f>
         <v/>
       </c>
-      <c r="P131" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A131,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q131" s="15" t="n">
-        <f aca="false">IFERROR(H131-P131,"")</f>
-        <v>0</v>
+      <c r="P131" s="15" t="str">
+        <f aca="false">IF($A131="","",IF(COUNTIF($A$3:$A131,$A131)=1,SUMIF(cobranza!$B$3:$B$1000,$A131,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q131" s="15" t="str">
+        <f aca="false">IF($A131="","",IF(COUNTIF($A$3:$A131,$A131)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A131,$C$3:$C$1000,"&lt;&gt;Demo")-P131,"↑"))</f>
+        <v/>
       </c>
       <c r="R131" s="17"/>
     </row>
@@ -6515,13 +6515,13 @@
         <f aca="false">IFERROR(N132/H132,"")</f>
         <v/>
       </c>
-      <c r="P132" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A132,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q132" s="15" t="n">
-        <f aca="false">IFERROR(H132-P132,"")</f>
-        <v>0</v>
+      <c r="P132" s="15" t="str">
+        <f aca="false">IF($A132="","",IF(COUNTIF($A$3:$A132,$A132)=1,SUMIF(cobranza!$B$3:$B$1000,$A132,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q132" s="15" t="str">
+        <f aca="false">IF($A132="","",IF(COUNTIF($A$3:$A132,$A132)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A132,$C$3:$C$1000,"&lt;&gt;Demo")-P132,"↑"))</f>
+        <v/>
       </c>
       <c r="R132" s="17"/>
     </row>
@@ -6547,13 +6547,13 @@
         <f aca="false">IFERROR(N133/H133,"")</f>
         <v/>
       </c>
-      <c r="P133" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A133,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q133" s="15" t="n">
-        <f aca="false">IFERROR(H133-P133,"")</f>
-        <v>0</v>
+      <c r="P133" s="15" t="str">
+        <f aca="false">IF($A133="","",IF(COUNTIF($A$3:$A133,$A133)=1,SUMIF(cobranza!$B$3:$B$1000,$A133,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q133" s="15" t="str">
+        <f aca="false">IF($A133="","",IF(COUNTIF($A$3:$A133,$A133)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A133,$C$3:$C$1000,"&lt;&gt;Demo")-P133,"↑"))</f>
+        <v/>
       </c>
       <c r="R133" s="17"/>
     </row>
@@ -6579,13 +6579,13 @@
         <f aca="false">IFERROR(N134/H134,"")</f>
         <v/>
       </c>
-      <c r="P134" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A134,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q134" s="15" t="n">
-        <f aca="false">IFERROR(H134-P134,"")</f>
-        <v>0</v>
+      <c r="P134" s="15" t="str">
+        <f aca="false">IF($A134="","",IF(COUNTIF($A$3:$A134,$A134)=1,SUMIF(cobranza!$B$3:$B$1000,$A134,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q134" s="15" t="str">
+        <f aca="false">IF($A134="","",IF(COUNTIF($A$3:$A134,$A134)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A134,$C$3:$C$1000,"&lt;&gt;Demo")-P134,"↑"))</f>
+        <v/>
       </c>
       <c r="R134" s="17"/>
     </row>
@@ -6611,13 +6611,13 @@
         <f aca="false">IFERROR(N135/H135,"")</f>
         <v/>
       </c>
-      <c r="P135" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A135,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q135" s="15" t="n">
-        <f aca="false">IFERROR(H135-P135,"")</f>
-        <v>0</v>
+      <c r="P135" s="15" t="str">
+        <f aca="false">IF($A135="","",IF(COUNTIF($A$3:$A135,$A135)=1,SUMIF(cobranza!$B$3:$B$1000,$A135,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q135" s="15" t="str">
+        <f aca="false">IF($A135="","",IF(COUNTIF($A$3:$A135,$A135)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A135,$C$3:$C$1000,"&lt;&gt;Demo")-P135,"↑"))</f>
+        <v/>
       </c>
       <c r="R135" s="17"/>
     </row>
@@ -6643,13 +6643,13 @@
         <f aca="false">IFERROR(N136/H136,"")</f>
         <v/>
       </c>
-      <c r="P136" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A136,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q136" s="15" t="n">
-        <f aca="false">IFERROR(H136-P136,"")</f>
-        <v>0</v>
+      <c r="P136" s="15" t="str">
+        <f aca="false">IF($A136="","",IF(COUNTIF($A$3:$A136,$A136)=1,SUMIF(cobranza!$B$3:$B$1000,$A136,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q136" s="15" t="str">
+        <f aca="false">IF($A136="","",IF(COUNTIF($A$3:$A136,$A136)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A136,$C$3:$C$1000,"&lt;&gt;Demo")-P136,"↑"))</f>
+        <v/>
       </c>
       <c r="R136" s="17"/>
     </row>
@@ -6675,13 +6675,13 @@
         <f aca="false">IFERROR(N137/H137,"")</f>
         <v/>
       </c>
-      <c r="P137" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A137,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q137" s="15" t="n">
-        <f aca="false">IFERROR(H137-P137,"")</f>
-        <v>0</v>
+      <c r="P137" s="15" t="str">
+        <f aca="false">IF($A137="","",IF(COUNTIF($A$3:$A137,$A137)=1,SUMIF(cobranza!$B$3:$B$1000,$A137,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q137" s="15" t="str">
+        <f aca="false">IF($A137="","",IF(COUNTIF($A$3:$A137,$A137)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A137,$C$3:$C$1000,"&lt;&gt;Demo")-P137,"↑"))</f>
+        <v/>
       </c>
       <c r="R137" s="17"/>
     </row>
@@ -6707,13 +6707,13 @@
         <f aca="false">IFERROR(N138/H138,"")</f>
         <v/>
       </c>
-      <c r="P138" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A138,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q138" s="15" t="n">
-        <f aca="false">IFERROR(H138-P138,"")</f>
-        <v>0</v>
+      <c r="P138" s="15" t="str">
+        <f aca="false">IF($A138="","",IF(COUNTIF($A$3:$A138,$A138)=1,SUMIF(cobranza!$B$3:$B$1000,$A138,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q138" s="15" t="str">
+        <f aca="false">IF($A138="","",IF(COUNTIF($A$3:$A138,$A138)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A138,$C$3:$C$1000,"&lt;&gt;Demo")-P138,"↑"))</f>
+        <v/>
       </c>
       <c r="R138" s="17"/>
     </row>
@@ -6739,13 +6739,13 @@
         <f aca="false">IFERROR(N139/H139,"")</f>
         <v/>
       </c>
-      <c r="P139" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A139,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q139" s="15" t="n">
-        <f aca="false">IFERROR(H139-P139,"")</f>
-        <v>0</v>
+      <c r="P139" s="15" t="str">
+        <f aca="false">IF($A139="","",IF(COUNTIF($A$3:$A139,$A139)=1,SUMIF(cobranza!$B$3:$B$1000,$A139,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q139" s="15" t="str">
+        <f aca="false">IF($A139="","",IF(COUNTIF($A$3:$A139,$A139)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A139,$C$3:$C$1000,"&lt;&gt;Demo")-P139,"↑"))</f>
+        <v/>
       </c>
       <c r="R139" s="17"/>
     </row>
@@ -6771,13 +6771,13 @@
         <f aca="false">IFERROR(N140/H140,"")</f>
         <v/>
       </c>
-      <c r="P140" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A140,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q140" s="15" t="n">
-        <f aca="false">IFERROR(H140-P140,"")</f>
-        <v>0</v>
+      <c r="P140" s="15" t="str">
+        <f aca="false">IF($A140="","",IF(COUNTIF($A$3:$A140,$A140)=1,SUMIF(cobranza!$B$3:$B$1000,$A140,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q140" s="15" t="str">
+        <f aca="false">IF($A140="","",IF(COUNTIF($A$3:$A140,$A140)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A140,$C$3:$C$1000,"&lt;&gt;Demo")-P140,"↑"))</f>
+        <v/>
       </c>
       <c r="R140" s="17"/>
     </row>
@@ -6803,13 +6803,13 @@
         <f aca="false">IFERROR(N141/H141,"")</f>
         <v/>
       </c>
-      <c r="P141" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A141,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q141" s="15" t="n">
-        <f aca="false">IFERROR(H141-P141,"")</f>
-        <v>0</v>
+      <c r="P141" s="15" t="str">
+        <f aca="false">IF($A141="","",IF(COUNTIF($A$3:$A141,$A141)=1,SUMIF(cobranza!$B$3:$B$1000,$A141,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q141" s="15" t="str">
+        <f aca="false">IF($A141="","",IF(COUNTIF($A$3:$A141,$A141)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A141,$C$3:$C$1000,"&lt;&gt;Demo")-P141,"↑"))</f>
+        <v/>
       </c>
       <c r="R141" s="17"/>
     </row>
@@ -6835,13 +6835,13 @@
         <f aca="false">IFERROR(N142/H142,"")</f>
         <v/>
       </c>
-      <c r="P142" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A142,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q142" s="15" t="n">
-        <f aca="false">IFERROR(H142-P142,"")</f>
-        <v>0</v>
+      <c r="P142" s="15" t="str">
+        <f aca="false">IF($A142="","",IF(COUNTIF($A$3:$A142,$A142)=1,SUMIF(cobranza!$B$3:$B$1000,$A142,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q142" s="15" t="str">
+        <f aca="false">IF($A142="","",IF(COUNTIF($A$3:$A142,$A142)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A142,$C$3:$C$1000,"&lt;&gt;Demo")-P142,"↑"))</f>
+        <v/>
       </c>
       <c r="R142" s="17"/>
     </row>
@@ -6867,13 +6867,13 @@
         <f aca="false">IFERROR(N143/H143,"")</f>
         <v/>
       </c>
-      <c r="P143" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A143,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q143" s="15" t="n">
-        <f aca="false">IFERROR(H143-P143,"")</f>
-        <v>0</v>
+      <c r="P143" s="15" t="str">
+        <f aca="false">IF($A143="","",IF(COUNTIF($A$3:$A143,$A143)=1,SUMIF(cobranza!$B$3:$B$1000,$A143,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q143" s="15" t="str">
+        <f aca="false">IF($A143="","",IF(COUNTIF($A$3:$A143,$A143)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A143,$C$3:$C$1000,"&lt;&gt;Demo")-P143,"↑"))</f>
+        <v/>
       </c>
       <c r="R143" s="17"/>
     </row>
@@ -6899,13 +6899,13 @@
         <f aca="false">IFERROR(N144/H144,"")</f>
         <v/>
       </c>
-      <c r="P144" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A144,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q144" s="15" t="n">
-        <f aca="false">IFERROR(H144-P144,"")</f>
-        <v>0</v>
+      <c r="P144" s="15" t="str">
+        <f aca="false">IF($A144="","",IF(COUNTIF($A$3:$A144,$A144)=1,SUMIF(cobranza!$B$3:$B$1000,$A144,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q144" s="15" t="str">
+        <f aca="false">IF($A144="","",IF(COUNTIF($A$3:$A144,$A144)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A144,$C$3:$C$1000,"&lt;&gt;Demo")-P144,"↑"))</f>
+        <v/>
       </c>
       <c r="R144" s="17"/>
     </row>
@@ -6931,13 +6931,13 @@
         <f aca="false">IFERROR(N145/H145,"")</f>
         <v/>
       </c>
-      <c r="P145" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A145,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q145" s="15" t="n">
-        <f aca="false">IFERROR(H145-P145,"")</f>
-        <v>0</v>
+      <c r="P145" s="15" t="str">
+        <f aca="false">IF($A145="","",IF(COUNTIF($A$3:$A145,$A145)=1,SUMIF(cobranza!$B$3:$B$1000,$A145,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q145" s="15" t="str">
+        <f aca="false">IF($A145="","",IF(COUNTIF($A$3:$A145,$A145)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A145,$C$3:$C$1000,"&lt;&gt;Demo")-P145,"↑"))</f>
+        <v/>
       </c>
       <c r="R145" s="17"/>
     </row>
@@ -6963,13 +6963,13 @@
         <f aca="false">IFERROR(N146/H146,"")</f>
         <v/>
       </c>
-      <c r="P146" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A146,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q146" s="15" t="n">
-        <f aca="false">IFERROR(H146-P146,"")</f>
-        <v>0</v>
+      <c r="P146" s="15" t="str">
+        <f aca="false">IF($A146="","",IF(COUNTIF($A$3:$A146,$A146)=1,SUMIF(cobranza!$B$3:$B$1000,$A146,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q146" s="15" t="str">
+        <f aca="false">IF($A146="","",IF(COUNTIF($A$3:$A146,$A146)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A146,$C$3:$C$1000,"&lt;&gt;Demo")-P146,"↑"))</f>
+        <v/>
       </c>
       <c r="R146" s="17"/>
     </row>
@@ -6995,13 +6995,13 @@
         <f aca="false">IFERROR(N147/H147,"")</f>
         <v/>
       </c>
-      <c r="P147" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A147,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q147" s="15" t="n">
-        <f aca="false">IFERROR(H147-P147,"")</f>
-        <v>0</v>
+      <c r="P147" s="15" t="str">
+        <f aca="false">IF($A147="","",IF(COUNTIF($A$3:$A147,$A147)=1,SUMIF(cobranza!$B$3:$B$1000,$A147,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q147" s="15" t="str">
+        <f aca="false">IF($A147="","",IF(COUNTIF($A$3:$A147,$A147)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A147,$C$3:$C$1000,"&lt;&gt;Demo")-P147,"↑"))</f>
+        <v/>
       </c>
       <c r="R147" s="17"/>
     </row>
@@ -7027,13 +7027,13 @@
         <f aca="false">IFERROR(N148/H148,"")</f>
         <v/>
       </c>
-      <c r="P148" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A148,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q148" s="15" t="n">
-        <f aca="false">IFERROR(H148-P148,"")</f>
-        <v>0</v>
+      <c r="P148" s="15" t="str">
+        <f aca="false">IF($A148="","",IF(COUNTIF($A$3:$A148,$A148)=1,SUMIF(cobranza!$B$3:$B$1000,$A148,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q148" s="15" t="str">
+        <f aca="false">IF($A148="","",IF(COUNTIF($A$3:$A148,$A148)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A148,$C$3:$C$1000,"&lt;&gt;Demo")-P148,"↑"))</f>
+        <v/>
       </c>
       <c r="R148" s="17"/>
     </row>
@@ -7059,13 +7059,13 @@
         <f aca="false">IFERROR(N149/H149,"")</f>
         <v/>
       </c>
-      <c r="P149" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A149,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q149" s="15" t="n">
-        <f aca="false">IFERROR(H149-P149,"")</f>
-        <v>0</v>
+      <c r="P149" s="15" t="str">
+        <f aca="false">IF($A149="","",IF(COUNTIF($A$3:$A149,$A149)=1,SUMIF(cobranza!$B$3:$B$1000,$A149,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q149" s="15" t="str">
+        <f aca="false">IF($A149="","",IF(COUNTIF($A$3:$A149,$A149)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A149,$C$3:$C$1000,"&lt;&gt;Demo")-P149,"↑"))</f>
+        <v/>
       </c>
       <c r="R149" s="17"/>
     </row>
@@ -7091,13 +7091,13 @@
         <f aca="false">IFERROR(N150/H150,"")</f>
         <v/>
       </c>
-      <c r="P150" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A150,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q150" s="15" t="n">
-        <f aca="false">IFERROR(H150-P150,"")</f>
-        <v>0</v>
+      <c r="P150" s="15" t="str">
+        <f aca="false">IF($A150="","",IF(COUNTIF($A$3:$A150,$A150)=1,SUMIF(cobranza!$B$3:$B$1000,$A150,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q150" s="15" t="str">
+        <f aca="false">IF($A150="","",IF(COUNTIF($A$3:$A150,$A150)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A150,$C$3:$C$1000,"&lt;&gt;Demo")-P150,"↑"))</f>
+        <v/>
       </c>
       <c r="R150" s="17"/>
     </row>
@@ -7123,13 +7123,13 @@
         <f aca="false">IFERROR(N151/H151,"")</f>
         <v/>
       </c>
-      <c r="P151" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A151,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q151" s="15" t="n">
-        <f aca="false">IFERROR(H151-P151,"")</f>
-        <v>0</v>
+      <c r="P151" s="15" t="str">
+        <f aca="false">IF($A151="","",IF(COUNTIF($A$3:$A151,$A151)=1,SUMIF(cobranza!$B$3:$B$1000,$A151,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q151" s="15" t="str">
+        <f aca="false">IF($A151="","",IF(COUNTIF($A$3:$A151,$A151)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A151,$C$3:$C$1000,"&lt;&gt;Demo")-P151,"↑"))</f>
+        <v/>
       </c>
       <c r="R151" s="17"/>
     </row>
@@ -7155,13 +7155,13 @@
         <f aca="false">IFERROR(N152/H152,"")</f>
         <v/>
       </c>
-      <c r="P152" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A152,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q152" s="15" t="n">
-        <f aca="false">IFERROR(H152-P152,"")</f>
-        <v>0</v>
+      <c r="P152" s="15" t="str">
+        <f aca="false">IF($A152="","",IF(COUNTIF($A$3:$A152,$A152)=1,SUMIF(cobranza!$B$3:$B$1000,$A152,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q152" s="15" t="str">
+        <f aca="false">IF($A152="","",IF(COUNTIF($A$3:$A152,$A152)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A152,$C$3:$C$1000,"&lt;&gt;Demo")-P152,"↑"))</f>
+        <v/>
       </c>
       <c r="R152" s="17"/>
     </row>
@@ -7187,13 +7187,13 @@
         <f aca="false">IFERROR(N153/H153,"")</f>
         <v/>
       </c>
-      <c r="P153" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A153,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q153" s="15" t="n">
-        <f aca="false">IFERROR(H153-P153,"")</f>
-        <v>0</v>
+      <c r="P153" s="15" t="str">
+        <f aca="false">IF($A153="","",IF(COUNTIF($A$3:$A153,$A153)=1,SUMIF(cobranza!$B$3:$B$1000,$A153,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q153" s="15" t="str">
+        <f aca="false">IF($A153="","",IF(COUNTIF($A$3:$A153,$A153)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A153,$C$3:$C$1000,"&lt;&gt;Demo")-P153,"↑"))</f>
+        <v/>
       </c>
       <c r="R153" s="17"/>
     </row>
@@ -7219,13 +7219,13 @@
         <f aca="false">IFERROR(N154/H154,"")</f>
         <v/>
       </c>
-      <c r="P154" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A154,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q154" s="15" t="n">
-        <f aca="false">IFERROR(H154-P154,"")</f>
-        <v>0</v>
+      <c r="P154" s="15" t="str">
+        <f aca="false">IF($A154="","",IF(COUNTIF($A$3:$A154,$A154)=1,SUMIF(cobranza!$B$3:$B$1000,$A154,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q154" s="15" t="str">
+        <f aca="false">IF($A154="","",IF(COUNTIF($A$3:$A154,$A154)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A154,$C$3:$C$1000,"&lt;&gt;Demo")-P154,"↑"))</f>
+        <v/>
       </c>
       <c r="R154" s="17"/>
     </row>
@@ -7251,13 +7251,13 @@
         <f aca="false">IFERROR(N155/H155,"")</f>
         <v/>
       </c>
-      <c r="P155" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A155,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q155" s="15" t="n">
-        <f aca="false">IFERROR(H155-P155,"")</f>
-        <v>0</v>
+      <c r="P155" s="15" t="str">
+        <f aca="false">IF($A155="","",IF(COUNTIF($A$3:$A155,$A155)=1,SUMIF(cobranza!$B$3:$B$1000,$A155,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q155" s="15" t="str">
+        <f aca="false">IF($A155="","",IF(COUNTIF($A$3:$A155,$A155)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A155,$C$3:$C$1000,"&lt;&gt;Demo")-P155,"↑"))</f>
+        <v/>
       </c>
       <c r="R155" s="17"/>
     </row>
@@ -7283,13 +7283,13 @@
         <f aca="false">IFERROR(N156/H156,"")</f>
         <v/>
       </c>
-      <c r="P156" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A156,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q156" s="15" t="n">
-        <f aca="false">IFERROR(H156-P156,"")</f>
-        <v>0</v>
+      <c r="P156" s="15" t="str">
+        <f aca="false">IF($A156="","",IF(COUNTIF($A$3:$A156,$A156)=1,SUMIF(cobranza!$B$3:$B$1000,$A156,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q156" s="15" t="str">
+        <f aca="false">IF($A156="","",IF(COUNTIF($A$3:$A156,$A156)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A156,$C$3:$C$1000,"&lt;&gt;Demo")-P156,"↑"))</f>
+        <v/>
       </c>
       <c r="R156" s="17"/>
     </row>
@@ -7315,13 +7315,13 @@
         <f aca="false">IFERROR(N157/H157,"")</f>
         <v/>
       </c>
-      <c r="P157" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A157,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q157" s="15" t="n">
-        <f aca="false">IFERROR(H157-P157,"")</f>
-        <v>0</v>
+      <c r="P157" s="15" t="str">
+        <f aca="false">IF($A157="","",IF(COUNTIF($A$3:$A157,$A157)=1,SUMIF(cobranza!$B$3:$B$1000,$A157,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q157" s="15" t="str">
+        <f aca="false">IF($A157="","",IF(COUNTIF($A$3:$A157,$A157)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A157,$C$3:$C$1000,"&lt;&gt;Demo")-P157,"↑"))</f>
+        <v/>
       </c>
       <c r="R157" s="17"/>
     </row>
@@ -7347,13 +7347,13 @@
         <f aca="false">IFERROR(N158/H158,"")</f>
         <v/>
       </c>
-      <c r="P158" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A158,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q158" s="15" t="n">
-        <f aca="false">IFERROR(H158-P158,"")</f>
-        <v>0</v>
+      <c r="P158" s="15" t="str">
+        <f aca="false">IF($A158="","",IF(COUNTIF($A$3:$A158,$A158)=1,SUMIF(cobranza!$B$3:$B$1000,$A158,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q158" s="15" t="str">
+        <f aca="false">IF($A158="","",IF(COUNTIF($A$3:$A158,$A158)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A158,$C$3:$C$1000,"&lt;&gt;Demo")-P158,"↑"))</f>
+        <v/>
       </c>
       <c r="R158" s="17"/>
     </row>
@@ -7379,13 +7379,13 @@
         <f aca="false">IFERROR(N159/H159,"")</f>
         <v/>
       </c>
-      <c r="P159" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A159,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q159" s="15" t="n">
-        <f aca="false">IFERROR(H159-P159,"")</f>
-        <v>0</v>
+      <c r="P159" s="15" t="str">
+        <f aca="false">IF($A159="","",IF(COUNTIF($A$3:$A159,$A159)=1,SUMIF(cobranza!$B$3:$B$1000,$A159,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q159" s="15" t="str">
+        <f aca="false">IF($A159="","",IF(COUNTIF($A$3:$A159,$A159)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A159,$C$3:$C$1000,"&lt;&gt;Demo")-P159,"↑"))</f>
+        <v/>
       </c>
       <c r="R159" s="17"/>
     </row>
@@ -7411,13 +7411,13 @@
         <f aca="false">IFERROR(N160/H160,"")</f>
         <v/>
       </c>
-      <c r="P160" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A160,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q160" s="15" t="n">
-        <f aca="false">IFERROR(H160-P160,"")</f>
-        <v>0</v>
+      <c r="P160" s="15" t="str">
+        <f aca="false">IF($A160="","",IF(COUNTIF($A$3:$A160,$A160)=1,SUMIF(cobranza!$B$3:$B$1000,$A160,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q160" s="15" t="str">
+        <f aca="false">IF($A160="","",IF(COUNTIF($A$3:$A160,$A160)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A160,$C$3:$C$1000,"&lt;&gt;Demo")-P160,"↑"))</f>
+        <v/>
       </c>
       <c r="R160" s="17"/>
     </row>
@@ -7443,13 +7443,13 @@
         <f aca="false">IFERROR(N161/H161,"")</f>
         <v/>
       </c>
-      <c r="P161" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A161,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q161" s="15" t="n">
-        <f aca="false">IFERROR(H161-P161,"")</f>
-        <v>0</v>
+      <c r="P161" s="15" t="str">
+        <f aca="false">IF($A161="","",IF(COUNTIF($A$3:$A161,$A161)=1,SUMIF(cobranza!$B$3:$B$1000,$A161,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q161" s="15" t="str">
+        <f aca="false">IF($A161="","",IF(COUNTIF($A$3:$A161,$A161)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A161,$C$3:$C$1000,"&lt;&gt;Demo")-P161,"↑"))</f>
+        <v/>
       </c>
       <c r="R161" s="17"/>
     </row>
@@ -7475,13 +7475,13 @@
         <f aca="false">IFERROR(N162/H162,"")</f>
         <v/>
       </c>
-      <c r="P162" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A162,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q162" s="15" t="n">
-        <f aca="false">IFERROR(H162-P162,"")</f>
-        <v>0</v>
+      <c r="P162" s="15" t="str">
+        <f aca="false">IF($A162="","",IF(COUNTIF($A$3:$A162,$A162)=1,SUMIF(cobranza!$B$3:$B$1000,$A162,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q162" s="15" t="str">
+        <f aca="false">IF($A162="","",IF(COUNTIF($A$3:$A162,$A162)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A162,$C$3:$C$1000,"&lt;&gt;Demo")-P162,"↑"))</f>
+        <v/>
       </c>
       <c r="R162" s="17"/>
     </row>
@@ -7507,13 +7507,13 @@
         <f aca="false">IFERROR(N163/H163,"")</f>
         <v/>
       </c>
-      <c r="P163" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A163,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q163" s="15" t="n">
-        <f aca="false">IFERROR(H163-P163,"")</f>
-        <v>0</v>
+      <c r="P163" s="15" t="str">
+        <f aca="false">IF($A163="","",IF(COUNTIF($A$3:$A163,$A163)=1,SUMIF(cobranza!$B$3:$B$1000,$A163,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q163" s="15" t="str">
+        <f aca="false">IF($A163="","",IF(COUNTIF($A$3:$A163,$A163)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A163,$C$3:$C$1000,"&lt;&gt;Demo")-P163,"↑"))</f>
+        <v/>
       </c>
       <c r="R163" s="17"/>
     </row>
@@ -7539,13 +7539,13 @@
         <f aca="false">IFERROR(N164/H164,"")</f>
         <v/>
       </c>
-      <c r="P164" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A164,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q164" s="15" t="n">
-        <f aca="false">IFERROR(H164-P164,"")</f>
-        <v>0</v>
+      <c r="P164" s="15" t="str">
+        <f aca="false">IF($A164="","",IF(COUNTIF($A$3:$A164,$A164)=1,SUMIF(cobranza!$B$3:$B$1000,$A164,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q164" s="15" t="str">
+        <f aca="false">IF($A164="","",IF(COUNTIF($A$3:$A164,$A164)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A164,$C$3:$C$1000,"&lt;&gt;Demo")-P164,"↑"))</f>
+        <v/>
       </c>
       <c r="R164" s="17"/>
     </row>
@@ -7571,13 +7571,13 @@
         <f aca="false">IFERROR(N165/H165,"")</f>
         <v/>
       </c>
-      <c r="P165" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A165,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q165" s="15" t="n">
-        <f aca="false">IFERROR(H165-P165,"")</f>
-        <v>0</v>
+      <c r="P165" s="15" t="str">
+        <f aca="false">IF($A165="","",IF(COUNTIF($A$3:$A165,$A165)=1,SUMIF(cobranza!$B$3:$B$1000,$A165,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q165" s="15" t="str">
+        <f aca="false">IF($A165="","",IF(COUNTIF($A$3:$A165,$A165)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A165,$C$3:$C$1000,"&lt;&gt;Demo")-P165,"↑"))</f>
+        <v/>
       </c>
       <c r="R165" s="17"/>
     </row>
@@ -7603,13 +7603,13 @@
         <f aca="false">IFERROR(N166/H166,"")</f>
         <v/>
       </c>
-      <c r="P166" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A166,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q166" s="15" t="n">
-        <f aca="false">IFERROR(H166-P166,"")</f>
-        <v>0</v>
+      <c r="P166" s="15" t="str">
+        <f aca="false">IF($A166="","",IF(COUNTIF($A$3:$A166,$A166)=1,SUMIF(cobranza!$B$3:$B$1000,$A166,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q166" s="15" t="str">
+        <f aca="false">IF($A166="","",IF(COUNTIF($A$3:$A166,$A166)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A166,$C$3:$C$1000,"&lt;&gt;Demo")-P166,"↑"))</f>
+        <v/>
       </c>
       <c r="R166" s="17"/>
     </row>
@@ -7635,13 +7635,13 @@
         <f aca="false">IFERROR(N167/H167,"")</f>
         <v/>
       </c>
-      <c r="P167" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A167,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q167" s="15" t="n">
-        <f aca="false">IFERROR(H167-P167,"")</f>
-        <v>0</v>
+      <c r="P167" s="15" t="str">
+        <f aca="false">IF($A167="","",IF(COUNTIF($A$3:$A167,$A167)=1,SUMIF(cobranza!$B$3:$B$1000,$A167,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q167" s="15" t="str">
+        <f aca="false">IF($A167="","",IF(COUNTIF($A$3:$A167,$A167)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A167,$C$3:$C$1000,"&lt;&gt;Demo")-P167,"↑"))</f>
+        <v/>
       </c>
       <c r="R167" s="17"/>
     </row>
@@ -7667,13 +7667,13 @@
         <f aca="false">IFERROR(N168/H168,"")</f>
         <v/>
       </c>
-      <c r="P168" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A168,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q168" s="15" t="n">
-        <f aca="false">IFERROR(H168-P168,"")</f>
-        <v>0</v>
+      <c r="P168" s="15" t="str">
+        <f aca="false">IF($A168="","",IF(COUNTIF($A$3:$A168,$A168)=1,SUMIF(cobranza!$B$3:$B$1000,$A168,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q168" s="15" t="str">
+        <f aca="false">IF($A168="","",IF(COUNTIF($A$3:$A168,$A168)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A168,$C$3:$C$1000,"&lt;&gt;Demo")-P168,"↑"))</f>
+        <v/>
       </c>
       <c r="R168" s="17"/>
     </row>
@@ -7699,13 +7699,13 @@
         <f aca="false">IFERROR(N169/H169,"")</f>
         <v/>
       </c>
-      <c r="P169" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A169,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q169" s="15" t="n">
-        <f aca="false">IFERROR(H169-P169,"")</f>
-        <v>0</v>
+      <c r="P169" s="15" t="str">
+        <f aca="false">IF($A169="","",IF(COUNTIF($A$3:$A169,$A169)=1,SUMIF(cobranza!$B$3:$B$1000,$A169,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q169" s="15" t="str">
+        <f aca="false">IF($A169="","",IF(COUNTIF($A$3:$A169,$A169)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A169,$C$3:$C$1000,"&lt;&gt;Demo")-P169,"↑"))</f>
+        <v/>
       </c>
       <c r="R169" s="17"/>
     </row>
@@ -7731,13 +7731,13 @@
         <f aca="false">IFERROR(N170/H170,"")</f>
         <v/>
       </c>
-      <c r="P170" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A170,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q170" s="15" t="n">
-        <f aca="false">IFERROR(H170-P170,"")</f>
-        <v>0</v>
+      <c r="P170" s="15" t="str">
+        <f aca="false">IF($A170="","",IF(COUNTIF($A$3:$A170,$A170)=1,SUMIF(cobranza!$B$3:$B$1000,$A170,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q170" s="15" t="str">
+        <f aca="false">IF($A170="","",IF(COUNTIF($A$3:$A170,$A170)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A170,$C$3:$C$1000,"&lt;&gt;Demo")-P170,"↑"))</f>
+        <v/>
       </c>
       <c r="R170" s="17"/>
     </row>
@@ -7763,13 +7763,13 @@
         <f aca="false">IFERROR(N171/H171,"")</f>
         <v/>
       </c>
-      <c r="P171" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A171,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q171" s="15" t="n">
-        <f aca="false">IFERROR(H171-P171,"")</f>
-        <v>0</v>
+      <c r="P171" s="15" t="str">
+        <f aca="false">IF($A171="","",IF(COUNTIF($A$3:$A171,$A171)=1,SUMIF(cobranza!$B$3:$B$1000,$A171,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q171" s="15" t="str">
+        <f aca="false">IF($A171="","",IF(COUNTIF($A$3:$A171,$A171)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A171,$C$3:$C$1000,"&lt;&gt;Demo")-P171,"↑"))</f>
+        <v/>
       </c>
       <c r="R171" s="17"/>
     </row>
@@ -7795,13 +7795,13 @@
         <f aca="false">IFERROR(N172/H172,"")</f>
         <v/>
       </c>
-      <c r="P172" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A172,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q172" s="15" t="n">
-        <f aca="false">IFERROR(H172-P172,"")</f>
-        <v>0</v>
+      <c r="P172" s="15" t="str">
+        <f aca="false">IF($A172="","",IF(COUNTIF($A$3:$A172,$A172)=1,SUMIF(cobranza!$B$3:$B$1000,$A172,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q172" s="15" t="str">
+        <f aca="false">IF($A172="","",IF(COUNTIF($A$3:$A172,$A172)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A172,$C$3:$C$1000,"&lt;&gt;Demo")-P172,"↑"))</f>
+        <v/>
       </c>
       <c r="R172" s="17"/>
     </row>
@@ -7827,13 +7827,13 @@
         <f aca="false">IFERROR(N173/H173,"")</f>
         <v/>
       </c>
-      <c r="P173" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A173,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q173" s="15" t="n">
-        <f aca="false">IFERROR(H173-P173,"")</f>
-        <v>0</v>
+      <c r="P173" s="15" t="str">
+        <f aca="false">IF($A173="","",IF(COUNTIF($A$3:$A173,$A173)=1,SUMIF(cobranza!$B$3:$B$1000,$A173,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q173" s="15" t="str">
+        <f aca="false">IF($A173="","",IF(COUNTIF($A$3:$A173,$A173)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A173,$C$3:$C$1000,"&lt;&gt;Demo")-P173,"↑"))</f>
+        <v/>
       </c>
       <c r="R173" s="17"/>
     </row>
@@ -7859,13 +7859,13 @@
         <f aca="false">IFERROR(N174/H174,"")</f>
         <v/>
       </c>
-      <c r="P174" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A174,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q174" s="15" t="n">
-        <f aca="false">IFERROR(H174-P174,"")</f>
-        <v>0</v>
+      <c r="P174" s="15" t="str">
+        <f aca="false">IF($A174="","",IF(COUNTIF($A$3:$A174,$A174)=1,SUMIF(cobranza!$B$3:$B$1000,$A174,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q174" s="15" t="str">
+        <f aca="false">IF($A174="","",IF(COUNTIF($A$3:$A174,$A174)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A174,$C$3:$C$1000,"&lt;&gt;Demo")-P174,"↑"))</f>
+        <v/>
       </c>
       <c r="R174" s="17"/>
     </row>
@@ -7891,13 +7891,13 @@
         <f aca="false">IFERROR(N175/H175,"")</f>
         <v/>
       </c>
-      <c r="P175" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A175,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q175" s="15" t="n">
-        <f aca="false">IFERROR(H175-P175,"")</f>
-        <v>0</v>
+      <c r="P175" s="15" t="str">
+        <f aca="false">IF($A175="","",IF(COUNTIF($A$3:$A175,$A175)=1,SUMIF(cobranza!$B$3:$B$1000,$A175,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q175" s="15" t="str">
+        <f aca="false">IF($A175="","",IF(COUNTIF($A$3:$A175,$A175)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A175,$C$3:$C$1000,"&lt;&gt;Demo")-P175,"↑"))</f>
+        <v/>
       </c>
       <c r="R175" s="17"/>
     </row>
@@ -7923,13 +7923,13 @@
         <f aca="false">IFERROR(N176/H176,"")</f>
         <v/>
       </c>
-      <c r="P176" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A176,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q176" s="15" t="n">
-        <f aca="false">IFERROR(H176-P176,"")</f>
-        <v>0</v>
+      <c r="P176" s="15" t="str">
+        <f aca="false">IF($A176="","",IF(COUNTIF($A$3:$A176,$A176)=1,SUMIF(cobranza!$B$3:$B$1000,$A176,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q176" s="15" t="str">
+        <f aca="false">IF($A176="","",IF(COUNTIF($A$3:$A176,$A176)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A176,$C$3:$C$1000,"&lt;&gt;Demo")-P176,"↑"))</f>
+        <v/>
       </c>
       <c r="R176" s="17"/>
     </row>
@@ -7955,13 +7955,13 @@
         <f aca="false">IFERROR(N177/H177,"")</f>
         <v/>
       </c>
-      <c r="P177" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A177,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q177" s="15" t="n">
-        <f aca="false">IFERROR(H177-P177,"")</f>
-        <v>0</v>
+      <c r="P177" s="15" t="str">
+        <f aca="false">IF($A177="","",IF(COUNTIF($A$3:$A177,$A177)=1,SUMIF(cobranza!$B$3:$B$1000,$A177,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q177" s="15" t="str">
+        <f aca="false">IF($A177="","",IF(COUNTIF($A$3:$A177,$A177)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A177,$C$3:$C$1000,"&lt;&gt;Demo")-P177,"↑"))</f>
+        <v/>
       </c>
       <c r="R177" s="17"/>
     </row>
@@ -7987,13 +7987,13 @@
         <f aca="false">IFERROR(N178/H178,"")</f>
         <v/>
       </c>
-      <c r="P178" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A178,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q178" s="15" t="n">
-        <f aca="false">IFERROR(H178-P178,"")</f>
-        <v>0</v>
+      <c r="P178" s="15" t="str">
+        <f aca="false">IF($A178="","",IF(COUNTIF($A$3:$A178,$A178)=1,SUMIF(cobranza!$B$3:$B$1000,$A178,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q178" s="15" t="str">
+        <f aca="false">IF($A178="","",IF(COUNTIF($A$3:$A178,$A178)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A178,$C$3:$C$1000,"&lt;&gt;Demo")-P178,"↑"))</f>
+        <v/>
       </c>
       <c r="R178" s="17"/>
     </row>
@@ -8019,13 +8019,13 @@
         <f aca="false">IFERROR(N179/H179,"")</f>
         <v/>
       </c>
-      <c r="P179" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A179,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q179" s="15" t="n">
-        <f aca="false">IFERROR(H179-P179,"")</f>
-        <v>0</v>
+      <c r="P179" s="15" t="str">
+        <f aca="false">IF($A179="","",IF(COUNTIF($A$3:$A179,$A179)=1,SUMIF(cobranza!$B$3:$B$1000,$A179,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q179" s="15" t="str">
+        <f aca="false">IF($A179="","",IF(COUNTIF($A$3:$A179,$A179)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A179,$C$3:$C$1000,"&lt;&gt;Demo")-P179,"↑"))</f>
+        <v/>
       </c>
       <c r="R179" s="17"/>
     </row>
@@ -8051,13 +8051,13 @@
         <f aca="false">IFERROR(N180/H180,"")</f>
         <v/>
       </c>
-      <c r="P180" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A180,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q180" s="15" t="n">
-        <f aca="false">IFERROR(H180-P180,"")</f>
-        <v>0</v>
+      <c r="P180" s="15" t="str">
+        <f aca="false">IF($A180="","",IF(COUNTIF($A$3:$A180,$A180)=1,SUMIF(cobranza!$B$3:$B$1000,$A180,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q180" s="15" t="str">
+        <f aca="false">IF($A180="","",IF(COUNTIF($A$3:$A180,$A180)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A180,$C$3:$C$1000,"&lt;&gt;Demo")-P180,"↑"))</f>
+        <v/>
       </c>
       <c r="R180" s="17"/>
     </row>
@@ -8083,13 +8083,13 @@
         <f aca="false">IFERROR(N181/H181,"")</f>
         <v/>
       </c>
-      <c r="P181" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A181,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q181" s="15" t="n">
-        <f aca="false">IFERROR(H181-P181,"")</f>
-        <v>0</v>
+      <c r="P181" s="15" t="str">
+        <f aca="false">IF($A181="","",IF(COUNTIF($A$3:$A181,$A181)=1,SUMIF(cobranza!$B$3:$B$1000,$A181,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q181" s="15" t="str">
+        <f aca="false">IF($A181="","",IF(COUNTIF($A$3:$A181,$A181)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A181,$C$3:$C$1000,"&lt;&gt;Demo")-P181,"↑"))</f>
+        <v/>
       </c>
       <c r="R181" s="17"/>
     </row>
@@ -8115,13 +8115,13 @@
         <f aca="false">IFERROR(N182/H182,"")</f>
         <v/>
       </c>
-      <c r="P182" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A182,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q182" s="15" t="n">
-        <f aca="false">IFERROR(H182-P182,"")</f>
-        <v>0</v>
+      <c r="P182" s="15" t="str">
+        <f aca="false">IF($A182="","",IF(COUNTIF($A$3:$A182,$A182)=1,SUMIF(cobranza!$B$3:$B$1000,$A182,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q182" s="15" t="str">
+        <f aca="false">IF($A182="","",IF(COUNTIF($A$3:$A182,$A182)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A182,$C$3:$C$1000,"&lt;&gt;Demo")-P182,"↑"))</f>
+        <v/>
       </c>
       <c r="R182" s="17"/>
     </row>
@@ -8147,13 +8147,13 @@
         <f aca="false">IFERROR(N183/H183,"")</f>
         <v/>
       </c>
-      <c r="P183" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A183,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q183" s="15" t="n">
-        <f aca="false">IFERROR(H183-P183,"")</f>
-        <v>0</v>
+      <c r="P183" s="15" t="str">
+        <f aca="false">IF($A183="","",IF(COUNTIF($A$3:$A183,$A183)=1,SUMIF(cobranza!$B$3:$B$1000,$A183,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q183" s="15" t="str">
+        <f aca="false">IF($A183="","",IF(COUNTIF($A$3:$A183,$A183)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A183,$C$3:$C$1000,"&lt;&gt;Demo")-P183,"↑"))</f>
+        <v/>
       </c>
       <c r="R183" s="17"/>
     </row>
@@ -8179,13 +8179,13 @@
         <f aca="false">IFERROR(N184/H184,"")</f>
         <v/>
       </c>
-      <c r="P184" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A184,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q184" s="15" t="n">
-        <f aca="false">IFERROR(H184-P184,"")</f>
-        <v>0</v>
+      <c r="P184" s="15" t="str">
+        <f aca="false">IF($A184="","",IF(COUNTIF($A$3:$A184,$A184)=1,SUMIF(cobranza!$B$3:$B$1000,$A184,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q184" s="15" t="str">
+        <f aca="false">IF($A184="","",IF(COUNTIF($A$3:$A184,$A184)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A184,$C$3:$C$1000,"&lt;&gt;Demo")-P184,"↑"))</f>
+        <v/>
       </c>
       <c r="R184" s="17"/>
     </row>
@@ -8211,13 +8211,13 @@
         <f aca="false">IFERROR(N185/H185,"")</f>
         <v/>
       </c>
-      <c r="P185" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A185,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q185" s="15" t="n">
-        <f aca="false">IFERROR(H185-P185,"")</f>
-        <v>0</v>
+      <c r="P185" s="15" t="str">
+        <f aca="false">IF($A185="","",IF(COUNTIF($A$3:$A185,$A185)=1,SUMIF(cobranza!$B$3:$B$1000,$A185,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q185" s="15" t="str">
+        <f aca="false">IF($A185="","",IF(COUNTIF($A$3:$A185,$A185)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A185,$C$3:$C$1000,"&lt;&gt;Demo")-P185,"↑"))</f>
+        <v/>
       </c>
       <c r="R185" s="17"/>
     </row>
@@ -8243,13 +8243,13 @@
         <f aca="false">IFERROR(N186/H186,"")</f>
         <v/>
       </c>
-      <c r="P186" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A186,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q186" s="15" t="n">
-        <f aca="false">IFERROR(H186-P186,"")</f>
-        <v>0</v>
+      <c r="P186" s="15" t="str">
+        <f aca="false">IF($A186="","",IF(COUNTIF($A$3:$A186,$A186)=1,SUMIF(cobranza!$B$3:$B$1000,$A186,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q186" s="15" t="str">
+        <f aca="false">IF($A186="","",IF(COUNTIF($A$3:$A186,$A186)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A186,$C$3:$C$1000,"&lt;&gt;Demo")-P186,"↑"))</f>
+        <v/>
       </c>
       <c r="R186" s="17"/>
     </row>
@@ -8275,13 +8275,13 @@
         <f aca="false">IFERROR(N187/H187,"")</f>
         <v/>
       </c>
-      <c r="P187" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A187,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q187" s="15" t="n">
-        <f aca="false">IFERROR(H187-P187,"")</f>
-        <v>0</v>
+      <c r="P187" s="15" t="str">
+        <f aca="false">IF($A187="","",IF(COUNTIF($A$3:$A187,$A187)=1,SUMIF(cobranza!$B$3:$B$1000,$A187,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q187" s="15" t="str">
+        <f aca="false">IF($A187="","",IF(COUNTIF($A$3:$A187,$A187)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A187,$C$3:$C$1000,"&lt;&gt;Demo")-P187,"↑"))</f>
+        <v/>
       </c>
       <c r="R187" s="17"/>
     </row>
@@ -8307,13 +8307,13 @@
         <f aca="false">IFERROR(N188/H188,"")</f>
         <v/>
       </c>
-      <c r="P188" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A188,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q188" s="15" t="n">
-        <f aca="false">IFERROR(H188-P188,"")</f>
-        <v>0</v>
+      <c r="P188" s="15" t="str">
+        <f aca="false">IF($A188="","",IF(COUNTIF($A$3:$A188,$A188)=1,SUMIF(cobranza!$B$3:$B$1000,$A188,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q188" s="15" t="str">
+        <f aca="false">IF($A188="","",IF(COUNTIF($A$3:$A188,$A188)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A188,$C$3:$C$1000,"&lt;&gt;Demo")-P188,"↑"))</f>
+        <v/>
       </c>
       <c r="R188" s="17"/>
     </row>
@@ -8339,13 +8339,13 @@
         <f aca="false">IFERROR(N189/H189,"")</f>
         <v/>
       </c>
-      <c r="P189" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A189,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q189" s="15" t="n">
-        <f aca="false">IFERROR(H189-P189,"")</f>
-        <v>0</v>
+      <c r="P189" s="15" t="str">
+        <f aca="false">IF($A189="","",IF(COUNTIF($A$3:$A189,$A189)=1,SUMIF(cobranza!$B$3:$B$1000,$A189,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q189" s="15" t="str">
+        <f aca="false">IF($A189="","",IF(COUNTIF($A$3:$A189,$A189)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A189,$C$3:$C$1000,"&lt;&gt;Demo")-P189,"↑"))</f>
+        <v/>
       </c>
       <c r="R189" s="17"/>
     </row>
@@ -8371,13 +8371,13 @@
         <f aca="false">IFERROR(N190/H190,"")</f>
         <v/>
       </c>
-      <c r="P190" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A190,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q190" s="15" t="n">
-        <f aca="false">IFERROR(H190-P190,"")</f>
-        <v>0</v>
+      <c r="P190" s="15" t="str">
+        <f aca="false">IF($A190="","",IF(COUNTIF($A$3:$A190,$A190)=1,SUMIF(cobranza!$B$3:$B$1000,$A190,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q190" s="15" t="str">
+        <f aca="false">IF($A190="","",IF(COUNTIF($A$3:$A190,$A190)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A190,$C$3:$C$1000,"&lt;&gt;Demo")-P190,"↑"))</f>
+        <v/>
       </c>
       <c r="R190" s="17"/>
     </row>
@@ -8403,13 +8403,13 @@
         <f aca="false">IFERROR(N191/H191,"")</f>
         <v/>
       </c>
-      <c r="P191" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A191,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q191" s="15" t="n">
-        <f aca="false">IFERROR(H191-P191,"")</f>
-        <v>0</v>
+      <c r="P191" s="15" t="str">
+        <f aca="false">IF($A191="","",IF(COUNTIF($A$3:$A191,$A191)=1,SUMIF(cobranza!$B$3:$B$1000,$A191,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q191" s="15" t="str">
+        <f aca="false">IF($A191="","",IF(COUNTIF($A$3:$A191,$A191)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A191,$C$3:$C$1000,"&lt;&gt;Demo")-P191,"↑"))</f>
+        <v/>
       </c>
       <c r="R191" s="17"/>
     </row>
@@ -8435,13 +8435,13 @@
         <f aca="false">IFERROR(N192/H192,"")</f>
         <v/>
       </c>
-      <c r="P192" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A192,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q192" s="15" t="n">
-        <f aca="false">IFERROR(H192-P192,"")</f>
-        <v>0</v>
+      <c r="P192" s="15" t="str">
+        <f aca="false">IF($A192="","",IF(COUNTIF($A$3:$A192,$A192)=1,SUMIF(cobranza!$B$3:$B$1000,$A192,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q192" s="15" t="str">
+        <f aca="false">IF($A192="","",IF(COUNTIF($A$3:$A192,$A192)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A192,$C$3:$C$1000,"&lt;&gt;Demo")-P192,"↑"))</f>
+        <v/>
       </c>
       <c r="R192" s="17"/>
     </row>
@@ -8467,13 +8467,13 @@
         <f aca="false">IFERROR(N193/H193,"")</f>
         <v/>
       </c>
-      <c r="P193" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A193,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q193" s="15" t="n">
-        <f aca="false">IFERROR(H193-P193,"")</f>
-        <v>0</v>
+      <c r="P193" s="15" t="str">
+        <f aca="false">IF($A193="","",IF(COUNTIF($A$3:$A193,$A193)=1,SUMIF(cobranza!$B$3:$B$1000,$A193,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q193" s="15" t="str">
+        <f aca="false">IF($A193="","",IF(COUNTIF($A$3:$A193,$A193)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A193,$C$3:$C$1000,"&lt;&gt;Demo")-P193,"↑"))</f>
+        <v/>
       </c>
       <c r="R193" s="17"/>
     </row>
@@ -8499,13 +8499,13 @@
         <f aca="false">IFERROR(N194/H194,"")</f>
         <v/>
       </c>
-      <c r="P194" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A194,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q194" s="15" t="n">
-        <f aca="false">IFERROR(H194-P194,"")</f>
-        <v>0</v>
+      <c r="P194" s="15" t="str">
+        <f aca="false">IF($A194="","",IF(COUNTIF($A$3:$A194,$A194)=1,SUMIF(cobranza!$B$3:$B$1000,$A194,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q194" s="15" t="str">
+        <f aca="false">IF($A194="","",IF(COUNTIF($A$3:$A194,$A194)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A194,$C$3:$C$1000,"&lt;&gt;Demo")-P194,"↑"))</f>
+        <v/>
       </c>
       <c r="R194" s="17"/>
     </row>
@@ -8531,13 +8531,13 @@
         <f aca="false">IFERROR(N195/H195,"")</f>
         <v/>
       </c>
-      <c r="P195" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A195,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q195" s="15" t="n">
-        <f aca="false">IFERROR(H195-P195,"")</f>
-        <v>0</v>
+      <c r="P195" s="15" t="str">
+        <f aca="false">IF($A195="","",IF(COUNTIF($A$3:$A195,$A195)=1,SUMIF(cobranza!$B$3:$B$1000,$A195,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q195" s="15" t="str">
+        <f aca="false">IF($A195="","",IF(COUNTIF($A$3:$A195,$A195)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A195,$C$3:$C$1000,"&lt;&gt;Demo")-P195,"↑"))</f>
+        <v/>
       </c>
       <c r="R195" s="17"/>
     </row>
@@ -8563,13 +8563,13 @@
         <f aca="false">IFERROR(N196/H196,"")</f>
         <v/>
       </c>
-      <c r="P196" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A196,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q196" s="15" t="n">
-        <f aca="false">IFERROR(H196-P196,"")</f>
-        <v>0</v>
+      <c r="P196" s="15" t="str">
+        <f aca="false">IF($A196="","",IF(COUNTIF($A$3:$A196,$A196)=1,SUMIF(cobranza!$B$3:$B$1000,$A196,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q196" s="15" t="str">
+        <f aca="false">IF($A196="","",IF(COUNTIF($A$3:$A196,$A196)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A196,$C$3:$C$1000,"&lt;&gt;Demo")-P196,"↑"))</f>
+        <v/>
       </c>
       <c r="R196" s="17"/>
     </row>
@@ -8595,13 +8595,13 @@
         <f aca="false">IFERROR(N197/H197,"")</f>
         <v/>
       </c>
-      <c r="P197" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A197,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q197" s="15" t="n">
-        <f aca="false">IFERROR(H197-P197,"")</f>
-        <v>0</v>
+      <c r="P197" s="15" t="str">
+        <f aca="false">IF($A197="","",IF(COUNTIF($A$3:$A197,$A197)=1,SUMIF(cobranza!$B$3:$B$1000,$A197,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q197" s="15" t="str">
+        <f aca="false">IF($A197="","",IF(COUNTIF($A$3:$A197,$A197)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A197,$C$3:$C$1000,"&lt;&gt;Demo")-P197,"↑"))</f>
+        <v/>
       </c>
       <c r="R197" s="17"/>
     </row>
@@ -8627,13 +8627,13 @@
         <f aca="false">IFERROR(N198/H198,"")</f>
         <v/>
       </c>
-      <c r="P198" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A198,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q198" s="15" t="n">
-        <f aca="false">IFERROR(H198-P198,"")</f>
-        <v>0</v>
+      <c r="P198" s="15" t="str">
+        <f aca="false">IF($A198="","",IF(COUNTIF($A$3:$A198,$A198)=1,SUMIF(cobranza!$B$3:$B$1000,$A198,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q198" s="15" t="str">
+        <f aca="false">IF($A198="","",IF(COUNTIF($A$3:$A198,$A198)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A198,$C$3:$C$1000,"&lt;&gt;Demo")-P198,"↑"))</f>
+        <v/>
       </c>
       <c r="R198" s="17"/>
     </row>
@@ -8659,13 +8659,13 @@
         <f aca="false">IFERROR(N199/H199,"")</f>
         <v/>
       </c>
-      <c r="P199" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A199,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q199" s="15" t="n">
-        <f aca="false">IFERROR(H199-P199,"")</f>
-        <v>0</v>
+      <c r="P199" s="15" t="str">
+        <f aca="false">IF($A199="","",IF(COUNTIF($A$3:$A199,$A199)=1,SUMIF(cobranza!$B$3:$B$1000,$A199,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q199" s="15" t="str">
+        <f aca="false">IF($A199="","",IF(COUNTIF($A$3:$A199,$A199)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A199,$C$3:$C$1000,"&lt;&gt;Demo")-P199,"↑"))</f>
+        <v/>
       </c>
       <c r="R199" s="17"/>
     </row>
@@ -8691,13 +8691,13 @@
         <f aca="false">IFERROR(N200/H200,"")</f>
         <v/>
       </c>
-      <c r="P200" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A200,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q200" s="15" t="n">
-        <f aca="false">IFERROR(H200-P200,"")</f>
-        <v>0</v>
+      <c r="P200" s="15" t="str">
+        <f aca="false">IF($A200="","",IF(COUNTIF($A$3:$A200,$A200)=1,SUMIF(cobranza!$B$3:$B$1000,$A200,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q200" s="15" t="str">
+        <f aca="false">IF($A200="","",IF(COUNTIF($A$3:$A200,$A200)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A200,$C$3:$C$1000,"&lt;&gt;Demo")-P200,"↑"))</f>
+        <v/>
       </c>
       <c r="R200" s="17"/>
     </row>
@@ -8723,13 +8723,13 @@
         <f aca="false">IFERROR(N201/H201,"")</f>
         <v/>
       </c>
-      <c r="P201" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A201,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q201" s="15" t="n">
-        <f aca="false">IFERROR(H201-P201,"")</f>
-        <v>0</v>
+      <c r="P201" s="15" t="str">
+        <f aca="false">IF($A201="","",IF(COUNTIF($A$3:$A201,$A201)=1,SUMIF(cobranza!$B$3:$B$1000,$A201,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q201" s="15" t="str">
+        <f aca="false">IF($A201="","",IF(COUNTIF($A$3:$A201,$A201)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A201,$C$3:$C$1000,"&lt;&gt;Demo")-P201,"↑"))</f>
+        <v/>
       </c>
       <c r="R201" s="17"/>
     </row>
@@ -8755,13 +8755,13 @@
         <f aca="false">IFERROR(N202/H202,"")</f>
         <v/>
       </c>
-      <c r="P202" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A202,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q202" s="15" t="n">
-        <f aca="false">IFERROR(H202-P202,"")</f>
-        <v>0</v>
+      <c r="P202" s="15" t="str">
+        <f aca="false">IF($A202="","",IF(COUNTIF($A$3:$A202,$A202)=1,SUMIF(cobranza!$B$3:$B$1000,$A202,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q202" s="15" t="str">
+        <f aca="false">IF($A202="","",IF(COUNTIF($A$3:$A202,$A202)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A202,$C$3:$C$1000,"&lt;&gt;Demo")-P202,"↑"))</f>
+        <v/>
       </c>
       <c r="R202" s="17"/>
     </row>
@@ -8787,13 +8787,13 @@
         <f aca="false">IFERROR(N203/H203,"")</f>
         <v/>
       </c>
-      <c r="P203" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A203,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q203" s="15" t="n">
-        <f aca="false">IFERROR(H203-P203,"")</f>
-        <v>0</v>
+      <c r="P203" s="15" t="str">
+        <f aca="false">IF($A203="","",IF(COUNTIF($A$3:$A203,$A203)=1,SUMIF(cobranza!$B$3:$B$1000,$A203,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q203" s="15" t="str">
+        <f aca="false">IF($A203="","",IF(COUNTIF($A$3:$A203,$A203)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A203,$C$3:$C$1000,"&lt;&gt;Demo")-P203,"↑"))</f>
+        <v/>
       </c>
       <c r="R203" s="17"/>
     </row>
@@ -8819,13 +8819,13 @@
         <f aca="false">IFERROR(N204/H204,"")</f>
         <v/>
       </c>
-      <c r="P204" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A204,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q204" s="15" t="n">
-        <f aca="false">IFERROR(H204-P204,"")</f>
-        <v>0</v>
+      <c r="P204" s="15" t="str">
+        <f aca="false">IF($A204="","",IF(COUNTIF($A$3:$A204,$A204)=1,SUMIF(cobranza!$B$3:$B$1000,$A204,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q204" s="15" t="str">
+        <f aca="false">IF($A204="","",IF(COUNTIF($A$3:$A204,$A204)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A204,$C$3:$C$1000,"&lt;&gt;Demo")-P204,"↑"))</f>
+        <v/>
       </c>
       <c r="R204" s="17"/>
     </row>
@@ -8851,13 +8851,13 @@
         <f aca="false">IFERROR(N205/H205,"")</f>
         <v/>
       </c>
-      <c r="P205" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A205,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q205" s="15" t="n">
-        <f aca="false">IFERROR(H205-P205,"")</f>
-        <v>0</v>
+      <c r="P205" s="15" t="str">
+        <f aca="false">IF($A205="","",IF(COUNTIF($A$3:$A205,$A205)=1,SUMIF(cobranza!$B$3:$B$1000,$A205,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q205" s="15" t="str">
+        <f aca="false">IF($A205="","",IF(COUNTIF($A$3:$A205,$A205)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A205,$C$3:$C$1000,"&lt;&gt;Demo")-P205,"↑"))</f>
+        <v/>
       </c>
       <c r="R205" s="17"/>
     </row>
@@ -8883,13 +8883,13 @@
         <f aca="false">IFERROR(N206/H206,"")</f>
         <v/>
       </c>
-      <c r="P206" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A206,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q206" s="15" t="n">
-        <f aca="false">IFERROR(H206-P206,"")</f>
-        <v>0</v>
+      <c r="P206" s="15" t="str">
+        <f aca="false">IF($A206="","",IF(COUNTIF($A$3:$A206,$A206)=1,SUMIF(cobranza!$B$3:$B$1000,$A206,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q206" s="15" t="str">
+        <f aca="false">IF($A206="","",IF(COUNTIF($A$3:$A206,$A206)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A206,$C$3:$C$1000,"&lt;&gt;Demo")-P206,"↑"))</f>
+        <v/>
       </c>
       <c r="R206" s="17"/>
     </row>
@@ -8915,13 +8915,13 @@
         <f aca="false">IFERROR(N207/H207,"")</f>
         <v/>
       </c>
-      <c r="P207" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A207,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q207" s="15" t="n">
-        <f aca="false">IFERROR(H207-P207,"")</f>
-        <v>0</v>
+      <c r="P207" s="15" t="str">
+        <f aca="false">IF($A207="","",IF(COUNTIF($A$3:$A207,$A207)=1,SUMIF(cobranza!$B$3:$B$1000,$A207,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q207" s="15" t="str">
+        <f aca="false">IF($A207="","",IF(COUNTIF($A$3:$A207,$A207)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A207,$C$3:$C$1000,"&lt;&gt;Demo")-P207,"↑"))</f>
+        <v/>
       </c>
       <c r="R207" s="17"/>
     </row>
@@ -8947,13 +8947,13 @@
         <f aca="false">IFERROR(N208/H208,"")</f>
         <v/>
       </c>
-      <c r="P208" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A208,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q208" s="15" t="n">
-        <f aca="false">IFERROR(H208-P208,"")</f>
-        <v>0</v>
+      <c r="P208" s="15" t="str">
+        <f aca="false">IF($A208="","",IF(COUNTIF($A$3:$A208,$A208)=1,SUMIF(cobranza!$B$3:$B$1000,$A208,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q208" s="15" t="str">
+        <f aca="false">IF($A208="","",IF(COUNTIF($A$3:$A208,$A208)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A208,$C$3:$C$1000,"&lt;&gt;Demo")-P208,"↑"))</f>
+        <v/>
       </c>
       <c r="R208" s="17"/>
     </row>
@@ -8979,13 +8979,13 @@
         <f aca="false">IFERROR(N209/H209,"")</f>
         <v/>
       </c>
-      <c r="P209" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A209,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q209" s="15" t="n">
-        <f aca="false">IFERROR(H209-P209,"")</f>
-        <v>0</v>
+      <c r="P209" s="15" t="str">
+        <f aca="false">IF($A209="","",IF(COUNTIF($A$3:$A209,$A209)=1,SUMIF(cobranza!$B$3:$B$1000,$A209,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q209" s="15" t="str">
+        <f aca="false">IF($A209="","",IF(COUNTIF($A$3:$A209,$A209)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A209,$C$3:$C$1000,"&lt;&gt;Demo")-P209,"↑"))</f>
+        <v/>
       </c>
       <c r="R209" s="17"/>
     </row>
@@ -9011,13 +9011,13 @@
         <f aca="false">IFERROR(N210/H210,"")</f>
         <v/>
       </c>
-      <c r="P210" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A210,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q210" s="15" t="n">
-        <f aca="false">IFERROR(H210-P210,"")</f>
-        <v>0</v>
+      <c r="P210" s="15" t="str">
+        <f aca="false">IF($A210="","",IF(COUNTIF($A$3:$A210,$A210)=1,SUMIF(cobranza!$B$3:$B$1000,$A210,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q210" s="15" t="str">
+        <f aca="false">IF($A210="","",IF(COUNTIF($A$3:$A210,$A210)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A210,$C$3:$C$1000,"&lt;&gt;Demo")-P210,"↑"))</f>
+        <v/>
       </c>
       <c r="R210" s="17"/>
     </row>
@@ -9043,13 +9043,13 @@
         <f aca="false">IFERROR(N211/H211,"")</f>
         <v/>
       </c>
-      <c r="P211" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A211,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q211" s="15" t="n">
-        <f aca="false">IFERROR(H211-P211,"")</f>
-        <v>0</v>
+      <c r="P211" s="15" t="str">
+        <f aca="false">IF($A211="","",IF(COUNTIF($A$3:$A211,$A211)=1,SUMIF(cobranza!$B$3:$B$1000,$A211,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q211" s="15" t="str">
+        <f aca="false">IF($A211="","",IF(COUNTIF($A$3:$A211,$A211)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A211,$C$3:$C$1000,"&lt;&gt;Demo")-P211,"↑"))</f>
+        <v/>
       </c>
       <c r="R211" s="17"/>
     </row>
@@ -9075,13 +9075,13 @@
         <f aca="false">IFERROR(N212/H212,"")</f>
         <v/>
       </c>
-      <c r="P212" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A212,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q212" s="15" t="n">
-        <f aca="false">IFERROR(H212-P212,"")</f>
-        <v>0</v>
+      <c r="P212" s="15" t="str">
+        <f aca="false">IF($A212="","",IF(COUNTIF($A$3:$A212,$A212)=1,SUMIF(cobranza!$B$3:$B$1000,$A212,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q212" s="15" t="str">
+        <f aca="false">IF($A212="","",IF(COUNTIF($A$3:$A212,$A212)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A212,$C$3:$C$1000,"&lt;&gt;Demo")-P212,"↑"))</f>
+        <v/>
       </c>
       <c r="R212" s="17"/>
     </row>
@@ -9107,13 +9107,13 @@
         <f aca="false">IFERROR(N213/H213,"")</f>
         <v/>
       </c>
-      <c r="P213" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A213,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q213" s="15" t="n">
-        <f aca="false">IFERROR(H213-P213,"")</f>
-        <v>0</v>
+      <c r="P213" s="15" t="str">
+        <f aca="false">IF($A213="","",IF(COUNTIF($A$3:$A213,$A213)=1,SUMIF(cobranza!$B$3:$B$1000,$A213,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q213" s="15" t="str">
+        <f aca="false">IF($A213="","",IF(COUNTIF($A$3:$A213,$A213)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A213,$C$3:$C$1000,"&lt;&gt;Demo")-P213,"↑"))</f>
+        <v/>
       </c>
       <c r="R213" s="17"/>
     </row>
@@ -9139,13 +9139,13 @@
         <f aca="false">IFERROR(N214/H214,"")</f>
         <v/>
       </c>
-      <c r="P214" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A214,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q214" s="15" t="n">
-        <f aca="false">IFERROR(H214-P214,"")</f>
-        <v>0</v>
+      <c r="P214" s="15" t="str">
+        <f aca="false">IF($A214="","",IF(COUNTIF($A$3:$A214,$A214)=1,SUMIF(cobranza!$B$3:$B$1000,$A214,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q214" s="15" t="str">
+        <f aca="false">IF($A214="","",IF(COUNTIF($A$3:$A214,$A214)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A214,$C$3:$C$1000,"&lt;&gt;Demo")-P214,"↑"))</f>
+        <v/>
       </c>
       <c r="R214" s="17"/>
     </row>
@@ -9171,13 +9171,13 @@
         <f aca="false">IFERROR(N215/H215,"")</f>
         <v/>
       </c>
-      <c r="P215" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A215,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q215" s="15" t="n">
-        <f aca="false">IFERROR(H215-P215,"")</f>
-        <v>0</v>
+      <c r="P215" s="15" t="str">
+        <f aca="false">IF($A215="","",IF(COUNTIF($A$3:$A215,$A215)=1,SUMIF(cobranza!$B$3:$B$1000,$A215,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q215" s="15" t="str">
+        <f aca="false">IF($A215="","",IF(COUNTIF($A$3:$A215,$A215)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A215,$C$3:$C$1000,"&lt;&gt;Demo")-P215,"↑"))</f>
+        <v/>
       </c>
       <c r="R215" s="17"/>
     </row>
@@ -9203,13 +9203,13 @@
         <f aca="false">IFERROR(N216/H216,"")</f>
         <v/>
       </c>
-      <c r="P216" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A216,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q216" s="15" t="n">
-        <f aca="false">IFERROR(H216-P216,"")</f>
-        <v>0</v>
+      <c r="P216" s="15" t="str">
+        <f aca="false">IF($A216="","",IF(COUNTIF($A$3:$A216,$A216)=1,SUMIF(cobranza!$B$3:$B$1000,$A216,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q216" s="15" t="str">
+        <f aca="false">IF($A216="","",IF(COUNTIF($A$3:$A216,$A216)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A216,$C$3:$C$1000,"&lt;&gt;Demo")-P216,"↑"))</f>
+        <v/>
       </c>
       <c r="R216" s="17"/>
     </row>
@@ -9235,13 +9235,13 @@
         <f aca="false">IFERROR(N217/H217,"")</f>
         <v/>
       </c>
-      <c r="P217" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A217,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q217" s="15" t="n">
-        <f aca="false">IFERROR(H217-P217,"")</f>
-        <v>0</v>
+      <c r="P217" s="15" t="str">
+        <f aca="false">IF($A217="","",IF(COUNTIF($A$3:$A217,$A217)=1,SUMIF(cobranza!$B$3:$B$1000,$A217,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q217" s="15" t="str">
+        <f aca="false">IF($A217="","",IF(COUNTIF($A$3:$A217,$A217)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A217,$C$3:$C$1000,"&lt;&gt;Demo")-P217,"↑"))</f>
+        <v/>
       </c>
       <c r="R217" s="17"/>
     </row>
@@ -9267,13 +9267,13 @@
         <f aca="false">IFERROR(N218/H218,"")</f>
         <v/>
       </c>
-      <c r="P218" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A218,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q218" s="15" t="n">
-        <f aca="false">IFERROR(H218-P218,"")</f>
-        <v>0</v>
+      <c r="P218" s="15" t="str">
+        <f aca="false">IF($A218="","",IF(COUNTIF($A$3:$A218,$A218)=1,SUMIF(cobranza!$B$3:$B$1000,$A218,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q218" s="15" t="str">
+        <f aca="false">IF($A218="","",IF(COUNTIF($A$3:$A218,$A218)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A218,$C$3:$C$1000,"&lt;&gt;Demo")-P218,"↑"))</f>
+        <v/>
       </c>
       <c r="R218" s="17"/>
     </row>
@@ -9299,13 +9299,13 @@
         <f aca="false">IFERROR(N219/H219,"")</f>
         <v/>
       </c>
-      <c r="P219" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A219,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q219" s="15" t="n">
-        <f aca="false">IFERROR(H219-P219,"")</f>
-        <v>0</v>
+      <c r="P219" s="15" t="str">
+        <f aca="false">IF($A219="","",IF(COUNTIF($A$3:$A219,$A219)=1,SUMIF(cobranza!$B$3:$B$1000,$A219,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q219" s="15" t="str">
+        <f aca="false">IF($A219="","",IF(COUNTIF($A$3:$A219,$A219)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A219,$C$3:$C$1000,"&lt;&gt;Demo")-P219,"↑"))</f>
+        <v/>
       </c>
       <c r="R219" s="17"/>
     </row>
@@ -9331,13 +9331,13 @@
         <f aca="false">IFERROR(N220/H220,"")</f>
         <v/>
       </c>
-      <c r="P220" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A220,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q220" s="15" t="n">
-        <f aca="false">IFERROR(H220-P220,"")</f>
-        <v>0</v>
+      <c r="P220" s="15" t="str">
+        <f aca="false">IF($A220="","",IF(COUNTIF($A$3:$A220,$A220)=1,SUMIF(cobranza!$B$3:$B$1000,$A220,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q220" s="15" t="str">
+        <f aca="false">IF($A220="","",IF(COUNTIF($A$3:$A220,$A220)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A220,$C$3:$C$1000,"&lt;&gt;Demo")-P220,"↑"))</f>
+        <v/>
       </c>
       <c r="R220" s="17"/>
     </row>
@@ -9363,13 +9363,13 @@
         <f aca="false">IFERROR(N221/H221,"")</f>
         <v/>
       </c>
-      <c r="P221" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A221,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q221" s="15" t="n">
-        <f aca="false">IFERROR(H221-P221,"")</f>
-        <v>0</v>
+      <c r="P221" s="15" t="str">
+        <f aca="false">IF($A221="","",IF(COUNTIF($A$3:$A221,$A221)=1,SUMIF(cobranza!$B$3:$B$1000,$A221,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q221" s="15" t="str">
+        <f aca="false">IF($A221="","",IF(COUNTIF($A$3:$A221,$A221)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A221,$C$3:$C$1000,"&lt;&gt;Demo")-P221,"↑"))</f>
+        <v/>
       </c>
       <c r="R221" s="17"/>
     </row>
@@ -9395,13 +9395,13 @@
         <f aca="false">IFERROR(N222/H222,"")</f>
         <v/>
       </c>
-      <c r="P222" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A222,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q222" s="15" t="n">
-        <f aca="false">IFERROR(H222-P222,"")</f>
-        <v>0</v>
+      <c r="P222" s="15" t="str">
+        <f aca="false">IF($A222="","",IF(COUNTIF($A$3:$A222,$A222)=1,SUMIF(cobranza!$B$3:$B$1000,$A222,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q222" s="15" t="str">
+        <f aca="false">IF($A222="","",IF(COUNTIF($A$3:$A222,$A222)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A222,$C$3:$C$1000,"&lt;&gt;Demo")-P222,"↑"))</f>
+        <v/>
       </c>
       <c r="R222" s="17"/>
     </row>
@@ -9427,13 +9427,13 @@
         <f aca="false">IFERROR(N223/H223,"")</f>
         <v/>
       </c>
-      <c r="P223" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A223,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q223" s="15" t="n">
-        <f aca="false">IFERROR(H223-P223,"")</f>
-        <v>0</v>
+      <c r="P223" s="15" t="str">
+        <f aca="false">IF($A223="","",IF(COUNTIF($A$3:$A223,$A223)=1,SUMIF(cobranza!$B$3:$B$1000,$A223,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q223" s="15" t="str">
+        <f aca="false">IF($A223="","",IF(COUNTIF($A$3:$A223,$A223)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A223,$C$3:$C$1000,"&lt;&gt;Demo")-P223,"↑"))</f>
+        <v/>
       </c>
       <c r="R223" s="17"/>
     </row>
@@ -9459,13 +9459,13 @@
         <f aca="false">IFERROR(N224/H224,"")</f>
         <v/>
       </c>
-      <c r="P224" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A224,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q224" s="15" t="n">
-        <f aca="false">IFERROR(H224-P224,"")</f>
-        <v>0</v>
+      <c r="P224" s="15" t="str">
+        <f aca="false">IF($A224="","",IF(COUNTIF($A$3:$A224,$A224)=1,SUMIF(cobranza!$B$3:$B$1000,$A224,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q224" s="15" t="str">
+        <f aca="false">IF($A224="","",IF(COUNTIF($A$3:$A224,$A224)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A224,$C$3:$C$1000,"&lt;&gt;Demo")-P224,"↑"))</f>
+        <v/>
       </c>
       <c r="R224" s="17"/>
     </row>
@@ -9491,13 +9491,13 @@
         <f aca="false">IFERROR(N225/H225,"")</f>
         <v/>
       </c>
-      <c r="P225" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A225,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q225" s="15" t="n">
-        <f aca="false">IFERROR(H225-P225,"")</f>
-        <v>0</v>
+      <c r="P225" s="15" t="str">
+        <f aca="false">IF($A225="","",IF(COUNTIF($A$3:$A225,$A225)=1,SUMIF(cobranza!$B$3:$B$1000,$A225,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q225" s="15" t="str">
+        <f aca="false">IF($A225="","",IF(COUNTIF($A$3:$A225,$A225)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A225,$C$3:$C$1000,"&lt;&gt;Demo")-P225,"↑"))</f>
+        <v/>
       </c>
       <c r="R225" s="17"/>
     </row>
@@ -9523,13 +9523,13 @@
         <f aca="false">IFERROR(N226/H226,"")</f>
         <v/>
       </c>
-      <c r="P226" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A226,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q226" s="15" t="n">
-        <f aca="false">IFERROR(H226-P226,"")</f>
-        <v>0</v>
+      <c r="P226" s="15" t="str">
+        <f aca="false">IF($A226="","",IF(COUNTIF($A$3:$A226,$A226)=1,SUMIF(cobranza!$B$3:$B$1000,$A226,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q226" s="15" t="str">
+        <f aca="false">IF($A226="","",IF(COUNTIF($A$3:$A226,$A226)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A226,$C$3:$C$1000,"&lt;&gt;Demo")-P226,"↑"))</f>
+        <v/>
       </c>
       <c r="R226" s="17"/>
     </row>
@@ -9555,13 +9555,13 @@
         <f aca="false">IFERROR(N227/H227,"")</f>
         <v/>
       </c>
-      <c r="P227" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A227,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q227" s="15" t="n">
-        <f aca="false">IFERROR(H227-P227,"")</f>
-        <v>0</v>
+      <c r="P227" s="15" t="str">
+        <f aca="false">IF($A227="","",IF(COUNTIF($A$3:$A227,$A227)=1,SUMIF(cobranza!$B$3:$B$1000,$A227,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q227" s="15" t="str">
+        <f aca="false">IF($A227="","",IF(COUNTIF($A$3:$A227,$A227)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A227,$C$3:$C$1000,"&lt;&gt;Demo")-P227,"↑"))</f>
+        <v/>
       </c>
       <c r="R227" s="17"/>
     </row>
@@ -9587,13 +9587,13 @@
         <f aca="false">IFERROR(N228/H228,"")</f>
         <v/>
       </c>
-      <c r="P228" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A228,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q228" s="15" t="n">
-        <f aca="false">IFERROR(H228-P228,"")</f>
-        <v>0</v>
+      <c r="P228" s="15" t="str">
+        <f aca="false">IF($A228="","",IF(COUNTIF($A$3:$A228,$A228)=1,SUMIF(cobranza!$B$3:$B$1000,$A228,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q228" s="15" t="str">
+        <f aca="false">IF($A228="","",IF(COUNTIF($A$3:$A228,$A228)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A228,$C$3:$C$1000,"&lt;&gt;Demo")-P228,"↑"))</f>
+        <v/>
       </c>
       <c r="R228" s="17"/>
     </row>
@@ -9619,13 +9619,13 @@
         <f aca="false">IFERROR(N229/H229,"")</f>
         <v/>
       </c>
-      <c r="P229" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A229,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q229" s="15" t="n">
-        <f aca="false">IFERROR(H229-P229,"")</f>
-        <v>0</v>
+      <c r="P229" s="15" t="str">
+        <f aca="false">IF($A229="","",IF(COUNTIF($A$3:$A229,$A229)=1,SUMIF(cobranza!$B$3:$B$1000,$A229,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q229" s="15" t="str">
+        <f aca="false">IF($A229="","",IF(COUNTIF($A$3:$A229,$A229)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A229,$C$3:$C$1000,"&lt;&gt;Demo")-P229,"↑"))</f>
+        <v/>
       </c>
       <c r="R229" s="17"/>
     </row>
@@ -9651,13 +9651,13 @@
         <f aca="false">IFERROR(N230/H230,"")</f>
         <v/>
       </c>
-      <c r="P230" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A230,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q230" s="15" t="n">
-        <f aca="false">IFERROR(H230-P230,"")</f>
-        <v>0</v>
+      <c r="P230" s="15" t="str">
+        <f aca="false">IF($A230="","",IF(COUNTIF($A$3:$A230,$A230)=1,SUMIF(cobranza!$B$3:$B$1000,$A230,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q230" s="15" t="str">
+        <f aca="false">IF($A230="","",IF(COUNTIF($A$3:$A230,$A230)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A230,$C$3:$C$1000,"&lt;&gt;Demo")-P230,"↑"))</f>
+        <v/>
       </c>
       <c r="R230" s="17"/>
     </row>
@@ -9683,13 +9683,13 @@
         <f aca="false">IFERROR(N231/H231,"")</f>
         <v/>
       </c>
-      <c r="P231" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A231,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q231" s="15" t="n">
-        <f aca="false">IFERROR(H231-P231,"")</f>
-        <v>0</v>
+      <c r="P231" s="15" t="str">
+        <f aca="false">IF($A231="","",IF(COUNTIF($A$3:$A231,$A231)=1,SUMIF(cobranza!$B$3:$B$1000,$A231,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q231" s="15" t="str">
+        <f aca="false">IF($A231="","",IF(COUNTIF($A$3:$A231,$A231)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A231,$C$3:$C$1000,"&lt;&gt;Demo")-P231,"↑"))</f>
+        <v/>
       </c>
       <c r="R231" s="17"/>
     </row>
@@ -9715,13 +9715,13 @@
         <f aca="false">IFERROR(N232/H232,"")</f>
         <v/>
       </c>
-      <c r="P232" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A232,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q232" s="15" t="n">
-        <f aca="false">IFERROR(H232-P232,"")</f>
-        <v>0</v>
+      <c r="P232" s="15" t="str">
+        <f aca="false">IF($A232="","",IF(COUNTIF($A$3:$A232,$A232)=1,SUMIF(cobranza!$B$3:$B$1000,$A232,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q232" s="15" t="str">
+        <f aca="false">IF($A232="","",IF(COUNTIF($A$3:$A232,$A232)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A232,$C$3:$C$1000,"&lt;&gt;Demo")-P232,"↑"))</f>
+        <v/>
       </c>
       <c r="R232" s="17"/>
     </row>
@@ -9747,13 +9747,13 @@
         <f aca="false">IFERROR(N233/H233,"")</f>
         <v/>
       </c>
-      <c r="P233" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A233,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q233" s="15" t="n">
-        <f aca="false">IFERROR(H233-P233,"")</f>
-        <v>0</v>
+      <c r="P233" s="15" t="str">
+        <f aca="false">IF($A233="","",IF(COUNTIF($A$3:$A233,$A233)=1,SUMIF(cobranza!$B$3:$B$1000,$A233,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q233" s="15" t="str">
+        <f aca="false">IF($A233="","",IF(COUNTIF($A$3:$A233,$A233)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A233,$C$3:$C$1000,"&lt;&gt;Demo")-P233,"↑"))</f>
+        <v/>
       </c>
       <c r="R233" s="17"/>
     </row>
@@ -9779,13 +9779,13 @@
         <f aca="false">IFERROR(N234/H234,"")</f>
         <v/>
       </c>
-      <c r="P234" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A234,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q234" s="15" t="n">
-        <f aca="false">IFERROR(H234-P234,"")</f>
-        <v>0</v>
+      <c r="P234" s="15" t="str">
+        <f aca="false">IF($A234="","",IF(COUNTIF($A$3:$A234,$A234)=1,SUMIF(cobranza!$B$3:$B$1000,$A234,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q234" s="15" t="str">
+        <f aca="false">IF($A234="","",IF(COUNTIF($A$3:$A234,$A234)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A234,$C$3:$C$1000,"&lt;&gt;Demo")-P234,"↑"))</f>
+        <v/>
       </c>
       <c r="R234" s="17"/>
     </row>
@@ -9811,13 +9811,13 @@
         <f aca="false">IFERROR(N235/H235,"")</f>
         <v/>
       </c>
-      <c r="P235" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A235,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q235" s="15" t="n">
-        <f aca="false">IFERROR(H235-P235,"")</f>
-        <v>0</v>
+      <c r="P235" s="15" t="str">
+        <f aca="false">IF($A235="","",IF(COUNTIF($A$3:$A235,$A235)=1,SUMIF(cobranza!$B$3:$B$1000,$A235,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q235" s="15" t="str">
+        <f aca="false">IF($A235="","",IF(COUNTIF($A$3:$A235,$A235)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A235,$C$3:$C$1000,"&lt;&gt;Demo")-P235,"↑"))</f>
+        <v/>
       </c>
       <c r="R235" s="17"/>
     </row>
@@ -9843,13 +9843,13 @@
         <f aca="false">IFERROR(N236/H236,"")</f>
         <v/>
       </c>
-      <c r="P236" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A236,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q236" s="15" t="n">
-        <f aca="false">IFERROR(H236-P236,"")</f>
-        <v>0</v>
+      <c r="P236" s="15" t="str">
+        <f aca="false">IF($A236="","",IF(COUNTIF($A$3:$A236,$A236)=1,SUMIF(cobranza!$B$3:$B$1000,$A236,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q236" s="15" t="str">
+        <f aca="false">IF($A236="","",IF(COUNTIF($A$3:$A236,$A236)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A236,$C$3:$C$1000,"&lt;&gt;Demo")-P236,"↑"))</f>
+        <v/>
       </c>
       <c r="R236" s="17"/>
     </row>
@@ -9875,13 +9875,13 @@
         <f aca="false">IFERROR(N237/H237,"")</f>
         <v/>
       </c>
-      <c r="P237" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A237,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q237" s="15" t="n">
-        <f aca="false">IFERROR(H237-P237,"")</f>
-        <v>0</v>
+      <c r="P237" s="15" t="str">
+        <f aca="false">IF($A237="","",IF(COUNTIF($A$3:$A237,$A237)=1,SUMIF(cobranza!$B$3:$B$1000,$A237,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q237" s="15" t="str">
+        <f aca="false">IF($A237="","",IF(COUNTIF($A$3:$A237,$A237)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A237,$C$3:$C$1000,"&lt;&gt;Demo")-P237,"↑"))</f>
+        <v/>
       </c>
       <c r="R237" s="17"/>
     </row>
@@ -9907,13 +9907,13 @@
         <f aca="false">IFERROR(N238/H238,"")</f>
         <v/>
       </c>
-      <c r="P238" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A238,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q238" s="15" t="n">
-        <f aca="false">IFERROR(H238-P238,"")</f>
-        <v>0</v>
+      <c r="P238" s="15" t="str">
+        <f aca="false">IF($A238="","",IF(COUNTIF($A$3:$A238,$A238)=1,SUMIF(cobranza!$B$3:$B$1000,$A238,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q238" s="15" t="str">
+        <f aca="false">IF($A238="","",IF(COUNTIF($A$3:$A238,$A238)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A238,$C$3:$C$1000,"&lt;&gt;Demo")-P238,"↑"))</f>
+        <v/>
       </c>
       <c r="R238" s="17"/>
     </row>
@@ -9939,13 +9939,13 @@
         <f aca="false">IFERROR(N239/H239,"")</f>
         <v/>
       </c>
-      <c r="P239" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A239,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q239" s="15" t="n">
-        <f aca="false">IFERROR(H239-P239,"")</f>
-        <v>0</v>
+      <c r="P239" s="15" t="str">
+        <f aca="false">IF($A239="","",IF(COUNTIF($A$3:$A239,$A239)=1,SUMIF(cobranza!$B$3:$B$1000,$A239,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q239" s="15" t="str">
+        <f aca="false">IF($A239="","",IF(COUNTIF($A$3:$A239,$A239)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A239,$C$3:$C$1000,"&lt;&gt;Demo")-P239,"↑"))</f>
+        <v/>
       </c>
       <c r="R239" s="17"/>
     </row>
@@ -9971,13 +9971,13 @@
         <f aca="false">IFERROR(N240/H240,"")</f>
         <v/>
       </c>
-      <c r="P240" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A240,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q240" s="15" t="n">
-        <f aca="false">IFERROR(H240-P240,"")</f>
-        <v>0</v>
+      <c r="P240" s="15" t="str">
+        <f aca="false">IF($A240="","",IF(COUNTIF($A$3:$A240,$A240)=1,SUMIF(cobranza!$B$3:$B$1000,$A240,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q240" s="15" t="str">
+        <f aca="false">IF($A240="","",IF(COUNTIF($A$3:$A240,$A240)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A240,$C$3:$C$1000,"&lt;&gt;Demo")-P240,"↑"))</f>
+        <v/>
       </c>
       <c r="R240" s="17"/>
     </row>
@@ -10003,13 +10003,13 @@
         <f aca="false">IFERROR(N241/H241,"")</f>
         <v/>
       </c>
-      <c r="P241" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A241,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q241" s="15" t="n">
-        <f aca="false">IFERROR(H241-P241,"")</f>
-        <v>0</v>
+      <c r="P241" s="15" t="str">
+        <f aca="false">IF($A241="","",IF(COUNTIF($A$3:$A241,$A241)=1,SUMIF(cobranza!$B$3:$B$1000,$A241,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q241" s="15" t="str">
+        <f aca="false">IF($A241="","",IF(COUNTIF($A$3:$A241,$A241)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A241,$C$3:$C$1000,"&lt;&gt;Demo")-P241,"↑"))</f>
+        <v/>
       </c>
       <c r="R241" s="17"/>
     </row>
@@ -10035,13 +10035,13 @@
         <f aca="false">IFERROR(N242/H242,"")</f>
         <v/>
       </c>
-      <c r="P242" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A242,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q242" s="15" t="n">
-        <f aca="false">IFERROR(H242-P242,"")</f>
-        <v>0</v>
+      <c r="P242" s="15" t="str">
+        <f aca="false">IF($A242="","",IF(COUNTIF($A$3:$A242,$A242)=1,SUMIF(cobranza!$B$3:$B$1000,$A242,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q242" s="15" t="str">
+        <f aca="false">IF($A242="","",IF(COUNTIF($A$3:$A242,$A242)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A242,$C$3:$C$1000,"&lt;&gt;Demo")-P242,"↑"))</f>
+        <v/>
       </c>
       <c r="R242" s="17"/>
     </row>
@@ -10067,13 +10067,13 @@
         <f aca="false">IFERROR(N243/H243,"")</f>
         <v/>
       </c>
-      <c r="P243" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A243,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q243" s="15" t="n">
-        <f aca="false">IFERROR(H243-P243,"")</f>
-        <v>0</v>
+      <c r="P243" s="15" t="str">
+        <f aca="false">IF($A243="","",IF(COUNTIF($A$3:$A243,$A243)=1,SUMIF(cobranza!$B$3:$B$1000,$A243,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q243" s="15" t="str">
+        <f aca="false">IF($A243="","",IF(COUNTIF($A$3:$A243,$A243)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A243,$C$3:$C$1000,"&lt;&gt;Demo")-P243,"↑"))</f>
+        <v/>
       </c>
       <c r="R243" s="17"/>
     </row>
@@ -10099,13 +10099,13 @@
         <f aca="false">IFERROR(N244/H244,"")</f>
         <v/>
       </c>
-      <c r="P244" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A244,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q244" s="15" t="n">
-        <f aca="false">IFERROR(H244-P244,"")</f>
-        <v>0</v>
+      <c r="P244" s="15" t="str">
+        <f aca="false">IF($A244="","",IF(COUNTIF($A$3:$A244,$A244)=1,SUMIF(cobranza!$B$3:$B$1000,$A244,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q244" s="15" t="str">
+        <f aca="false">IF($A244="","",IF(COUNTIF($A$3:$A244,$A244)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A244,$C$3:$C$1000,"&lt;&gt;Demo")-P244,"↑"))</f>
+        <v/>
       </c>
       <c r="R244" s="17"/>
     </row>
@@ -10131,13 +10131,13 @@
         <f aca="false">IFERROR(N245/H245,"")</f>
         <v/>
       </c>
-      <c r="P245" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A245,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q245" s="15" t="n">
-        <f aca="false">IFERROR(H245-P245,"")</f>
-        <v>0</v>
+      <c r="P245" s="15" t="str">
+        <f aca="false">IF($A245="","",IF(COUNTIF($A$3:$A245,$A245)=1,SUMIF(cobranza!$B$3:$B$1000,$A245,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q245" s="15" t="str">
+        <f aca="false">IF($A245="","",IF(COUNTIF($A$3:$A245,$A245)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A245,$C$3:$C$1000,"&lt;&gt;Demo")-P245,"↑"))</f>
+        <v/>
       </c>
       <c r="R245" s="17"/>
     </row>
@@ -10163,13 +10163,13 @@
         <f aca="false">IFERROR(N246/H246,"")</f>
         <v/>
       </c>
-      <c r="P246" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A246,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q246" s="15" t="n">
-        <f aca="false">IFERROR(H246-P246,"")</f>
-        <v>0</v>
+      <c r="P246" s="15" t="str">
+        <f aca="false">IF($A246="","",IF(COUNTIF($A$3:$A246,$A246)=1,SUMIF(cobranza!$B$3:$B$1000,$A246,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q246" s="15" t="str">
+        <f aca="false">IF($A246="","",IF(COUNTIF($A$3:$A246,$A246)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A246,$C$3:$C$1000,"&lt;&gt;Demo")-P246,"↑"))</f>
+        <v/>
       </c>
       <c r="R246" s="17"/>
     </row>
@@ -10195,13 +10195,13 @@
         <f aca="false">IFERROR(N247/H247,"")</f>
         <v/>
       </c>
-      <c r="P247" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A247,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q247" s="15" t="n">
-        <f aca="false">IFERROR(H247-P247,"")</f>
-        <v>0</v>
+      <c r="P247" s="15" t="str">
+        <f aca="false">IF($A247="","",IF(COUNTIF($A$3:$A247,$A247)=1,SUMIF(cobranza!$B$3:$B$1000,$A247,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q247" s="15" t="str">
+        <f aca="false">IF($A247="","",IF(COUNTIF($A$3:$A247,$A247)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A247,$C$3:$C$1000,"&lt;&gt;Demo")-P247,"↑"))</f>
+        <v/>
       </c>
       <c r="R247" s="17"/>
     </row>
@@ -10227,13 +10227,13 @@
         <f aca="false">IFERROR(N248/H248,"")</f>
         <v/>
       </c>
-      <c r="P248" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A248,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q248" s="15" t="n">
-        <f aca="false">IFERROR(H248-P248,"")</f>
-        <v>0</v>
+      <c r="P248" s="15" t="str">
+        <f aca="false">IF($A248="","",IF(COUNTIF($A$3:$A248,$A248)=1,SUMIF(cobranza!$B$3:$B$1000,$A248,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q248" s="15" t="str">
+        <f aca="false">IF($A248="","",IF(COUNTIF($A$3:$A248,$A248)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A248,$C$3:$C$1000,"&lt;&gt;Demo")-P248,"↑"))</f>
+        <v/>
       </c>
       <c r="R248" s="17"/>
     </row>
@@ -10259,13 +10259,13 @@
         <f aca="false">IFERROR(N249/H249,"")</f>
         <v/>
       </c>
-      <c r="P249" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A249,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q249" s="15" t="n">
-        <f aca="false">IFERROR(H249-P249,"")</f>
-        <v>0</v>
+      <c r="P249" s="15" t="str">
+        <f aca="false">IF($A249="","",IF(COUNTIF($A$3:$A249,$A249)=1,SUMIF(cobranza!$B$3:$B$1000,$A249,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q249" s="15" t="str">
+        <f aca="false">IF($A249="","",IF(COUNTIF($A$3:$A249,$A249)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A249,$C$3:$C$1000,"&lt;&gt;Demo")-P249,"↑"))</f>
+        <v/>
       </c>
       <c r="R249" s="17"/>
     </row>
@@ -10291,13 +10291,13 @@
         <f aca="false">IFERROR(N250/H250,"")</f>
         <v/>
       </c>
-      <c r="P250" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A250,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q250" s="15" t="n">
-        <f aca="false">IFERROR(H250-P250,"")</f>
-        <v>0</v>
+      <c r="P250" s="15" t="str">
+        <f aca="false">IF($A250="","",IF(COUNTIF($A$3:$A250,$A250)=1,SUMIF(cobranza!$B$3:$B$1000,$A250,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q250" s="15" t="str">
+        <f aca="false">IF($A250="","",IF(COUNTIF($A$3:$A250,$A250)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A250,$C$3:$C$1000,"&lt;&gt;Demo")-P250,"↑"))</f>
+        <v/>
       </c>
       <c r="R250" s="17"/>
     </row>
@@ -10323,13 +10323,13 @@
         <f aca="false">IFERROR(N251/H251,"")</f>
         <v/>
       </c>
-      <c r="P251" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A251,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q251" s="15" t="n">
-        <f aca="false">IFERROR(H251-P251,"")</f>
-        <v>0</v>
+      <c r="P251" s="15" t="str">
+        <f aca="false">IF($A251="","",IF(COUNTIF($A$3:$A251,$A251)=1,SUMIF(cobranza!$B$3:$B$1000,$A251,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q251" s="15" t="str">
+        <f aca="false">IF($A251="","",IF(COUNTIF($A$3:$A251,$A251)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A251,$C$3:$C$1000,"&lt;&gt;Demo")-P251,"↑"))</f>
+        <v/>
       </c>
       <c r="R251" s="17"/>
     </row>
@@ -10355,13 +10355,13 @@
         <f aca="false">IFERROR(N252/H252,"")</f>
         <v/>
       </c>
-      <c r="P252" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A252,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q252" s="15" t="n">
-        <f aca="false">IFERROR(H252-P252,"")</f>
-        <v>0</v>
+      <c r="P252" s="15" t="str">
+        <f aca="false">IF($A252="","",IF(COUNTIF($A$3:$A252,$A252)=1,SUMIF(cobranza!$B$3:$B$1000,$A252,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q252" s="15" t="str">
+        <f aca="false">IF($A252="","",IF(COUNTIF($A$3:$A252,$A252)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A252,$C$3:$C$1000,"&lt;&gt;Demo")-P252,"↑"))</f>
+        <v/>
       </c>
       <c r="R252" s="17"/>
     </row>
@@ -10387,13 +10387,13 @@
         <f aca="false">IFERROR(N253/H253,"")</f>
         <v/>
       </c>
-      <c r="P253" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A253,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q253" s="15" t="n">
-        <f aca="false">IFERROR(H253-P253,"")</f>
-        <v>0</v>
+      <c r="P253" s="15" t="str">
+        <f aca="false">IF($A253="","",IF(COUNTIF($A$3:$A253,$A253)=1,SUMIF(cobranza!$B$3:$B$1000,$A253,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q253" s="15" t="str">
+        <f aca="false">IF($A253="","",IF(COUNTIF($A$3:$A253,$A253)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A253,$C$3:$C$1000,"&lt;&gt;Demo")-P253,"↑"))</f>
+        <v/>
       </c>
       <c r="R253" s="17"/>
     </row>
@@ -10419,13 +10419,13 @@
         <f aca="false">IFERROR(N254/H254,"")</f>
         <v/>
       </c>
-      <c r="P254" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A254,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q254" s="15" t="n">
-        <f aca="false">IFERROR(H254-P254,"")</f>
-        <v>0</v>
+      <c r="P254" s="15" t="str">
+        <f aca="false">IF($A254="","",IF(COUNTIF($A$3:$A254,$A254)=1,SUMIF(cobranza!$B$3:$B$1000,$A254,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q254" s="15" t="str">
+        <f aca="false">IF($A254="","",IF(COUNTIF($A$3:$A254,$A254)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A254,$C$3:$C$1000,"&lt;&gt;Demo")-P254,"↑"))</f>
+        <v/>
       </c>
       <c r="R254" s="17"/>
     </row>
@@ -10451,13 +10451,13 @@
         <f aca="false">IFERROR(N255/H255,"")</f>
         <v/>
       </c>
-      <c r="P255" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A255,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q255" s="15" t="n">
-        <f aca="false">IFERROR(H255-P255,"")</f>
-        <v>0</v>
+      <c r="P255" s="15" t="str">
+        <f aca="false">IF($A255="","",IF(COUNTIF($A$3:$A255,$A255)=1,SUMIF(cobranza!$B$3:$B$1000,$A255,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q255" s="15" t="str">
+        <f aca="false">IF($A255="","",IF(COUNTIF($A$3:$A255,$A255)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A255,$C$3:$C$1000,"&lt;&gt;Demo")-P255,"↑"))</f>
+        <v/>
       </c>
       <c r="R255" s="17"/>
     </row>
@@ -10483,13 +10483,13 @@
         <f aca="false">IFERROR(N256/H256,"")</f>
         <v/>
       </c>
-      <c r="P256" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A256,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q256" s="15" t="n">
-        <f aca="false">IFERROR(H256-P256,"")</f>
-        <v>0</v>
+      <c r="P256" s="15" t="str">
+        <f aca="false">IF($A256="","",IF(COUNTIF($A$3:$A256,$A256)=1,SUMIF(cobranza!$B$3:$B$1000,$A256,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q256" s="15" t="str">
+        <f aca="false">IF($A256="","",IF(COUNTIF($A$3:$A256,$A256)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A256,$C$3:$C$1000,"&lt;&gt;Demo")-P256,"↑"))</f>
+        <v/>
       </c>
       <c r="R256" s="17"/>
     </row>
@@ -10515,13 +10515,13 @@
         <f aca="false">IFERROR(N257/H257,"")</f>
         <v/>
       </c>
-      <c r="P257" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A257,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q257" s="15" t="n">
-        <f aca="false">IFERROR(H257-P257,"")</f>
-        <v>0</v>
+      <c r="P257" s="15" t="str">
+        <f aca="false">IF($A257="","",IF(COUNTIF($A$3:$A257,$A257)=1,SUMIF(cobranza!$B$3:$B$1000,$A257,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q257" s="15" t="str">
+        <f aca="false">IF($A257="","",IF(COUNTIF($A$3:$A257,$A257)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A257,$C$3:$C$1000,"&lt;&gt;Demo")-P257,"↑"))</f>
+        <v/>
       </c>
       <c r="R257" s="17"/>
     </row>
@@ -10547,13 +10547,13 @@
         <f aca="false">IFERROR(N258/H258,"")</f>
         <v/>
       </c>
-      <c r="P258" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A258,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q258" s="15" t="n">
-        <f aca="false">IFERROR(H258-P258,"")</f>
-        <v>0</v>
+      <c r="P258" s="15" t="str">
+        <f aca="false">IF($A258="","",IF(COUNTIF($A$3:$A258,$A258)=1,SUMIF(cobranza!$B$3:$B$1000,$A258,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q258" s="15" t="str">
+        <f aca="false">IF($A258="","",IF(COUNTIF($A$3:$A258,$A258)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A258,$C$3:$C$1000,"&lt;&gt;Demo")-P258,"↑"))</f>
+        <v/>
       </c>
       <c r="R258" s="17"/>
     </row>
@@ -10579,13 +10579,13 @@
         <f aca="false">IFERROR(N259/H259,"")</f>
         <v/>
       </c>
-      <c r="P259" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A259,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q259" s="15" t="n">
-        <f aca="false">IFERROR(H259-P259,"")</f>
-        <v>0</v>
+      <c r="P259" s="15" t="str">
+        <f aca="false">IF($A259="","",IF(COUNTIF($A$3:$A259,$A259)=1,SUMIF(cobranza!$B$3:$B$1000,$A259,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q259" s="15" t="str">
+        <f aca="false">IF($A259="","",IF(COUNTIF($A$3:$A259,$A259)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A259,$C$3:$C$1000,"&lt;&gt;Demo")-P259,"↑"))</f>
+        <v/>
       </c>
       <c r="R259" s="17"/>
     </row>
@@ -10611,13 +10611,13 @@
         <f aca="false">IFERROR(N260/H260,"")</f>
         <v/>
       </c>
-      <c r="P260" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A260,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q260" s="15" t="n">
-        <f aca="false">IFERROR(H260-P260,"")</f>
-        <v>0</v>
+      <c r="P260" s="15" t="str">
+        <f aca="false">IF($A260="","",IF(COUNTIF($A$3:$A260,$A260)=1,SUMIF(cobranza!$B$3:$B$1000,$A260,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q260" s="15" t="str">
+        <f aca="false">IF($A260="","",IF(COUNTIF($A$3:$A260,$A260)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A260,$C$3:$C$1000,"&lt;&gt;Demo")-P260,"↑"))</f>
+        <v/>
       </c>
       <c r="R260" s="17"/>
     </row>
@@ -10643,13 +10643,13 @@
         <f aca="false">IFERROR(N261/H261,"")</f>
         <v/>
       </c>
-      <c r="P261" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A261,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q261" s="15" t="n">
-        <f aca="false">IFERROR(H261-P261,"")</f>
-        <v>0</v>
+      <c r="P261" s="15" t="str">
+        <f aca="false">IF($A261="","",IF(COUNTIF($A$3:$A261,$A261)=1,SUMIF(cobranza!$B$3:$B$1000,$A261,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q261" s="15" t="str">
+        <f aca="false">IF($A261="","",IF(COUNTIF($A$3:$A261,$A261)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A261,$C$3:$C$1000,"&lt;&gt;Demo")-P261,"↑"))</f>
+        <v/>
       </c>
       <c r="R261" s="17"/>
     </row>
@@ -10675,13 +10675,13 @@
         <f aca="false">IFERROR(N262/H262,"")</f>
         <v/>
       </c>
-      <c r="P262" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A262,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q262" s="15" t="n">
-        <f aca="false">IFERROR(H262-P262,"")</f>
-        <v>0</v>
+      <c r="P262" s="15" t="str">
+        <f aca="false">IF($A262="","",IF(COUNTIF($A$3:$A262,$A262)=1,SUMIF(cobranza!$B$3:$B$1000,$A262,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q262" s="15" t="str">
+        <f aca="false">IF($A262="","",IF(COUNTIF($A$3:$A262,$A262)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A262,$C$3:$C$1000,"&lt;&gt;Demo")-P262,"↑"))</f>
+        <v/>
       </c>
       <c r="R262" s="17"/>
     </row>
@@ -10707,13 +10707,13 @@
         <f aca="false">IFERROR(N263/H263,"")</f>
         <v/>
       </c>
-      <c r="P263" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A263,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q263" s="15" t="n">
-        <f aca="false">IFERROR(H263-P263,"")</f>
-        <v>0</v>
+      <c r="P263" s="15" t="str">
+        <f aca="false">IF($A263="","",IF(COUNTIF($A$3:$A263,$A263)=1,SUMIF(cobranza!$B$3:$B$1000,$A263,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q263" s="15" t="str">
+        <f aca="false">IF($A263="","",IF(COUNTIF($A$3:$A263,$A263)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A263,$C$3:$C$1000,"&lt;&gt;Demo")-P263,"↑"))</f>
+        <v/>
       </c>
       <c r="R263" s="17"/>
     </row>
@@ -10739,13 +10739,13 @@
         <f aca="false">IFERROR(N264/H264,"")</f>
         <v/>
       </c>
-      <c r="P264" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A264,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q264" s="15" t="n">
-        <f aca="false">IFERROR(H264-P264,"")</f>
-        <v>0</v>
+      <c r="P264" s="15" t="str">
+        <f aca="false">IF($A264="","",IF(COUNTIF($A$3:$A264,$A264)=1,SUMIF(cobranza!$B$3:$B$1000,$A264,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q264" s="15" t="str">
+        <f aca="false">IF($A264="","",IF(COUNTIF($A$3:$A264,$A264)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A264,$C$3:$C$1000,"&lt;&gt;Demo")-P264,"↑"))</f>
+        <v/>
       </c>
       <c r="R264" s="17"/>
     </row>
@@ -10771,13 +10771,13 @@
         <f aca="false">IFERROR(N265/H265,"")</f>
         <v/>
       </c>
-      <c r="P265" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A265,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q265" s="15" t="n">
-        <f aca="false">IFERROR(H265-P265,"")</f>
-        <v>0</v>
+      <c r="P265" s="15" t="str">
+        <f aca="false">IF($A265="","",IF(COUNTIF($A$3:$A265,$A265)=1,SUMIF(cobranza!$B$3:$B$1000,$A265,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q265" s="15" t="str">
+        <f aca="false">IF($A265="","",IF(COUNTIF($A$3:$A265,$A265)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A265,$C$3:$C$1000,"&lt;&gt;Demo")-P265,"↑"))</f>
+        <v/>
       </c>
       <c r="R265" s="17"/>
     </row>
@@ -10803,13 +10803,13 @@
         <f aca="false">IFERROR(N266/H266,"")</f>
         <v/>
       </c>
-      <c r="P266" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A266,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q266" s="15" t="n">
-        <f aca="false">IFERROR(H266-P266,"")</f>
-        <v>0</v>
+      <c r="P266" s="15" t="str">
+        <f aca="false">IF($A266="","",IF(COUNTIF($A$3:$A266,$A266)=1,SUMIF(cobranza!$B$3:$B$1000,$A266,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q266" s="15" t="str">
+        <f aca="false">IF($A266="","",IF(COUNTIF($A$3:$A266,$A266)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A266,$C$3:$C$1000,"&lt;&gt;Demo")-P266,"↑"))</f>
+        <v/>
       </c>
       <c r="R266" s="17"/>
     </row>
@@ -10835,13 +10835,13 @@
         <f aca="false">IFERROR(N267/H267,"")</f>
         <v/>
       </c>
-      <c r="P267" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A267,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q267" s="15" t="n">
-        <f aca="false">IFERROR(H267-P267,"")</f>
-        <v>0</v>
+      <c r="P267" s="15" t="str">
+        <f aca="false">IF($A267="","",IF(COUNTIF($A$3:$A267,$A267)=1,SUMIF(cobranza!$B$3:$B$1000,$A267,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q267" s="15" t="str">
+        <f aca="false">IF($A267="","",IF(COUNTIF($A$3:$A267,$A267)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A267,$C$3:$C$1000,"&lt;&gt;Demo")-P267,"↑"))</f>
+        <v/>
       </c>
       <c r="R267" s="17"/>
     </row>
@@ -10867,13 +10867,13 @@
         <f aca="false">IFERROR(N268/H268,"")</f>
         <v/>
       </c>
-      <c r="P268" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A268,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q268" s="15" t="n">
-        <f aca="false">IFERROR(H268-P268,"")</f>
-        <v>0</v>
+      <c r="P268" s="15" t="str">
+        <f aca="false">IF($A268="","",IF(COUNTIF($A$3:$A268,$A268)=1,SUMIF(cobranza!$B$3:$B$1000,$A268,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q268" s="15" t="str">
+        <f aca="false">IF($A268="","",IF(COUNTIF($A$3:$A268,$A268)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A268,$C$3:$C$1000,"&lt;&gt;Demo")-P268,"↑"))</f>
+        <v/>
       </c>
       <c r="R268" s="17"/>
     </row>
@@ -10899,13 +10899,13 @@
         <f aca="false">IFERROR(N269/H269,"")</f>
         <v/>
       </c>
-      <c r="P269" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A269,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q269" s="15" t="n">
-        <f aca="false">IFERROR(H269-P269,"")</f>
-        <v>0</v>
+      <c r="P269" s="15" t="str">
+        <f aca="false">IF($A269="","",IF(COUNTIF($A$3:$A269,$A269)=1,SUMIF(cobranza!$B$3:$B$1000,$A269,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q269" s="15" t="str">
+        <f aca="false">IF($A269="","",IF(COUNTIF($A$3:$A269,$A269)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A269,$C$3:$C$1000,"&lt;&gt;Demo")-P269,"↑"))</f>
+        <v/>
       </c>
       <c r="R269" s="17"/>
     </row>
@@ -10931,13 +10931,13 @@
         <f aca="false">IFERROR(N270/H270,"")</f>
         <v/>
       </c>
-      <c r="P270" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A270,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q270" s="15" t="n">
-        <f aca="false">IFERROR(H270-P270,"")</f>
-        <v>0</v>
+      <c r="P270" s="15" t="str">
+        <f aca="false">IF($A270="","",IF(COUNTIF($A$3:$A270,$A270)=1,SUMIF(cobranza!$B$3:$B$1000,$A270,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q270" s="15" t="str">
+        <f aca="false">IF($A270="","",IF(COUNTIF($A$3:$A270,$A270)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A270,$C$3:$C$1000,"&lt;&gt;Demo")-P270,"↑"))</f>
+        <v/>
       </c>
       <c r="R270" s="17"/>
     </row>
@@ -10963,13 +10963,13 @@
         <f aca="false">IFERROR(N271/H271,"")</f>
         <v/>
       </c>
-      <c r="P271" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A271,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q271" s="15" t="n">
-        <f aca="false">IFERROR(H271-P271,"")</f>
-        <v>0</v>
+      <c r="P271" s="15" t="str">
+        <f aca="false">IF($A271="","",IF(COUNTIF($A$3:$A271,$A271)=1,SUMIF(cobranza!$B$3:$B$1000,$A271,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q271" s="15" t="str">
+        <f aca="false">IF($A271="","",IF(COUNTIF($A$3:$A271,$A271)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A271,$C$3:$C$1000,"&lt;&gt;Demo")-P271,"↑"))</f>
+        <v/>
       </c>
       <c r="R271" s="17"/>
     </row>
@@ -10995,13 +10995,13 @@
         <f aca="false">IFERROR(N272/H272,"")</f>
         <v/>
       </c>
-      <c r="P272" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A272,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q272" s="15" t="n">
-        <f aca="false">IFERROR(H272-P272,"")</f>
-        <v>0</v>
+      <c r="P272" s="15" t="str">
+        <f aca="false">IF($A272="","",IF(COUNTIF($A$3:$A272,$A272)=1,SUMIF(cobranza!$B$3:$B$1000,$A272,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q272" s="15" t="str">
+        <f aca="false">IF($A272="","",IF(COUNTIF($A$3:$A272,$A272)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A272,$C$3:$C$1000,"&lt;&gt;Demo")-P272,"↑"))</f>
+        <v/>
       </c>
       <c r="R272" s="17"/>
     </row>
@@ -11027,13 +11027,13 @@
         <f aca="false">IFERROR(N273/H273,"")</f>
         <v/>
       </c>
-      <c r="P273" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A273,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q273" s="15" t="n">
-        <f aca="false">IFERROR(H273-P273,"")</f>
-        <v>0</v>
+      <c r="P273" s="15" t="str">
+        <f aca="false">IF($A273="","",IF(COUNTIF($A$3:$A273,$A273)=1,SUMIF(cobranza!$B$3:$B$1000,$A273,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q273" s="15" t="str">
+        <f aca="false">IF($A273="","",IF(COUNTIF($A$3:$A273,$A273)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A273,$C$3:$C$1000,"&lt;&gt;Demo")-P273,"↑"))</f>
+        <v/>
       </c>
       <c r="R273" s="17"/>
     </row>
@@ -11059,13 +11059,13 @@
         <f aca="false">IFERROR(N274/H274,"")</f>
         <v/>
       </c>
-      <c r="P274" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A274,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q274" s="15" t="n">
-        <f aca="false">IFERROR(H274-P274,"")</f>
-        <v>0</v>
+      <c r="P274" s="15" t="str">
+        <f aca="false">IF($A274="","",IF(COUNTIF($A$3:$A274,$A274)=1,SUMIF(cobranza!$B$3:$B$1000,$A274,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q274" s="15" t="str">
+        <f aca="false">IF($A274="","",IF(COUNTIF($A$3:$A274,$A274)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A274,$C$3:$C$1000,"&lt;&gt;Demo")-P274,"↑"))</f>
+        <v/>
       </c>
       <c r="R274" s="17"/>
     </row>
@@ -11091,13 +11091,13 @@
         <f aca="false">IFERROR(N275/H275,"")</f>
         <v/>
       </c>
-      <c r="P275" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A275,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q275" s="15" t="n">
-        <f aca="false">IFERROR(H275-P275,"")</f>
-        <v>0</v>
+      <c r="P275" s="15" t="str">
+        <f aca="false">IF($A275="","",IF(COUNTIF($A$3:$A275,$A275)=1,SUMIF(cobranza!$B$3:$B$1000,$A275,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q275" s="15" t="str">
+        <f aca="false">IF($A275="","",IF(COUNTIF($A$3:$A275,$A275)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A275,$C$3:$C$1000,"&lt;&gt;Demo")-P275,"↑"))</f>
+        <v/>
       </c>
       <c r="R275" s="17"/>
     </row>
@@ -11123,13 +11123,13 @@
         <f aca="false">IFERROR(N276/H276,"")</f>
         <v/>
       </c>
-      <c r="P276" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A276,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q276" s="15" t="n">
-        <f aca="false">IFERROR(H276-P276,"")</f>
-        <v>0</v>
+      <c r="P276" s="15" t="str">
+        <f aca="false">IF($A276="","",IF(COUNTIF($A$3:$A276,$A276)=1,SUMIF(cobranza!$B$3:$B$1000,$A276,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q276" s="15" t="str">
+        <f aca="false">IF($A276="","",IF(COUNTIF($A$3:$A276,$A276)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A276,$C$3:$C$1000,"&lt;&gt;Demo")-P276,"↑"))</f>
+        <v/>
       </c>
       <c r="R276" s="17"/>
     </row>
@@ -11155,13 +11155,13 @@
         <f aca="false">IFERROR(N277/H277,"")</f>
         <v/>
       </c>
-      <c r="P277" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A277,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q277" s="15" t="n">
-        <f aca="false">IFERROR(H277-P277,"")</f>
-        <v>0</v>
+      <c r="P277" s="15" t="str">
+        <f aca="false">IF($A277="","",IF(COUNTIF($A$3:$A277,$A277)=1,SUMIF(cobranza!$B$3:$B$1000,$A277,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q277" s="15" t="str">
+        <f aca="false">IF($A277="","",IF(COUNTIF($A$3:$A277,$A277)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A277,$C$3:$C$1000,"&lt;&gt;Demo")-P277,"↑"))</f>
+        <v/>
       </c>
       <c r="R277" s="17"/>
     </row>
@@ -11187,13 +11187,13 @@
         <f aca="false">IFERROR(N278/H278,"")</f>
         <v/>
       </c>
-      <c r="P278" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A278,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q278" s="15" t="n">
-        <f aca="false">IFERROR(H278-P278,"")</f>
-        <v>0</v>
+      <c r="P278" s="15" t="str">
+        <f aca="false">IF($A278="","",IF(COUNTIF($A$3:$A278,$A278)=1,SUMIF(cobranza!$B$3:$B$1000,$A278,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q278" s="15" t="str">
+        <f aca="false">IF($A278="","",IF(COUNTIF($A$3:$A278,$A278)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A278,$C$3:$C$1000,"&lt;&gt;Demo")-P278,"↑"))</f>
+        <v/>
       </c>
       <c r="R278" s="17"/>
     </row>
@@ -11219,13 +11219,13 @@
         <f aca="false">IFERROR(N279/H279,"")</f>
         <v/>
       </c>
-      <c r="P279" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A279,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q279" s="15" t="n">
-        <f aca="false">IFERROR(H279-P279,"")</f>
-        <v>0</v>
+      <c r="P279" s="15" t="str">
+        <f aca="false">IF($A279="","",IF(COUNTIF($A$3:$A279,$A279)=1,SUMIF(cobranza!$B$3:$B$1000,$A279,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q279" s="15" t="str">
+        <f aca="false">IF($A279="","",IF(COUNTIF($A$3:$A279,$A279)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A279,$C$3:$C$1000,"&lt;&gt;Demo")-P279,"↑"))</f>
+        <v/>
       </c>
       <c r="R279" s="17"/>
     </row>
@@ -11251,13 +11251,13 @@
         <f aca="false">IFERROR(N280/H280,"")</f>
         <v/>
       </c>
-      <c r="P280" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A280,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q280" s="15" t="n">
-        <f aca="false">IFERROR(H280-P280,"")</f>
-        <v>0</v>
+      <c r="P280" s="15" t="str">
+        <f aca="false">IF($A280="","",IF(COUNTIF($A$3:$A280,$A280)=1,SUMIF(cobranza!$B$3:$B$1000,$A280,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q280" s="15" t="str">
+        <f aca="false">IF($A280="","",IF(COUNTIF($A$3:$A280,$A280)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A280,$C$3:$C$1000,"&lt;&gt;Demo")-P280,"↑"))</f>
+        <v/>
       </c>
       <c r="R280" s="17"/>
     </row>
@@ -11283,13 +11283,13 @@
         <f aca="false">IFERROR(N281/H281,"")</f>
         <v/>
       </c>
-      <c r="P281" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A281,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q281" s="15" t="n">
-        <f aca="false">IFERROR(H281-P281,"")</f>
-        <v>0</v>
+      <c r="P281" s="15" t="str">
+        <f aca="false">IF($A281="","",IF(COUNTIF($A$3:$A281,$A281)=1,SUMIF(cobranza!$B$3:$B$1000,$A281,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q281" s="15" t="str">
+        <f aca="false">IF($A281="","",IF(COUNTIF($A$3:$A281,$A281)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A281,$C$3:$C$1000,"&lt;&gt;Demo")-P281,"↑"))</f>
+        <v/>
       </c>
       <c r="R281" s="17"/>
     </row>
@@ -11315,13 +11315,13 @@
         <f aca="false">IFERROR(N282/H282,"")</f>
         <v/>
       </c>
-      <c r="P282" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A282,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q282" s="15" t="n">
-        <f aca="false">IFERROR(H282-P282,"")</f>
-        <v>0</v>
+      <c r="P282" s="15" t="str">
+        <f aca="false">IF($A282="","",IF(COUNTIF($A$3:$A282,$A282)=1,SUMIF(cobranza!$B$3:$B$1000,$A282,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q282" s="15" t="str">
+        <f aca="false">IF($A282="","",IF(COUNTIF($A$3:$A282,$A282)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A282,$C$3:$C$1000,"&lt;&gt;Demo")-P282,"↑"))</f>
+        <v/>
       </c>
       <c r="R282" s="17"/>
     </row>
@@ -11347,13 +11347,13 @@
         <f aca="false">IFERROR(N283/H283,"")</f>
         <v/>
       </c>
-      <c r="P283" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A283,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q283" s="15" t="n">
-        <f aca="false">IFERROR(H283-P283,"")</f>
-        <v>0</v>
+      <c r="P283" s="15" t="str">
+        <f aca="false">IF($A283="","",IF(COUNTIF($A$3:$A283,$A283)=1,SUMIF(cobranza!$B$3:$B$1000,$A283,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q283" s="15" t="str">
+        <f aca="false">IF($A283="","",IF(COUNTIF($A$3:$A283,$A283)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A283,$C$3:$C$1000,"&lt;&gt;Demo")-P283,"↑"))</f>
+        <v/>
       </c>
       <c r="R283" s="17"/>
     </row>
@@ -11379,13 +11379,13 @@
         <f aca="false">IFERROR(N284/H284,"")</f>
         <v/>
       </c>
-      <c r="P284" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A284,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q284" s="15" t="n">
-        <f aca="false">IFERROR(H284-P284,"")</f>
-        <v>0</v>
+      <c r="P284" s="15" t="str">
+        <f aca="false">IF($A284="","",IF(COUNTIF($A$3:$A284,$A284)=1,SUMIF(cobranza!$B$3:$B$1000,$A284,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q284" s="15" t="str">
+        <f aca="false">IF($A284="","",IF(COUNTIF($A$3:$A284,$A284)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A284,$C$3:$C$1000,"&lt;&gt;Demo")-P284,"↑"))</f>
+        <v/>
       </c>
       <c r="R284" s="17"/>
     </row>
@@ -11411,13 +11411,13 @@
         <f aca="false">IFERROR(N285/H285,"")</f>
         <v/>
       </c>
-      <c r="P285" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A285,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q285" s="15" t="n">
-        <f aca="false">IFERROR(H285-P285,"")</f>
-        <v>0</v>
+      <c r="P285" s="15" t="str">
+        <f aca="false">IF($A285="","",IF(COUNTIF($A$3:$A285,$A285)=1,SUMIF(cobranza!$B$3:$B$1000,$A285,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q285" s="15" t="str">
+        <f aca="false">IF($A285="","",IF(COUNTIF($A$3:$A285,$A285)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A285,$C$3:$C$1000,"&lt;&gt;Demo")-P285,"↑"))</f>
+        <v/>
       </c>
       <c r="R285" s="17"/>
     </row>
@@ -11443,13 +11443,13 @@
         <f aca="false">IFERROR(N286/H286,"")</f>
         <v/>
       </c>
-      <c r="P286" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A286,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q286" s="15" t="n">
-        <f aca="false">IFERROR(H286-P286,"")</f>
-        <v>0</v>
+      <c r="P286" s="15" t="str">
+        <f aca="false">IF($A286="","",IF(COUNTIF($A$3:$A286,$A286)=1,SUMIF(cobranza!$B$3:$B$1000,$A286,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q286" s="15" t="str">
+        <f aca="false">IF($A286="","",IF(COUNTIF($A$3:$A286,$A286)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A286,$C$3:$C$1000,"&lt;&gt;Demo")-P286,"↑"))</f>
+        <v/>
       </c>
       <c r="R286" s="17"/>
     </row>
@@ -11475,13 +11475,13 @@
         <f aca="false">IFERROR(N287/H287,"")</f>
         <v/>
       </c>
-      <c r="P287" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A287,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q287" s="15" t="n">
-        <f aca="false">IFERROR(H287-P287,"")</f>
-        <v>0</v>
+      <c r="P287" s="15" t="str">
+        <f aca="false">IF($A287="","",IF(COUNTIF($A$3:$A287,$A287)=1,SUMIF(cobranza!$B$3:$B$1000,$A287,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q287" s="15" t="str">
+        <f aca="false">IF($A287="","",IF(COUNTIF($A$3:$A287,$A287)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A287,$C$3:$C$1000,"&lt;&gt;Demo")-P287,"↑"))</f>
+        <v/>
       </c>
       <c r="R287" s="17"/>
     </row>
@@ -11507,13 +11507,13 @@
         <f aca="false">IFERROR(N288/H288,"")</f>
         <v/>
       </c>
-      <c r="P288" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A288,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q288" s="15" t="n">
-        <f aca="false">IFERROR(H288-P288,"")</f>
-        <v>0</v>
+      <c r="P288" s="15" t="str">
+        <f aca="false">IF($A288="","",IF(COUNTIF($A$3:$A288,$A288)=1,SUMIF(cobranza!$B$3:$B$1000,$A288,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q288" s="15" t="str">
+        <f aca="false">IF($A288="","",IF(COUNTIF($A$3:$A288,$A288)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A288,$C$3:$C$1000,"&lt;&gt;Demo")-P288,"↑"))</f>
+        <v/>
       </c>
       <c r="R288" s="17"/>
     </row>
@@ -11539,13 +11539,13 @@
         <f aca="false">IFERROR(N289/H289,"")</f>
         <v/>
       </c>
-      <c r="P289" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A289,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q289" s="15" t="n">
-        <f aca="false">IFERROR(H289-P289,"")</f>
-        <v>0</v>
+      <c r="P289" s="15" t="str">
+        <f aca="false">IF($A289="","",IF(COUNTIF($A$3:$A289,$A289)=1,SUMIF(cobranza!$B$3:$B$1000,$A289,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q289" s="15" t="str">
+        <f aca="false">IF($A289="","",IF(COUNTIF($A$3:$A289,$A289)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A289,$C$3:$C$1000,"&lt;&gt;Demo")-P289,"↑"))</f>
+        <v/>
       </c>
       <c r="R289" s="17"/>
     </row>
@@ -11571,13 +11571,13 @@
         <f aca="false">IFERROR(N290/H290,"")</f>
         <v/>
       </c>
-      <c r="P290" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A290,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q290" s="15" t="n">
-        <f aca="false">IFERROR(H290-P290,"")</f>
-        <v>0</v>
+      <c r="P290" s="15" t="str">
+        <f aca="false">IF($A290="","",IF(COUNTIF($A$3:$A290,$A290)=1,SUMIF(cobranza!$B$3:$B$1000,$A290,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q290" s="15" t="str">
+        <f aca="false">IF($A290="","",IF(COUNTIF($A$3:$A290,$A290)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A290,$C$3:$C$1000,"&lt;&gt;Demo")-P290,"↑"))</f>
+        <v/>
       </c>
       <c r="R290" s="17"/>
     </row>
@@ -11603,13 +11603,13 @@
         <f aca="false">IFERROR(N291/H291,"")</f>
         <v/>
       </c>
-      <c r="P291" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A291,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q291" s="15" t="n">
-        <f aca="false">IFERROR(H291-P291,"")</f>
-        <v>0</v>
+      <c r="P291" s="15" t="str">
+        <f aca="false">IF($A291="","",IF(COUNTIF($A$3:$A291,$A291)=1,SUMIF(cobranza!$B$3:$B$1000,$A291,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q291" s="15" t="str">
+        <f aca="false">IF($A291="","",IF(COUNTIF($A$3:$A291,$A291)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A291,$C$3:$C$1000,"&lt;&gt;Demo")-P291,"↑"))</f>
+        <v/>
       </c>
       <c r="R291" s="17"/>
     </row>
@@ -11635,13 +11635,13 @@
         <f aca="false">IFERROR(N292/H292,"")</f>
         <v/>
       </c>
-      <c r="P292" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A292,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q292" s="15" t="n">
-        <f aca="false">IFERROR(H292-P292,"")</f>
-        <v>0</v>
+      <c r="P292" s="15" t="str">
+        <f aca="false">IF($A292="","",IF(COUNTIF($A$3:$A292,$A292)=1,SUMIF(cobranza!$B$3:$B$1000,$A292,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q292" s="15" t="str">
+        <f aca="false">IF($A292="","",IF(COUNTIF($A$3:$A292,$A292)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A292,$C$3:$C$1000,"&lt;&gt;Demo")-P292,"↑"))</f>
+        <v/>
       </c>
       <c r="R292" s="17"/>
     </row>
@@ -11667,13 +11667,13 @@
         <f aca="false">IFERROR(N293/H293,"")</f>
         <v/>
       </c>
-      <c r="P293" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A293,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q293" s="15" t="n">
-        <f aca="false">IFERROR(H293-P293,"")</f>
-        <v>0</v>
+      <c r="P293" s="15" t="str">
+        <f aca="false">IF($A293="","",IF(COUNTIF($A$3:$A293,$A293)=1,SUMIF(cobranza!$B$3:$B$1000,$A293,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q293" s="15" t="str">
+        <f aca="false">IF($A293="","",IF(COUNTIF($A$3:$A293,$A293)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A293,$C$3:$C$1000,"&lt;&gt;Demo")-P293,"↑"))</f>
+        <v/>
       </c>
       <c r="R293" s="17"/>
     </row>
@@ -11699,13 +11699,13 @@
         <f aca="false">IFERROR(N294/H294,"")</f>
         <v/>
       </c>
-      <c r="P294" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A294,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q294" s="15" t="n">
-        <f aca="false">IFERROR(H294-P294,"")</f>
-        <v>0</v>
+      <c r="P294" s="15" t="str">
+        <f aca="false">IF($A294="","",IF(COUNTIF($A$3:$A294,$A294)=1,SUMIF(cobranza!$B$3:$B$1000,$A294,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q294" s="15" t="str">
+        <f aca="false">IF($A294="","",IF(COUNTIF($A$3:$A294,$A294)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A294,$C$3:$C$1000,"&lt;&gt;Demo")-P294,"↑"))</f>
+        <v/>
       </c>
       <c r="R294" s="17"/>
     </row>
@@ -11731,13 +11731,13 @@
         <f aca="false">IFERROR(N295/H295,"")</f>
         <v/>
       </c>
-      <c r="P295" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A295,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q295" s="15" t="n">
-        <f aca="false">IFERROR(H295-P295,"")</f>
-        <v>0</v>
+      <c r="P295" s="15" t="str">
+        <f aca="false">IF($A295="","",IF(COUNTIF($A$3:$A295,$A295)=1,SUMIF(cobranza!$B$3:$B$1000,$A295,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q295" s="15" t="str">
+        <f aca="false">IF($A295="","",IF(COUNTIF($A$3:$A295,$A295)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A295,$C$3:$C$1000,"&lt;&gt;Demo")-P295,"↑"))</f>
+        <v/>
       </c>
       <c r="R295" s="17"/>
     </row>
@@ -11763,13 +11763,13 @@
         <f aca="false">IFERROR(N296/H296,"")</f>
         <v/>
       </c>
-      <c r="P296" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A296,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q296" s="15" t="n">
-        <f aca="false">IFERROR(H296-P296,"")</f>
-        <v>0</v>
+      <c r="P296" s="15" t="str">
+        <f aca="false">IF($A296="","",IF(COUNTIF($A$3:$A296,$A296)=1,SUMIF(cobranza!$B$3:$B$1000,$A296,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q296" s="15" t="str">
+        <f aca="false">IF($A296="","",IF(COUNTIF($A$3:$A296,$A296)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A296,$C$3:$C$1000,"&lt;&gt;Demo")-P296,"↑"))</f>
+        <v/>
       </c>
       <c r="R296" s="17"/>
     </row>
@@ -11795,13 +11795,13 @@
         <f aca="false">IFERROR(N297/H297,"")</f>
         <v/>
       </c>
-      <c r="P297" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A297,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q297" s="15" t="n">
-        <f aca="false">IFERROR(H297-P297,"")</f>
-        <v>0</v>
+      <c r="P297" s="15" t="str">
+        <f aca="false">IF($A297="","",IF(COUNTIF($A$3:$A297,$A297)=1,SUMIF(cobranza!$B$3:$B$1000,$A297,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q297" s="15" t="str">
+        <f aca="false">IF($A297="","",IF(COUNTIF($A$3:$A297,$A297)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A297,$C$3:$C$1000,"&lt;&gt;Demo")-P297,"↑"))</f>
+        <v/>
       </c>
       <c r="R297" s="17"/>
     </row>
@@ -11827,13 +11827,13 @@
         <f aca="false">IFERROR(N298/H298,"")</f>
         <v/>
       </c>
-      <c r="P298" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A298,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q298" s="15" t="n">
-        <f aca="false">IFERROR(H298-P298,"")</f>
-        <v>0</v>
+      <c r="P298" s="15" t="str">
+        <f aca="false">IF($A298="","",IF(COUNTIF($A$3:$A298,$A298)=1,SUMIF(cobranza!$B$3:$B$1000,$A298,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q298" s="15" t="str">
+        <f aca="false">IF($A298="","",IF(COUNTIF($A$3:$A298,$A298)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A298,$C$3:$C$1000,"&lt;&gt;Demo")-P298,"↑"))</f>
+        <v/>
       </c>
       <c r="R298" s="17"/>
     </row>
@@ -11859,13 +11859,13 @@
         <f aca="false">IFERROR(N299/H299,"")</f>
         <v/>
       </c>
-      <c r="P299" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A299,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q299" s="15" t="n">
-        <f aca="false">IFERROR(H299-P299,"")</f>
-        <v>0</v>
+      <c r="P299" s="15" t="str">
+        <f aca="false">IF($A299="","",IF(COUNTIF($A$3:$A299,$A299)=1,SUMIF(cobranza!$B$3:$B$1000,$A299,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q299" s="15" t="str">
+        <f aca="false">IF($A299="","",IF(COUNTIF($A$3:$A299,$A299)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A299,$C$3:$C$1000,"&lt;&gt;Demo")-P299,"↑"))</f>
+        <v/>
       </c>
       <c r="R299" s="17"/>
     </row>
@@ -11891,13 +11891,13 @@
         <f aca="false">IFERROR(N300/H300,"")</f>
         <v/>
       </c>
-      <c r="P300" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A300,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q300" s="15" t="n">
-        <f aca="false">IFERROR(H300-P300,"")</f>
-        <v>0</v>
+      <c r="P300" s="15" t="str">
+        <f aca="false">IF($A300="","",IF(COUNTIF($A$3:$A300,$A300)=1,SUMIF(cobranza!$B$3:$B$1000,$A300,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q300" s="15" t="str">
+        <f aca="false">IF($A300="","",IF(COUNTIF($A$3:$A300,$A300)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A300,$C$3:$C$1000,"&lt;&gt;Demo")-P300,"↑"))</f>
+        <v/>
       </c>
       <c r="R300" s="17"/>
     </row>
@@ -11923,13 +11923,13 @@
         <f aca="false">IFERROR(N301/H301,"")</f>
         <v/>
       </c>
-      <c r="P301" s="15" t="n">
-        <f aca="false">IFERROR(SUMIF(cobranza!$B$3:$B$1000,A301,cobranza!$D$3:$D$1000),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q301" s="15" t="n">
-        <f aca="false">IFERROR(H301-P301,"")</f>
-        <v>0</v>
+      <c r="P301" s="15" t="str">
+        <f aca="false">IF($A301="","",IF(COUNTIF($A$3:$A301,$A301)=1,SUMIF(cobranza!$B$3:$B$1000,$A301,cobranza!$D$3:$D$1000),"↑"))</f>
+        <v/>
+      </c>
+      <c r="Q301" s="15" t="str">
+        <f aca="false">IF($A301="","",IF(COUNTIF($A$3:$A301,$A301)=1,SUMIFS($H$3:$H$1000,$A$3:$A$1000,$A301,$C$3:$C$1000,"&lt;&gt;Demo")-P301,"↑"))</f>
+        <v/>
       </c>
       <c r="R301" s="17"/>
     </row>
